--- a/configs/Affix.xlsx
+++ b/configs/Affix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D39176B7-F281-47C9-96DA-BEDB5017C18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30393F42-C89C-4408-850D-0A29CE4954CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="585">
   <si>
     <t>id</t>
   </si>
@@ -1786,6 +1786,45 @@
   </si>
   <si>
     <t>armor,belt,boot,glove,helm,necklace,pant,pauldron,ring,weapon,bracelet</t>
+  </si>
+  <si>
+    <t>prockill</t>
+  </si>
+  <si>
+    <t>killfwal1</t>
+  </si>
+  <si>
+    <t>fwal</t>
+  </si>
+  <si>
+    <t>killbclv1</t>
+  </si>
+  <si>
+    <t>bclv</t>
+  </si>
+  <si>
+    <t>killxcta1</t>
+  </si>
+  <si>
+    <t>xcta</t>
+  </si>
+  <si>
+    <t>火墙术的</t>
+  </si>
+  <si>
+    <t>killpskl1</t>
+  </si>
+  <si>
+    <t>骷髅术的</t>
+  </si>
+  <si>
+    <t>弯刀术的</t>
+  </si>
+  <si>
+    <t>指挥术的</t>
+  </si>
+  <si>
+    <t>pskl</t>
   </si>
 </sst>
 </file>
@@ -2305,7 +2344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q203"/>
+  <dimension ref="A1:Q207"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="2" width="12.26953125" style="1" bestFit="1" customWidth="1"/>
@@ -8305,7 +8344,7 @@
         <v>6-54</v>
       </c>
       <c r="Q133" s="1">
-        <f t="shared" ref="Q133:Q139" si="33">_xlfn.LET(_xlpm.a,($E133+P$3*$G133)*(1+P$2),_xlpm.b,($F133+P$3*$H133)*(1+P$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <f t="shared" ref="Q133:Q140" si="33">_xlfn.LET(_xlpm.a,($E133+P$3*$G133)*(1+P$2),_xlpm.b,($F133+P$3*$H133)*(1+P$2),_xlpm.a/2+_xlpm.b/2)</f>
         <v>30</v>
       </c>
     </row>
@@ -8344,7 +8383,7 @@
         <v>558</v>
       </c>
       <c r="N134" s="1" t="str">
-        <f t="shared" ref="N134:P149" si="34">_xlfn.LET(_xlpm.a,($E134+N$3*$G134)*(1+N$2),_xlpm.b,($F134+N$3*$H134)*(1+N$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
+        <f t="shared" ref="N134:P153" si="34">_xlfn.LET(_xlpm.a,($E134+N$3*$G134)*(1+N$2),_xlpm.b,($F134+N$3*$H134)*(1+N$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
         <v>1-1</v>
       </c>
       <c r="O134" s="1" t="str">
@@ -8617,106 +8656,118 @@
     </row>
     <row r="140" spans="1:17">
       <c r="A140" s="1" t="s">
-        <v>118</v>
+        <v>573</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>543</v>
+        <v>579</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>252</v>
+        <v>572</v>
       </c>
       <c r="E140" s="1">
         <v>1</v>
       </c>
       <c r="F140" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G140" s="1">
         <v>0</v>
       </c>
       <c r="H140" s="1">
-        <v>1.25</v>
+        <v>2</v>
+      </c>
+      <c r="K140" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="L140" s="1" t="s">
+        <v>564</v>
       </c>
       <c r="M140" s="1" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="N140" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>1-10</v>
+        <v>1-1</v>
       </c>
       <c r="O140" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>1-15</v>
+        <v>1-9</v>
       </c>
       <c r="P140" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>6-90</v>
+        <v>6-54</v>
       </c>
       <c r="Q140" s="1">
-        <f t="shared" ref="Q140" si="35">_xlfn.LET(_xlpm.a,($E140+P$3*$G140)*(1+P$2),_xlpm.b,($F140+P$3*$H140)*(1+P$2),_xlpm.a/2+_xlpm.b/2)</f>
-        <v>48</v>
+        <f t="shared" si="33"/>
+        <v>30</v>
       </c>
     </row>
     <row r="141" spans="1:17">
       <c r="A141" s="1" t="s">
-        <v>277</v>
+        <v>575</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>544</v>
+        <v>582</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>278</v>
+        <v>572</v>
       </c>
       <c r="E141" s="1">
         <v>1</v>
       </c>
       <c r="F141" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G141" s="1">
         <v>0</v>
       </c>
       <c r="H141" s="1">
-        <v>1.25</v>
+        <v>2</v>
+      </c>
+      <c r="K141" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="L141" s="1" t="s">
+        <v>564</v>
       </c>
       <c r="M141" s="1" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="N141" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>1-10</v>
+        <v>1-1</v>
       </c>
       <c r="O141" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>1-15</v>
+        <v>1-9</v>
       </c>
       <c r="P141" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>6-90</v>
+        <v>6-54</v>
       </c>
       <c r="Q141" s="1">
-        <f t="shared" ref="Q141" si="36">_xlfn.LET(_xlpm.a,($E141+P$3*$G141)*(1+P$2),_xlpm.b,($F141+P$3*$H141)*(1+P$2),_xlpm.a/2+_xlpm.b/2)</f>
-        <v>48</v>
+        <f t="shared" ref="Q141" si="35">_xlfn.LET(_xlpm.a,($E141+P$3*$G141)*(1+P$2),_xlpm.b,($F141+P$3*$H141)*(1+P$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <v>30</v>
       </c>
     </row>
     <row r="142" spans="1:17">
       <c r="A142" s="1" t="s">
-        <v>279</v>
+        <v>577</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>545</v>
+        <v>583</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>280</v>
+        <v>572</v>
       </c>
       <c r="E142" s="1">
         <v>1</v>
@@ -8728,10 +8779,16 @@
         <v>0</v>
       </c>
       <c r="H142" s="1">
-        <v>0.25</v>
+        <v>2</v>
+      </c>
+      <c r="K142" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="L142" s="1" t="s">
+        <v>564</v>
       </c>
       <c r="M142" s="1" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="N142" s="1" t="str">
         <f t="shared" si="34"/>
@@ -8739,494 +8796,512 @@
       </c>
       <c r="O142" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>1-2</v>
+        <v>1-9</v>
       </c>
       <c r="P142" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>6-12</v>
+        <v>6-54</v>
       </c>
       <c r="Q142" s="1">
-        <f t="shared" ref="Q142" si="37">_xlfn.LET(_xlpm.a,($E142+P$3*$G142)*(1+P$2),_xlpm.b,($F142+P$3*$H142)*(1+P$2),_xlpm.a/2+_xlpm.b/2)</f>
-        <v>9</v>
+        <f t="shared" ref="Q142" si="36">_xlfn.LET(_xlpm.a,($E142+P$3*$G142)*(1+P$2),_xlpm.b,($F142+P$3*$H142)*(1+P$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <v>30</v>
       </c>
     </row>
     <row r="143" spans="1:17">
       <c r="A143" s="1" t="s">
-        <v>283</v>
+        <v>580</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>546</v>
+        <v>581</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>281</v>
+        <v>572</v>
       </c>
       <c r="E143" s="1">
         <v>1</v>
       </c>
       <c r="F143" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G143" s="1">
         <v>0</v>
       </c>
       <c r="H143" s="1">
-        <v>1.25</v>
+        <v>2</v>
+      </c>
+      <c r="K143" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="L143" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="M143" s="1" t="s">
+        <v>570</v>
       </c>
       <c r="N143" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>1-5</v>
+        <v>1-1</v>
       </c>
       <c r="O143" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>1-10</v>
+        <v>1-9</v>
       </c>
       <c r="P143" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>6-60</v>
+        <v>6-54</v>
       </c>
       <c r="Q143" s="1">
-        <f t="shared" ref="Q143:Q144" si="38">_xlfn.LET(_xlpm.a,($E143+P$3*$G143)*(1+P$2),_xlpm.b,($F143+P$3*$H143)*(1+P$2),_xlpm.a/2+_xlpm.b/2)</f>
-        <v>33</v>
+        <f t="shared" ref="Q143" si="37">_xlfn.LET(_xlpm.a,($E143+P$3*$G143)*(1+P$2),_xlpm.b,($F143+P$3*$H143)*(1+P$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <v>30</v>
       </c>
     </row>
     <row r="144" spans="1:17">
       <c r="A144" s="1" t="s">
-        <v>284</v>
+        <v>118</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>282</v>
+        <v>252</v>
       </c>
       <c r="E144" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F144" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G144" s="1">
+        <v>0</v>
+      </c>
+      <c r="H144" s="1">
         <v>1.25</v>
       </c>
-      <c r="H144" s="1">
-        <v>8.75</v>
-      </c>
       <c r="M144" s="1" t="s">
-        <v>399</v>
+        <v>558</v>
       </c>
       <c r="N144" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>5-15</v>
+        <v>1-10</v>
       </c>
       <c r="O144" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>10-50</v>
+        <v>1-15</v>
       </c>
       <c r="P144" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>60-300</v>
+        <v>6-90</v>
       </c>
       <c r="Q144" s="1">
-        <f t="shared" si="38"/>
-        <v>180</v>
+        <f t="shared" ref="Q144" si="38">_xlfn.LET(_xlpm.a,($E144+P$3*$G144)*(1+P$2),_xlpm.b,($F144+P$3*$H144)*(1+P$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <v>48</v>
       </c>
     </row>
     <row r="145" spans="1:17">
       <c r="A145" s="1" t="s">
-        <v>302</v>
+        <v>277</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="E145" s="1">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="F145" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G145" s="1">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="H145" s="1">
         <v>1.25</v>
       </c>
+      <c r="M145" s="1" t="s">
+        <v>558</v>
+      </c>
       <c r="N145" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>2.5-5</v>
+        <v>1-10</v>
       </c>
       <c r="O145" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>5-10</v>
+        <v>1-15</v>
       </c>
       <c r="P145" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>30-60</v>
+        <v>6-90</v>
       </c>
       <c r="Q145" s="1">
         <f t="shared" ref="Q145" si="39">_xlfn.LET(_xlpm.a,($E145+P$3*$G145)*(1+P$2),_xlpm.b,($F145+P$3*$H145)*(1+P$2),_xlpm.a/2+_xlpm.b/2)</f>
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="146" spans="1:17">
       <c r="A146" s="1" t="s">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="E146" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F146" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G146" s="1">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="H146" s="1">
-        <v>2.5</v>
+        <v>0.25</v>
+      </c>
+      <c r="M146" s="1" t="s">
+        <v>558</v>
       </c>
       <c r="N146" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>5-10</v>
+        <v>1-1</v>
       </c>
       <c r="O146" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>10-20</v>
+        <v>1-2</v>
       </c>
       <c r="P146" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>60-120</v>
+        <v>6-12</v>
       </c>
       <c r="Q146" s="1">
-        <f t="shared" ref="Q146:Q185" si="40">_xlfn.LET(_xlpm.a,($E146+P$3*$G146)*(1+P$2),_xlpm.b,($F146+P$3*$H146)*(1+P$2),_xlpm.a/2+_xlpm.b/2)</f>
-        <v>90</v>
+        <f t="shared" ref="Q146" si="40">_xlfn.LET(_xlpm.a,($E146+P$3*$G146)*(1+P$2),_xlpm.b,($F146+P$3*$H146)*(1+P$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:17">
       <c r="A147" s="1" t="s">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="E147" s="1">
+        <v>1</v>
+      </c>
+      <c r="F147" s="1">
         <v>5</v>
       </c>
-      <c r="F147" s="1">
-        <v>10</v>
-      </c>
       <c r="G147" s="1">
+        <v>0</v>
+      </c>
+      <c r="H147" s="1">
         <v>1.25</v>
-      </c>
-      <c r="H147" s="1">
-        <v>2.5</v>
       </c>
       <c r="N147" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>5-10</v>
+        <v>1-5</v>
       </c>
       <c r="O147" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>10-20</v>
+        <v>1-10</v>
       </c>
       <c r="P147" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>60-120</v>
+        <v>6-60</v>
       </c>
       <c r="Q147" s="1">
-        <f t="shared" si="40"/>
-        <v>90</v>
+        <f t="shared" ref="Q147:Q148" si="41">_xlfn.LET(_xlpm.a,($E147+P$3*$G147)*(1+P$2),_xlpm.b,($F147+P$3*$H147)*(1+P$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <v>33</v>
       </c>
     </row>
     <row r="148" spans="1:17">
       <c r="A148" s="1" t="s">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="E148" s="1">
         <v>5</v>
       </c>
       <c r="F148" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G148" s="1">
         <v>1.25</v>
       </c>
       <c r="H148" s="1">
-        <v>2.5</v>
+        <v>8.75</v>
+      </c>
+      <c r="M148" s="1" t="s">
+        <v>399</v>
       </c>
       <c r="N148" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>5-10</v>
+        <v>5-15</v>
       </c>
       <c r="O148" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>10-20</v>
+        <v>10-50</v>
       </c>
       <c r="P148" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>60-120</v>
+        <v>60-300</v>
       </c>
       <c r="Q148" s="1">
-        <f t="shared" si="40"/>
-        <v>90</v>
+        <f t="shared" si="41"/>
+        <v>180</v>
       </c>
     </row>
     <row r="149" spans="1:17">
       <c r="A149" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E149" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="F149" s="1">
         <v>5</v>
       </c>
-      <c r="F149" s="1">
-        <v>10</v>
-      </c>
       <c r="G149" s="1">
+        <v>0.625</v>
+      </c>
+      <c r="H149" s="1">
         <v>1.25</v>
-      </c>
-      <c r="H149" s="1">
-        <v>2.5</v>
       </c>
       <c r="N149" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>5-10</v>
+        <v>2.5-5</v>
       </c>
       <c r="O149" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>10-20</v>
+        <v>5-10</v>
       </c>
       <c r="P149" s="1" t="str">
         <f t="shared" si="34"/>
-        <v>60-120</v>
+        <v>30-60</v>
       </c>
       <c r="Q149" s="1">
-        <f t="shared" si="40"/>
-        <v>90</v>
+        <f t="shared" ref="Q149" si="42">_xlfn.LET(_xlpm.a,($E149+P$3*$G149)*(1+P$2),_xlpm.b,($F149+P$3*$H149)*(1+P$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <v>45</v>
       </c>
     </row>
     <row r="150" spans="1:17">
       <c r="A150" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>308</v>
+        <v>549</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="E150" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F150" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G150" s="1">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="H150" s="1">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="N150" s="1" t="str">
-        <f t="shared" ref="N150:P165" si="41">_xlfn.LET(_xlpm.a,($E150+N$3*$G150)*(1+N$2),_xlpm.b,($F150+N$3*$H150)*(1+N$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
-        <v>1-1</v>
+        <f t="shared" si="34"/>
+        <v>5-10</v>
       </c>
       <c r="O150" s="1" t="str">
-        <f t="shared" si="41"/>
-        <v>1-3</v>
+        <f t="shared" si="34"/>
+        <v>10-20</v>
       </c>
       <c r="P150" s="1" t="str">
-        <f t="shared" si="41"/>
-        <v>6-18</v>
+        <f t="shared" si="34"/>
+        <v>60-120</v>
       </c>
       <c r="Q150" s="1">
-        <f t="shared" si="40"/>
-        <v>12</v>
+        <f t="shared" ref="Q150:Q189" si="43">_xlfn.LET(_xlpm.a,($E150+P$3*$G150)*(1+P$2),_xlpm.b,($F150+P$3*$H150)*(1+P$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <v>90</v>
       </c>
     </row>
     <row r="151" spans="1:17">
       <c r="A151" s="1" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>310</v>
+        <v>550</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="E151" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F151" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G151" s="1">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="H151" s="1">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="N151" s="1" t="str">
-        <f t="shared" si="41"/>
-        <v>1-1</v>
+        <f t="shared" si="34"/>
+        <v>5-10</v>
       </c>
       <c r="O151" s="1" t="str">
-        <f t="shared" si="41"/>
-        <v>1-3</v>
+        <f t="shared" si="34"/>
+        <v>10-20</v>
       </c>
       <c r="P151" s="1" t="str">
-        <f t="shared" si="41"/>
-        <v>6-18</v>
+        <f t="shared" si="34"/>
+        <v>60-120</v>
       </c>
       <c r="Q151" s="1">
-        <f t="shared" si="40"/>
-        <v>12</v>
+        <f t="shared" si="43"/>
+        <v>90</v>
       </c>
     </row>
     <row r="152" spans="1:17">
       <c r="A152" s="1" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>312</v>
+        <v>551</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="E152" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F152" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G152" s="1">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="H152" s="1">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="N152" s="1" t="str">
-        <f t="shared" si="41"/>
-        <v>1-1</v>
+        <f t="shared" si="34"/>
+        <v>5-10</v>
       </c>
       <c r="O152" s="1" t="str">
-        <f t="shared" si="41"/>
-        <v>1-3</v>
+        <f t="shared" si="34"/>
+        <v>10-20</v>
       </c>
       <c r="P152" s="1" t="str">
-        <f t="shared" si="41"/>
-        <v>6-18</v>
+        <f t="shared" si="34"/>
+        <v>60-120</v>
       </c>
       <c r="Q152" s="1">
-        <f t="shared" si="40"/>
-        <v>12</v>
+        <f t="shared" si="43"/>
+        <v>90</v>
       </c>
     </row>
     <row r="153" spans="1:17">
       <c r="A153" s="1" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>314</v>
+        <v>552</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="E153" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F153" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G153" s="1">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="H153" s="1">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="N153" s="1" t="str">
-        <f t="shared" si="41"/>
-        <v>1-1</v>
+        <f t="shared" si="34"/>
+        <v>5-10</v>
       </c>
       <c r="O153" s="1" t="str">
-        <f t="shared" si="41"/>
-        <v>1-3</v>
+        <f t="shared" si="34"/>
+        <v>10-20</v>
       </c>
       <c r="P153" s="1" t="str">
-        <f t="shared" si="41"/>
-        <v>6-18</v>
+        <f t="shared" si="34"/>
+        <v>60-120</v>
       </c>
       <c r="Q153" s="1">
-        <f t="shared" si="40"/>
-        <v>12</v>
+        <f t="shared" si="43"/>
+        <v>90</v>
       </c>
     </row>
     <row r="154" spans="1:17">
       <c r="A154" s="1" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="E154" s="1">
         <v>1</v>
@@ -9241,34 +9316,34 @@
         <v>0.5</v>
       </c>
       <c r="N154" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" ref="N154:P169" si="44">_xlfn.LET(_xlpm.a,($E154+N$3*$G154)*(1+N$2),_xlpm.b,($F154+N$3*$H154)*(1+N$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
         <v>1-1</v>
       </c>
       <c r="O154" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-3</v>
       </c>
       <c r="P154" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>6-18</v>
       </c>
       <c r="Q154" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="155" spans="1:17">
       <c r="A155" s="1" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E155" s="1">
         <v>1</v>
@@ -9283,34 +9358,34 @@
         <v>0.5</v>
       </c>
       <c r="N155" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-1</v>
       </c>
       <c r="O155" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-3</v>
       </c>
       <c r="P155" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>6-18</v>
       </c>
       <c r="Q155" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="156" spans="1:17">
       <c r="A156" s="1" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="E156" s="1">
         <v>1</v>
@@ -9325,34 +9400,34 @@
         <v>0.5</v>
       </c>
       <c r="N156" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-1</v>
       </c>
       <c r="O156" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-3</v>
       </c>
       <c r="P156" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>6-18</v>
       </c>
       <c r="Q156" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="157" spans="1:17">
       <c r="A157" s="1" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="E157" s="1">
         <v>1</v>
@@ -9367,34 +9442,34 @@
         <v>0.5</v>
       </c>
       <c r="N157" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-1</v>
       </c>
       <c r="O157" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-3</v>
       </c>
       <c r="P157" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>6-18</v>
       </c>
       <c r="Q157" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="158" spans="1:17">
       <c r="A158" s="1" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="E158" s="1">
         <v>1</v>
@@ -9409,34 +9484,34 @@
         <v>0.5</v>
       </c>
       <c r="N158" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-1</v>
       </c>
       <c r="O158" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-3</v>
       </c>
       <c r="P158" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>6-18</v>
       </c>
       <c r="Q158" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="159" spans="1:17">
       <c r="A159" s="1" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="E159" s="1">
         <v>1</v>
@@ -9451,34 +9526,34 @@
         <v>0.5</v>
       </c>
       <c r="N159" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-1</v>
       </c>
       <c r="O159" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-3</v>
       </c>
       <c r="P159" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>6-18</v>
       </c>
       <c r="Q159" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="160" spans="1:17">
       <c r="A160" s="1" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="E160" s="1">
         <v>1</v>
@@ -9493,34 +9568,34 @@
         <v>0.5</v>
       </c>
       <c r="N160" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-1</v>
       </c>
       <c r="O160" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-3</v>
       </c>
       <c r="P160" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>6-18</v>
       </c>
       <c r="Q160" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="161" spans="1:17">
       <c r="A161" s="1" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="E161" s="1">
         <v>1</v>
@@ -9535,34 +9610,34 @@
         <v>0.5</v>
       </c>
       <c r="N161" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-1</v>
       </c>
       <c r="O161" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-3</v>
       </c>
       <c r="P161" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>6-18</v>
       </c>
       <c r="Q161" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="162" spans="1:17">
       <c r="A162" s="1" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E162" s="1">
         <v>1</v>
@@ -9577,34 +9652,34 @@
         <v>0.5</v>
       </c>
       <c r="N162" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-1</v>
       </c>
       <c r="O162" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-3</v>
       </c>
       <c r="P162" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>6-18</v>
       </c>
       <c r="Q162" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="163" spans="1:17">
       <c r="A163" s="1" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="E163" s="1">
         <v>1</v>
@@ -9619,34 +9694,34 @@
         <v>0.5</v>
       </c>
       <c r="N163" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-1</v>
       </c>
       <c r="O163" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-3</v>
       </c>
       <c r="P163" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>6-18</v>
       </c>
       <c r="Q163" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="164" spans="1:17">
       <c r="A164" s="1" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="E164" s="1">
         <v>1</v>
@@ -9661,34 +9736,34 @@
         <v>0.5</v>
       </c>
       <c r="N164" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-1</v>
       </c>
       <c r="O164" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-3</v>
       </c>
       <c r="P164" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>6-18</v>
       </c>
       <c r="Q164" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="165" spans="1:17">
       <c r="A165" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E165" s="1">
         <v>1</v>
@@ -9703,34 +9778,34 @@
         <v>0.5</v>
       </c>
       <c r="N165" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-1</v>
       </c>
       <c r="O165" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>1-3</v>
       </c>
       <c r="P165" s="1" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>6-18</v>
       </c>
       <c r="Q165" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="166" spans="1:17">
       <c r="A166" s="1" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="E166" s="1">
         <v>1</v>
@@ -9745,34 +9820,34 @@
         <v>0.5</v>
       </c>
       <c r="N166" s="1" t="str">
-        <f t="shared" ref="N166:P187" si="42">_xlfn.LET(_xlpm.a,($E166+N$3*$G166)*(1+N$2),_xlpm.b,($F166+N$3*$H166)*(1+N$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
+        <f t="shared" si="44"/>
         <v>1-1</v>
       </c>
       <c r="O166" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>1-3</v>
       </c>
       <c r="P166" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>6-18</v>
       </c>
       <c r="Q166" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="167" spans="1:17">
       <c r="A167" s="1" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="E167" s="1">
         <v>1</v>
@@ -9787,34 +9862,34 @@
         <v>0.5</v>
       </c>
       <c r="N167" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>1-1</v>
       </c>
       <c r="O167" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>1-3</v>
       </c>
       <c r="P167" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>6-18</v>
       </c>
       <c r="Q167" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="168" spans="1:17">
       <c r="A168" s="1" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="E168" s="1">
         <v>1</v>
@@ -9829,34 +9904,34 @@
         <v>0.5</v>
       </c>
       <c r="N168" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>1-1</v>
       </c>
       <c r="O168" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>1-3</v>
       </c>
       <c r="P168" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>6-18</v>
       </c>
       <c r="Q168" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="169" spans="1:17">
       <c r="A169" s="1" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="E169" s="1">
         <v>1</v>
@@ -9871,34 +9946,34 @@
         <v>0.5</v>
       </c>
       <c r="N169" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>1-1</v>
       </c>
       <c r="O169" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>1-3</v>
       </c>
       <c r="P169" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>6-18</v>
       </c>
       <c r="Q169" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="170" spans="1:17">
       <c r="A170" s="1" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="E170" s="1">
         <v>1</v>
@@ -9913,34 +9988,34 @@
         <v>0.5</v>
       </c>
       <c r="N170" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" ref="N170:P191" si="45">_xlfn.LET(_xlpm.a,($E170+N$3*$G170)*(1+N$2),_xlpm.b,($F170+N$3*$H170)*(1+N$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
         <v>1-1</v>
       </c>
       <c r="O170" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-3</v>
       </c>
       <c r="P170" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>6-18</v>
       </c>
       <c r="Q170" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="171" spans="1:17">
       <c r="A171" s="1" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="E171" s="1">
         <v>1</v>
@@ -9955,34 +10030,34 @@
         <v>0.5</v>
       </c>
       <c r="N171" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-1</v>
       </c>
       <c r="O171" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-3</v>
       </c>
       <c r="P171" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>6-18</v>
       </c>
       <c r="Q171" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="172" spans="1:17">
       <c r="A172" s="1" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="E172" s="1">
         <v>1</v>
@@ -9997,34 +10072,34 @@
         <v>0.5</v>
       </c>
       <c r="N172" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-1</v>
       </c>
       <c r="O172" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-3</v>
       </c>
       <c r="P172" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>6-18</v>
       </c>
       <c r="Q172" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="173" spans="1:17">
       <c r="A173" s="1" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="E173" s="1">
         <v>1</v>
@@ -10039,34 +10114,34 @@
         <v>0.5</v>
       </c>
       <c r="N173" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-1</v>
       </c>
       <c r="O173" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-3</v>
       </c>
       <c r="P173" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>6-18</v>
       </c>
       <c r="Q173" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="174" spans="1:17">
       <c r="A174" s="1" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="E174" s="1">
         <v>1</v>
@@ -10081,34 +10156,34 @@
         <v>0.5</v>
       </c>
       <c r="N174" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-1</v>
       </c>
       <c r="O174" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-3</v>
       </c>
       <c r="P174" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>6-18</v>
       </c>
       <c r="Q174" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="175" spans="1:17">
       <c r="A175" s="1" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="E175" s="1">
         <v>1</v>
@@ -10123,34 +10198,34 @@
         <v>0.5</v>
       </c>
       <c r="N175" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-1</v>
       </c>
       <c r="O175" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-3</v>
       </c>
       <c r="P175" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>6-18</v>
       </c>
       <c r="Q175" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="176" spans="1:17">
       <c r="A176" s="1" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="E176" s="1">
         <v>1</v>
@@ -10165,34 +10240,34 @@
         <v>0.5</v>
       </c>
       <c r="N176" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-1</v>
       </c>
       <c r="O176" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-3</v>
       </c>
       <c r="P176" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>6-18</v>
       </c>
       <c r="Q176" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="177" spans="1:17">
       <c r="A177" s="1" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="E177" s="1">
         <v>1</v>
@@ -10207,34 +10282,34 @@
         <v>0.5</v>
       </c>
       <c r="N177" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-1</v>
       </c>
       <c r="O177" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-3</v>
       </c>
       <c r="P177" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>6-18</v>
       </c>
       <c r="Q177" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="178" spans="1:17">
       <c r="A178" s="1" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="E178" s="1">
         <v>1</v>
@@ -10249,34 +10324,34 @@
         <v>0.5</v>
       </c>
       <c r="N178" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-1</v>
       </c>
       <c r="O178" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-3</v>
       </c>
       <c r="P178" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>6-18</v>
       </c>
       <c r="Q178" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="179" spans="1:17">
       <c r="A179" s="1" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="E179" s="1">
         <v>1</v>
@@ -10291,34 +10366,34 @@
         <v>0.5</v>
       </c>
       <c r="N179" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-1</v>
       </c>
       <c r="O179" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-3</v>
       </c>
       <c r="P179" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>6-18</v>
       </c>
       <c r="Q179" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="180" spans="1:17">
       <c r="A180" s="1" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="E180" s="1">
         <v>1</v>
@@ -10333,34 +10408,34 @@
         <v>0.5</v>
       </c>
       <c r="N180" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-1</v>
       </c>
       <c r="O180" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-3</v>
       </c>
       <c r="P180" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>6-18</v>
       </c>
       <c r="Q180" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="181" spans="1:17">
       <c r="A181" s="1" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="E181" s="1">
         <v>1</v>
@@ -10375,34 +10450,34 @@
         <v>0.5</v>
       </c>
       <c r="N181" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-1</v>
       </c>
       <c r="O181" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-3</v>
       </c>
       <c r="P181" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>6-18</v>
       </c>
       <c r="Q181" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="182" spans="1:17">
       <c r="A182" s="1" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="E182" s="1">
         <v>1</v>
@@ -10417,34 +10492,34 @@
         <v>0.5</v>
       </c>
       <c r="N182" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-1</v>
       </c>
       <c r="O182" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-3</v>
       </c>
       <c r="P182" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>6-18</v>
       </c>
       <c r="Q182" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="183" spans="1:17">
       <c r="A183" s="1" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="E183" s="1">
         <v>1</v>
@@ -10459,34 +10534,34 @@
         <v>0.5</v>
       </c>
       <c r="N183" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-1</v>
       </c>
       <c r="O183" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-3</v>
       </c>
       <c r="P183" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>6-18</v>
       </c>
       <c r="Q183" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="184" spans="1:17">
       <c r="A184" s="1" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="E184" s="1">
         <v>1</v>
@@ -10501,34 +10576,34 @@
         <v>0.5</v>
       </c>
       <c r="N184" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-1</v>
       </c>
       <c r="O184" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-3</v>
       </c>
       <c r="P184" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>6-18</v>
       </c>
       <c r="Q184" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="185" spans="1:17">
       <c r="A185" s="1" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="E185" s="1">
         <v>1</v>
@@ -10543,34 +10618,34 @@
         <v>0.5</v>
       </c>
       <c r="N185" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-1</v>
       </c>
       <c r="O185" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-3</v>
       </c>
       <c r="P185" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>6-18</v>
       </c>
       <c r="Q185" s="1">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>12</v>
       </c>
     </row>
     <row r="186" spans="1:17">
       <c r="A186" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="E186" s="1">
         <v>1</v>
@@ -10582,37 +10657,37 @@
         <v>0</v>
       </c>
       <c r="H186" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N186" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-1</v>
       </c>
       <c r="O186" s="1" t="str">
-        <f t="shared" si="42"/>
-        <v>1-1</v>
+        <f t="shared" si="45"/>
+        <v>1-3</v>
       </c>
       <c r="P186" s="1" t="str">
-        <f t="shared" si="42"/>
-        <v>6-6</v>
+        <f t="shared" si="45"/>
+        <v>6-18</v>
       </c>
       <c r="Q186" s="1">
-        <f t="shared" ref="Q186" si="43">_xlfn.LET(_xlpm.a,($E186+P$3*$G186)*(1+P$2),_xlpm.b,($F186+P$3*$H186)*(1+P$2),_xlpm.a/2+_xlpm.b/2)</f>
-        <v>6</v>
+        <f t="shared" si="43"/>
+        <v>12</v>
       </c>
     </row>
     <row r="187" spans="1:17">
       <c r="A187" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="E187" s="1">
         <v>1</v>
@@ -10624,37 +10699,37 @@
         <v>0</v>
       </c>
       <c r="H187" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N187" s="1" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>1-1</v>
       </c>
       <c r="O187" s="1" t="str">
-        <f t="shared" si="42"/>
-        <v>1-1</v>
+        <f t="shared" si="45"/>
+        <v>1-3</v>
       </c>
       <c r="P187" s="1" t="str">
-        <f t="shared" si="42"/>
-        <v>6-6</v>
+        <f t="shared" si="45"/>
+        <v>6-18</v>
       </c>
       <c r="Q187" s="1">
-        <f t="shared" ref="Q187:Q203" si="44">_xlfn.LET(_xlpm.a,($E187+P$3*$G187)*(1+P$2),_xlpm.b,($F187+P$3*$H187)*(1+P$2),_xlpm.a/2+_xlpm.b/2)</f>
-        <v>6</v>
+        <f t="shared" si="43"/>
+        <v>12</v>
       </c>
     </row>
     <row r="188" spans="1:17">
       <c r="A188" s="1" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="E188" s="1">
         <v>1</v>
@@ -10666,37 +10741,37 @@
         <v>0</v>
       </c>
       <c r="H188" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N188" s="1" t="str">
-        <f t="shared" ref="N188:P203" si="45">_xlfn.LET(_xlpm.a,($E188+N$3*$G188)*(1+N$2),_xlpm.b,($F188+N$3*$H188)*(1+N$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
+        <f t="shared" si="45"/>
         <v>1-1</v>
       </c>
       <c r="O188" s="1" t="str">
         <f t="shared" si="45"/>
-        <v>1-1</v>
+        <v>1-3</v>
       </c>
       <c r="P188" s="1" t="str">
         <f t="shared" si="45"/>
-        <v>6-6</v>
+        <v>6-18</v>
       </c>
       <c r="Q188" s="1">
-        <f t="shared" si="44"/>
-        <v>6</v>
+        <f t="shared" si="43"/>
+        <v>12</v>
       </c>
     </row>
     <row r="189" spans="1:17">
       <c r="A189" s="1" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E189" s="1">
         <v>1</v>
@@ -10708,7 +10783,7 @@
         <v>0</v>
       </c>
       <c r="H189" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N189" s="1" t="str">
         <f t="shared" si="45"/>
@@ -10716,29 +10791,29 @@
       </c>
       <c r="O189" s="1" t="str">
         <f t="shared" si="45"/>
-        <v>1-1</v>
+        <v>1-3</v>
       </c>
       <c r="P189" s="1" t="str">
         <f t="shared" si="45"/>
-        <v>6-6</v>
+        <v>6-18</v>
       </c>
       <c r="Q189" s="1">
-        <f t="shared" si="44"/>
-        <v>6</v>
+        <f t="shared" si="43"/>
+        <v>12</v>
       </c>
     </row>
     <row r="190" spans="1:17">
       <c r="A190" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E190" s="1">
         <v>1</v>
@@ -10765,22 +10840,22 @@
         <v>6-6</v>
       </c>
       <c r="Q190" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" ref="Q190" si="46">_xlfn.LET(_xlpm.a,($E190+P$3*$G190)*(1+P$2),_xlpm.b,($F190+P$3*$H190)*(1+P$2),_xlpm.a/2+_xlpm.b/2)</f>
         <v>6</v>
       </c>
     </row>
     <row r="191" spans="1:17">
       <c r="A191" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E191" s="1">
         <v>1</v>
@@ -10807,22 +10882,22 @@
         <v>6-6</v>
       </c>
       <c r="Q191" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" ref="Q191:Q207" si="47">_xlfn.LET(_xlpm.a,($E191+P$3*$G191)*(1+P$2),_xlpm.b,($F191+P$3*$H191)*(1+P$2),_xlpm.a/2+_xlpm.b/2)</f>
         <v>6</v>
       </c>
     </row>
     <row r="192" spans="1:17">
       <c r="A192" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="E192" s="1">
         <v>1</v>
@@ -10837,34 +10912,34 @@
         <v>0</v>
       </c>
       <c r="N192" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" ref="N192:P207" si="48">_xlfn.LET(_xlpm.a,($E192+N$3*$G192)*(1+N$2),_xlpm.b,($F192+N$3*$H192)*(1+N$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
         <v>1-1</v>
       </c>
       <c r="O192" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>1-1</v>
       </c>
       <c r="P192" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>6-6</v>
       </c>
       <c r="Q192" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>6</v>
       </c>
     </row>
     <row r="193" spans="1:17">
       <c r="A193" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="E193" s="1">
         <v>1</v>
@@ -10879,34 +10954,34 @@
         <v>0</v>
       </c>
       <c r="N193" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>1-1</v>
       </c>
       <c r="O193" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>1-1</v>
       </c>
       <c r="P193" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>6-6</v>
       </c>
       <c r="Q193" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>6</v>
       </c>
     </row>
     <row r="194" spans="1:17">
       <c r="A194" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="E194" s="1">
         <v>1</v>
@@ -10921,34 +10996,34 @@
         <v>0</v>
       </c>
       <c r="N194" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>1-1</v>
       </c>
       <c r="O194" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>1-1</v>
       </c>
       <c r="P194" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>6-6</v>
       </c>
       <c r="Q194" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>6</v>
       </c>
     </row>
     <row r="195" spans="1:17">
       <c r="A195" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E195" s="1">
         <v>1</v>
@@ -10963,34 +11038,34 @@
         <v>0</v>
       </c>
       <c r="N195" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>1-1</v>
       </c>
       <c r="O195" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>1-1</v>
       </c>
       <c r="P195" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>6-6</v>
       </c>
       <c r="Q195" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>6</v>
       </c>
     </row>
     <row r="196" spans="1:17">
       <c r="A196" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="E196" s="1">
         <v>1</v>
@@ -11005,34 +11080,34 @@
         <v>0</v>
       </c>
       <c r="N196" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>1-1</v>
       </c>
       <c r="O196" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>1-1</v>
       </c>
       <c r="P196" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>6-6</v>
       </c>
       <c r="Q196" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>6</v>
       </c>
     </row>
     <row r="197" spans="1:17">
       <c r="A197" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="E197" s="1">
         <v>1</v>
@@ -11047,34 +11122,34 @@
         <v>0</v>
       </c>
       <c r="N197" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>1-1</v>
       </c>
       <c r="O197" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>1-1</v>
       </c>
       <c r="P197" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>6-6</v>
       </c>
       <c r="Q197" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>6</v>
       </c>
     </row>
     <row r="198" spans="1:17">
       <c r="A198" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E198" s="1">
         <v>1</v>
@@ -11089,34 +11164,34 @@
         <v>0</v>
       </c>
       <c r="N198" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>1-1</v>
       </c>
       <c r="O198" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>1-1</v>
       </c>
       <c r="P198" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>6-6</v>
       </c>
       <c r="Q198" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>6</v>
       </c>
     </row>
     <row r="199" spans="1:17">
       <c r="A199" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="E199" s="1">
         <v>1</v>
@@ -11131,34 +11206,34 @@
         <v>0</v>
       </c>
       <c r="N199" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>1-1</v>
       </c>
       <c r="O199" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>1-1</v>
       </c>
       <c r="P199" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>6-6</v>
       </c>
       <c r="Q199" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>6</v>
       </c>
     </row>
     <row r="200" spans="1:17">
       <c r="A200" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E200" s="1">
         <v>1</v>
@@ -11173,34 +11248,34 @@
         <v>0</v>
       </c>
       <c r="N200" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>1-1</v>
       </c>
       <c r="O200" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>1-1</v>
       </c>
       <c r="P200" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>6-6</v>
       </c>
       <c r="Q200" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>6</v>
       </c>
     </row>
     <row r="201" spans="1:17">
       <c r="A201" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E201" s="1">
         <v>1</v>
@@ -11215,34 +11290,34 @@
         <v>0</v>
       </c>
       <c r="N201" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>1-1</v>
       </c>
       <c r="O201" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>1-1</v>
       </c>
       <c r="P201" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>6-6</v>
       </c>
       <c r="Q201" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>6</v>
       </c>
     </row>
     <row r="202" spans="1:17">
       <c r="A202" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E202" s="1">
         <v>1</v>
@@ -11257,61 +11332,229 @@
         <v>0</v>
       </c>
       <c r="N202" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>1-1</v>
       </c>
       <c r="O202" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>1-1</v>
       </c>
       <c r="P202" s="1" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>6-6</v>
       </c>
       <c r="Q202" s="1">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>6</v>
       </c>
     </row>
     <row r="203" spans="1:17">
       <c r="A203" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="E203" s="1">
+        <v>1</v>
+      </c>
+      <c r="F203" s="1">
+        <v>1</v>
+      </c>
+      <c r="G203" s="1">
+        <v>0</v>
+      </c>
+      <c r="H203" s="1">
+        <v>0</v>
+      </c>
+      <c r="N203" s="1" t="str">
+        <f t="shared" si="48"/>
+        <v>1-1</v>
+      </c>
+      <c r="O203" s="1" t="str">
+        <f t="shared" si="48"/>
+        <v>1-1</v>
+      </c>
+      <c r="P203" s="1" t="str">
+        <f t="shared" si="48"/>
+        <v>6-6</v>
+      </c>
+      <c r="Q203" s="1">
+        <f t="shared" si="47"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="204" spans="1:17">
+      <c r="A204" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E204" s="1">
+        <v>1</v>
+      </c>
+      <c r="F204" s="1">
+        <v>1</v>
+      </c>
+      <c r="G204" s="1">
+        <v>0</v>
+      </c>
+      <c r="H204" s="1">
+        <v>0</v>
+      </c>
+      <c r="N204" s="1" t="str">
+        <f t="shared" si="48"/>
+        <v>1-1</v>
+      </c>
+      <c r="O204" s="1" t="str">
+        <f t="shared" si="48"/>
+        <v>1-1</v>
+      </c>
+      <c r="P204" s="1" t="str">
+        <f t="shared" si="48"/>
+        <v>6-6</v>
+      </c>
+      <c r="Q204" s="1">
+        <f t="shared" si="47"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="205" spans="1:17">
+      <c r="A205" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E205" s="1">
+        <v>1</v>
+      </c>
+      <c r="F205" s="1">
+        <v>1</v>
+      </c>
+      <c r="G205" s="1">
+        <v>0</v>
+      </c>
+      <c r="H205" s="1">
+        <v>0</v>
+      </c>
+      <c r="N205" s="1" t="str">
+        <f t="shared" si="48"/>
+        <v>1-1</v>
+      </c>
+      <c r="O205" s="1" t="str">
+        <f t="shared" si="48"/>
+        <v>1-1</v>
+      </c>
+      <c r="P205" s="1" t="str">
+        <f t="shared" si="48"/>
+        <v>6-6</v>
+      </c>
+      <c r="Q205" s="1">
+        <f t="shared" si="47"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="206" spans="1:17">
+      <c r="A206" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E206" s="1">
+        <v>1</v>
+      </c>
+      <c r="F206" s="1">
+        <v>1</v>
+      </c>
+      <c r="G206" s="1">
+        <v>0</v>
+      </c>
+      <c r="H206" s="1">
+        <v>0</v>
+      </c>
+      <c r="N206" s="1" t="str">
+        <f t="shared" si="48"/>
+        <v>1-1</v>
+      </c>
+      <c r="O206" s="1" t="str">
+        <f t="shared" si="48"/>
+        <v>1-1</v>
+      </c>
+      <c r="P206" s="1" t="str">
+        <f t="shared" si="48"/>
+        <v>6-6</v>
+      </c>
+      <c r="Q206" s="1">
+        <f t="shared" si="47"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="207" spans="1:17">
+      <c r="A207" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B203" s="1" t="s">
+      <c r="B207" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C203" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D203" s="1" t="s">
+      <c r="C207" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="E203" s="1">
-        <v>1</v>
-      </c>
-      <c r="F203" s="1">
-        <v>1</v>
-      </c>
-      <c r="G203" s="1">
-        <v>0</v>
-      </c>
-      <c r="H203" s="1">
-        <v>0</v>
-      </c>
-      <c r="N203" s="1" t="str">
-        <f t="shared" si="45"/>
-        <v>1-1</v>
-      </c>
-      <c r="O203" s="1" t="str">
-        <f t="shared" si="45"/>
-        <v>1-1</v>
-      </c>
-      <c r="P203" s="1" t="str">
-        <f t="shared" si="45"/>
+      <c r="E207" s="1">
+        <v>1</v>
+      </c>
+      <c r="F207" s="1">
+        <v>1</v>
+      </c>
+      <c r="G207" s="1">
+        <v>0</v>
+      </c>
+      <c r="H207" s="1">
+        <v>0</v>
+      </c>
+      <c r="N207" s="1" t="str">
+        <f t="shared" si="48"/>
+        <v>1-1</v>
+      </c>
+      <c r="O207" s="1" t="str">
+        <f t="shared" si="48"/>
+        <v>1-1</v>
+      </c>
+      <c r="P207" s="1" t="str">
+        <f t="shared" si="48"/>
         <v>6-6</v>
       </c>
-      <c r="Q203" s="1">
-        <f t="shared" si="44"/>
+      <c r="Q207" s="1">
+        <f t="shared" si="47"/>
         <v>6</v>
       </c>
     </row>
@@ -11335,16 +11578,16 @@
   <conditionalFormatting sqref="B136">
     <cfRule type="duplicateValues" dxfId="12" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B143:B144">
+  <conditionalFormatting sqref="B147:B148">
     <cfRule type="duplicateValues" dxfId="11" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B145:B149 B35">
+  <conditionalFormatting sqref="B149:B153 B35">
     <cfRule type="duplicateValues" dxfId="10" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B150:B185">
+  <conditionalFormatting sqref="B154:B189">
     <cfRule type="duplicateValues" dxfId="9" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B186:B203">
+  <conditionalFormatting sqref="B190:B207">
     <cfRule type="duplicateValues" dxfId="8" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D28:D32">
@@ -11359,16 +11602,16 @@
   <conditionalFormatting sqref="D96:D131">
     <cfRule type="duplicateValues" dxfId="4" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D143:D144">
+  <conditionalFormatting sqref="D147:D148">
     <cfRule type="duplicateValues" dxfId="3" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D145:D149 D35">
+  <conditionalFormatting sqref="D149:D153 D35">
     <cfRule type="duplicateValues" dxfId="2" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D150:D185">
+  <conditionalFormatting sqref="D154:D189">
     <cfRule type="duplicateValues" dxfId="1" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D186:D203">
+  <conditionalFormatting sqref="D190:D207">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/configs/Affix.xlsx
+++ b/configs/Affix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30393F42-C89C-4408-850D-0A29CE4954CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2644DE-5E75-4DAE-869F-26ECF272E5DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="584">
   <si>
     <t>id</t>
   </si>
@@ -1783,9 +1783,6 @@
   </si>
   <si>
     <t>weapon</t>
-  </si>
-  <si>
-    <t>armor,belt,boot,glove,helm,necklace,pant,pauldron,ring,weapon,bracelet</t>
   </si>
   <si>
     <t>prockill</t>
@@ -5841,9 +5838,6 @@
       <c r="H78" s="1">
         <v>0</v>
       </c>
-      <c r="M78" s="1" t="s">
-        <v>571</v>
-      </c>
       <c r="N78" s="1" t="str">
         <f t="shared" si="20"/>
         <v>1-1</v>
@@ -8656,16 +8650,16 @@
     </row>
     <row r="140" spans="1:17">
       <c r="A140" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E140" s="1">
         <v>1</v>
@@ -8680,7 +8674,7 @@
         <v>2</v>
       </c>
       <c r="K140" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="L140" s="1" t="s">
         <v>564</v>
@@ -8707,16 +8701,16 @@
     </row>
     <row r="141" spans="1:17">
       <c r="A141" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E141" s="1">
         <v>1</v>
@@ -8731,7 +8725,7 @@
         <v>2</v>
       </c>
       <c r="K141" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="L141" s="1" t="s">
         <v>564</v>
@@ -8758,16 +8752,16 @@
     </row>
     <row r="142" spans="1:17">
       <c r="A142" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E142" s="1">
         <v>1</v>
@@ -8782,7 +8776,7 @@
         <v>2</v>
       </c>
       <c r="K142" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="L142" s="1" t="s">
         <v>564</v>
@@ -8809,16 +8803,16 @@
     </row>
     <row r="143" spans="1:17">
       <c r="A143" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>581</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E143" s="1">
         <v>1</v>
@@ -8833,7 +8827,7 @@
         <v>2</v>
       </c>
       <c r="K143" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="L143" s="1" t="s">
         <v>564</v>

--- a/configs/Affix.xlsx
+++ b/configs/Affix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2644DE-5E75-4DAE-869F-26ECF272E5DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8B7BE6-AF60-4527-B537-20D6F679B0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="587">
   <si>
     <t>id</t>
   </si>
@@ -1734,27 +1734,12 @@
     <t>necklace,armor</t>
   </si>
   <si>
-    <t>necklace,charm</t>
-  </si>
-  <si>
-    <t>necklace,armor,charm</t>
-  </si>
-  <si>
-    <t>necklace,charm,ring</t>
-  </si>
-  <si>
-    <t>necklace,weapon,charm,ring</t>
-  </si>
-  <si>
     <t>necklace,ring</t>
   </si>
   <si>
     <t>necklace,armor,ring</t>
   </si>
   <si>
-    <t>necklace,armor,charm,ring</t>
-  </si>
-  <si>
     <t>skillChance</t>
   </si>
   <si>
@@ -1770,21 +1755,6 @@
     <t>SkillId</t>
   </si>
   <si>
-    <t>belt,necklace,ring</t>
-  </si>
-  <si>
-    <t>boot,glove,pauldron,weapon,bracelet</t>
-  </si>
-  <si>
-    <t>helm,pant,weapon</t>
-  </si>
-  <si>
-    <t>armor,weapon</t>
-  </si>
-  <si>
-    <t>weapon</t>
-  </si>
-  <si>
     <t>prockill</t>
   </si>
   <si>
@@ -1822,6 +1792,45 @@
   </si>
   <si>
     <t>pskl</t>
+  </si>
+  <si>
+    <t>necklace,ring,charm1,charm2,charm3,sword,sword2h,dao,dao2h,dagger,axe,axe2h,mace,mace2h,polearm</t>
+  </si>
+  <si>
+    <t>necklace,ring,charm1,charm2,charm3,staff,instrument</t>
+  </si>
+  <si>
+    <t>sword,sword2h,dao,dao2h,dagger,axe,axe2h,mace,mace2h,polearm,staff,instrument</t>
+  </si>
+  <si>
+    <t>sword,sword2h,dao,dao2h,dagger,axe,axe2h,mace,mace2h,polearm,staff,instrument,necklace,ring,charm1,charm2,charm3</t>
+  </si>
+  <si>
+    <t>necklace,ring,charm1,charm2,charm3,armor</t>
+  </si>
+  <si>
+    <t>necklace,charm3</t>
+  </si>
+  <si>
+    <t>necklace,armor,charm1,charm2,charm3</t>
+  </si>
+  <si>
+    <t>armor,belt,boot,glove,helm,necklace,pant,pauldron,ring,sword,sword2h,dao,dao2h,dagger,axe,axe2h,mace,mace2h,staff,polearm,instrument,bracelet</t>
+  </si>
+  <si>
+    <t>armor,boot,glove,helm,pant,pauldron,sword,sword2h,dao,dao2h,dagger,axe,axe2h,mace,mace2h,staff,polearm,instrument,bracelet</t>
+  </si>
+  <si>
+    <t>armor,helm,pant,sword,sword2h,dao,dao2h,axe,axe2h,mace,mace2h,staff,polearm,instrument</t>
+  </si>
+  <si>
+    <t>armor,sword,sword2h,dao,dao2h,axe,axe2h,mace,mace2h,staff,polearm</t>
+  </si>
+  <si>
+    <t>sword2h,dao2h,axe2h,mace2h,staff</t>
+  </si>
+  <si>
+    <t>necklace,armor,charm1,charm2,charm3,ring</t>
   </si>
 </sst>
 </file>
@@ -2391,7 +2400,7 @@
         <v>127</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>112</v>
@@ -2429,10 +2438,10 @@
         <v>141</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>113</v>
@@ -2499,7 +2508,7 @@
         <v>128</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>114</v>
@@ -2531,7 +2540,7 @@
         <v>0.4</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>556</v>
+        <v>574</v>
       </c>
       <c r="N5" s="1" t="str">
         <f t="shared" ref="N5:N13" si="0">_xlfn.LET(_xlpm.a,($E5+N$3*$G5)*(1+N$2),_xlpm.b,($F5+N$3*$H5)*(1+N$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
@@ -2576,7 +2585,7 @@
         <v>0.4</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
       <c r="N6" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2624,7 +2633,7 @@
         <v>0.15</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>557</v>
+        <v>577</v>
       </c>
       <c r="N7" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2675,7 +2684,7 @@
         <v>1</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>557</v>
+        <v>577</v>
       </c>
       <c r="N8" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2723,7 +2732,7 @@
         <v>0.15</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>557</v>
+        <v>577</v>
       </c>
       <c r="N9" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2771,7 +2780,7 @@
         <v>0.15</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>557</v>
+        <v>577</v>
       </c>
       <c r="N10" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2819,7 +2828,7 @@
         <v>0.15</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>557</v>
+        <v>577</v>
       </c>
       <c r="N11" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2867,7 +2876,7 @@
         <v>0.15</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>557</v>
+        <v>577</v>
       </c>
       <c r="N12" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2912,7 +2921,7 @@
         <v>75</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N13" s="1" t="str">
         <f t="shared" si="0"/>
@@ -2957,7 +2966,7 @@
         <v>75</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N14" s="1" t="str">
         <f t="shared" ref="N14:P35" si="4">_xlfn.LET(_xlpm.a,($E14+N$3*$G14)*(1+N$2),_xlpm.b,($F14+N$3*$H14)*(1+N$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
@@ -3002,7 +3011,7 @@
         <v>75</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N15" s="1" t="str">
         <f t="shared" si="4"/>
@@ -3047,7 +3056,7 @@
         <v>75</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N16" s="1" t="str">
         <f t="shared" si="4"/>
@@ -3092,7 +3101,7 @@
         <v>75</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N17" s="1" t="str">
         <f t="shared" si="4"/>
@@ -3137,7 +3146,7 @@
         <v>75</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N18" s="1" t="str">
         <f t="shared" si="4"/>
@@ -3182,7 +3191,7 @@
         <v>75</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N19" s="1" t="str">
         <f t="shared" si="4"/>
@@ -3227,7 +3236,7 @@
         <v>75</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N20" s="1" t="str">
         <f t="shared" si="4"/>
@@ -3272,7 +3281,7 @@
         <v>75</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N21" s="1" t="str">
         <f t="shared" si="4"/>
@@ -3317,7 +3326,7 @@
         <v>75</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N22" s="1" t="str">
         <f t="shared" si="4"/>
@@ -3847,7 +3856,7 @@
         <v>20</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="N33" s="1" t="str">
         <f t="shared" si="4"/>
@@ -3892,7 +3901,7 @@
         <v>20</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="N34" s="1" t="str">
         <f t="shared" si="4"/>
@@ -3937,7 +3946,7 @@
         <v>22.5</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="N35" s="1" t="str">
         <f t="shared" si="4"/>
@@ -3982,7 +3991,7 @@
         <v>2.4</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="N36" s="1" t="str">
         <f>_xlfn.LET(_xlpm.a,($E36+N$3*$G36)*(1+N$2),_xlpm.b,($F36+N$3*$H36)*(1+N$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
@@ -4027,7 +4036,7 @@
         <v>5</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="N37" s="1" t="str">
         <f>_xlfn.LET(_xlpm.a,($E37+N$3*$G37)*(1+N$2),_xlpm.b,($F37+N$3*$H37)*(1+N$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
@@ -4072,7 +4081,7 @@
         <v>5</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="N38" s="1" t="str">
         <f t="shared" ref="N38:P75" si="13">_xlfn.LET(_xlpm.a,($E38+N$3*$G38)*(1+N$2),_xlpm.b,($F38+N$3*$H38)*(1+N$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
@@ -4117,7 +4126,7 @@
         <v>5</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="N39" s="1" t="str">
         <f t="shared" si="13"/>
@@ -4162,7 +4171,7 @@
         <v>5</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="N40" s="1" t="str">
         <f t="shared" si="13"/>
@@ -4417,7 +4426,7 @@
         <v>2</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="N46" s="1" t="str">
         <f t="shared" si="13"/>
@@ -4462,7 +4471,7 @@
         <v>2</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="N47" s="1" t="str">
         <f t="shared" si="13"/>
@@ -4507,7 +4516,7 @@
         <v>2</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="N48" s="1" t="str">
         <f t="shared" si="13"/>
@@ -4552,7 +4561,7 @@
         <v>2</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="N49" s="1" t="str">
         <f t="shared" si="13"/>
@@ -4597,7 +4606,7 @@
         <v>2</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="N50" s="1" t="str">
         <f t="shared" si="13"/>
@@ -4642,7 +4651,7 @@
         <v>2</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="N51" s="1" t="str">
         <f t="shared" si="13"/>
@@ -4687,7 +4696,7 @@
         <v>4</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="N52" s="1" t="str">
         <f t="shared" si="13"/>
@@ -4816,7 +4825,7 @@
         <v>0.5</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="N55" s="1" t="str">
         <f t="shared" si="13"/>
@@ -4861,7 +4870,7 @@
         <v>0.5</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="N56" s="1" t="str">
         <f t="shared" si="13"/>
@@ -5035,7 +5044,7 @@
         <v>0.5</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="N60" s="1" t="str">
         <f t="shared" si="13"/>
@@ -5080,7 +5089,7 @@
         <v>0.5</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="N61" s="1" t="str">
         <f t="shared" si="13"/>
@@ -5254,7 +5263,7 @@
         <v>0.5</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="N65" s="1" t="str">
         <f t="shared" si="13"/>
@@ -5299,7 +5308,7 @@
         <v>0.5</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="N66" s="1" t="str">
         <f t="shared" si="13"/>
@@ -5524,7 +5533,7 @@
         <v>7.5</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>555</v>
+        <v>580</v>
       </c>
       <c r="N71" s="1" t="str">
         <f t="shared" si="13"/>
@@ -5569,7 +5578,7 @@
         <v>20</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>555</v>
+        <v>580</v>
       </c>
       <c r="N72" s="1" t="str">
         <f t="shared" si="13"/>
@@ -5614,7 +5623,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>566</v>
+        <v>581</v>
       </c>
       <c r="N73" s="1" t="str">
         <f t="shared" si="13"/>
@@ -5659,7 +5668,7 @@
         <v>0.25</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>567</v>
+        <v>582</v>
       </c>
       <c r="N74" s="1" t="str">
         <f t="shared" si="13"/>
@@ -5704,7 +5713,7 @@
         <v>0.5</v>
       </c>
       <c r="M75" s="1" t="s">
-        <v>568</v>
+        <v>583</v>
       </c>
       <c r="N75" s="1" t="str">
         <f t="shared" si="13"/>
@@ -5749,7 +5758,7 @@
         <v>0.75</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>569</v>
+        <v>584</v>
       </c>
       <c r="N76" s="1" t="str">
         <f t="shared" ref="N76:P91" si="20">_xlfn.LET(_xlpm.a,($E76+N$3*$G76)*(1+N$2),_xlpm.b,($F76+N$3*$H76)*(1+N$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
@@ -5794,7 +5803,7 @@
         <v>1</v>
       </c>
       <c r="M77" s="1" t="s">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="N77" s="1" t="str">
         <f t="shared" si="20"/>
@@ -5881,7 +5890,7 @@
         <v>5</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="N79" s="1" t="str">
         <f t="shared" si="20"/>
@@ -5926,7 +5935,7 @@
         <v>5</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="N80" s="1" t="str">
         <f t="shared" si="20"/>
@@ -5971,7 +5980,7 @@
         <v>6</v>
       </c>
       <c r="M81" s="1" t="s">
-        <v>560</v>
+        <v>586</v>
       </c>
       <c r="N81" s="1" t="str">
         <f t="shared" si="20"/>
@@ -6016,7 +6025,7 @@
         <v>10</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>560</v>
+        <v>586</v>
       </c>
       <c r="N82" s="1" t="str">
         <f t="shared" si="20"/>
@@ -6061,7 +6070,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N83" s="1" t="str">
         <f t="shared" si="20"/>
@@ -6106,7 +6115,7 @@
         <v>0.4</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="N84" s="1" t="str">
         <f t="shared" si="20"/>
@@ -6151,7 +6160,7 @@
         <v>0.4</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="N85" s="1" t="str">
         <f t="shared" si="20"/>
@@ -6196,7 +6205,7 @@
         <v>1.5</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N86" s="1" t="str">
         <f t="shared" si="20"/>
@@ -6241,7 +6250,7 @@
         <v>50</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N87" s="1" t="str">
         <f t="shared" si="20"/>
@@ -6286,7 +6295,7 @@
         <v>1.5</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N88" s="1" t="str">
         <f t="shared" si="20"/>
@@ -6331,7 +6340,7 @@
         <v>50</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N89" s="1" t="str">
         <f t="shared" si="20"/>
@@ -6376,7 +6385,7 @@
         <v>24</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>560</v>
+        <v>586</v>
       </c>
       <c r="N90" s="1" t="str">
         <f t="shared" si="20"/>
@@ -6421,7 +6430,7 @@
         <v>24</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>560</v>
+        <v>586</v>
       </c>
       <c r="N91" s="1" t="str">
         <f t="shared" si="20"/>
@@ -6466,7 +6475,7 @@
         <v>24</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>560</v>
+        <v>586</v>
       </c>
       <c r="N92" s="1" t="str">
         <f t="shared" ref="N92:P107" si="26">_xlfn.LET(_xlpm.a,($E92+N$3*$G92)*(1+N$2),_xlpm.b,($F92+N$3*$H92)*(1+N$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
@@ -6511,7 +6520,7 @@
         <v>24</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>560</v>
+        <v>586</v>
       </c>
       <c r="N93" s="1" t="str">
         <f t="shared" si="26"/>
@@ -6556,7 +6565,7 @@
         <v>1</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N94" s="1" t="str">
         <f t="shared" si="26"/>
@@ -6601,7 +6610,7 @@
         <v>1</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N95" s="1" t="str">
         <f t="shared" si="26"/>
@@ -6646,7 +6655,7 @@
         <v>0.5</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N96" s="1" t="str">
         <f t="shared" si="26"/>
@@ -6691,7 +6700,7 @@
         <v>0.5</v>
       </c>
       <c r="M97" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N97" s="1" t="str">
         <f t="shared" si="26"/>
@@ -6736,7 +6745,7 @@
         <v>0.5</v>
       </c>
       <c r="M98" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N98" s="1" t="str">
         <f t="shared" si="26"/>
@@ -6781,7 +6790,7 @@
         <v>0.5</v>
       </c>
       <c r="M99" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N99" s="1" t="str">
         <f t="shared" si="26"/>
@@ -6826,7 +6835,7 @@
         <v>0.5</v>
       </c>
       <c r="M100" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N100" s="1" t="str">
         <f t="shared" si="26"/>
@@ -6871,7 +6880,7 @@
         <v>0.5</v>
       </c>
       <c r="M101" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N101" s="1" t="str">
         <f t="shared" si="26"/>
@@ -6916,7 +6925,7 @@
         <v>0.5</v>
       </c>
       <c r="M102" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N102" s="1" t="str">
         <f t="shared" si="26"/>
@@ -6961,7 +6970,7 @@
         <v>0.5</v>
       </c>
       <c r="M103" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N103" s="1" t="str">
         <f t="shared" si="26"/>
@@ -7006,7 +7015,7 @@
         <v>0.5</v>
       </c>
       <c r="M104" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N104" s="1" t="str">
         <f t="shared" si="26"/>
@@ -7051,7 +7060,7 @@
         <v>0.5</v>
       </c>
       <c r="M105" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N105" s="1" t="str">
         <f t="shared" si="26"/>
@@ -7096,7 +7105,7 @@
         <v>0.5</v>
       </c>
       <c r="M106" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N106" s="1" t="str">
         <f t="shared" si="26"/>
@@ -7141,7 +7150,7 @@
         <v>0.5</v>
       </c>
       <c r="M107" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N107" s="1" t="str">
         <f t="shared" si="26"/>
@@ -7186,7 +7195,7 @@
         <v>0.5</v>
       </c>
       <c r="M108" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N108" s="1" t="str">
         <f t="shared" ref="N108:P133" si="31">_xlfn.LET(_xlpm.a,($E108+N$3*$G108)*(1+N$2),_xlpm.b,($F108+N$3*$H108)*(1+N$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
@@ -7231,7 +7240,7 @@
         <v>0.5</v>
       </c>
       <c r="M109" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N109" s="1" t="str">
         <f t="shared" si="31"/>
@@ -7276,7 +7285,7 @@
         <v>0.5</v>
       </c>
       <c r="M110" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N110" s="1" t="str">
         <f t="shared" si="31"/>
@@ -7321,7 +7330,7 @@
         <v>0.5</v>
       </c>
       <c r="M111" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N111" s="1" t="str">
         <f t="shared" si="31"/>
@@ -7366,7 +7375,7 @@
         <v>0.5</v>
       </c>
       <c r="M112" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N112" s="1" t="str">
         <f t="shared" si="31"/>
@@ -7411,7 +7420,7 @@
         <v>0.5</v>
       </c>
       <c r="M113" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N113" s="1" t="str">
         <f t="shared" si="31"/>
@@ -7456,7 +7465,7 @@
         <v>0.5</v>
       </c>
       <c r="M114" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N114" s="1" t="str">
         <f t="shared" si="31"/>
@@ -7501,7 +7510,7 @@
         <v>0.5</v>
       </c>
       <c r="M115" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N115" s="1" t="str">
         <f t="shared" si="31"/>
@@ -7546,7 +7555,7 @@
         <v>0.5</v>
       </c>
       <c r="M116" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N116" s="1" t="str">
         <f t="shared" si="31"/>
@@ -7591,7 +7600,7 @@
         <v>0.5</v>
       </c>
       <c r="M117" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N117" s="1" t="str">
         <f t="shared" si="31"/>
@@ -7636,7 +7645,7 @@
         <v>0.5</v>
       </c>
       <c r="M118" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N118" s="1" t="str">
         <f t="shared" si="31"/>
@@ -7681,7 +7690,7 @@
         <v>0.5</v>
       </c>
       <c r="M119" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N119" s="1" t="str">
         <f t="shared" si="31"/>
@@ -7726,7 +7735,7 @@
         <v>0.5</v>
       </c>
       <c r="M120" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N120" s="1" t="str">
         <f t="shared" si="31"/>
@@ -7771,7 +7780,7 @@
         <v>0.5</v>
       </c>
       <c r="M121" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N121" s="1" t="str">
         <f t="shared" si="31"/>
@@ -7816,7 +7825,7 @@
         <v>0.5</v>
       </c>
       <c r="M122" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N122" s="1" t="str">
         <f t="shared" si="31"/>
@@ -7861,7 +7870,7 @@
         <v>0.5</v>
       </c>
       <c r="M123" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N123" s="1" t="str">
         <f t="shared" si="31"/>
@@ -7906,7 +7915,7 @@
         <v>0.5</v>
       </c>
       <c r="M124" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N124" s="1" t="str">
         <f t="shared" si="31"/>
@@ -7951,7 +7960,7 @@
         <v>0.5</v>
       </c>
       <c r="M125" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N125" s="1" t="str">
         <f t="shared" si="31"/>
@@ -7996,7 +8005,7 @@
         <v>0.5</v>
       </c>
       <c r="M126" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N126" s="1" t="str">
         <f t="shared" si="31"/>
@@ -8041,7 +8050,7 @@
         <v>0.5</v>
       </c>
       <c r="M127" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N127" s="1" t="str">
         <f t="shared" si="31"/>
@@ -8086,7 +8095,7 @@
         <v>0.5</v>
       </c>
       <c r="M128" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N128" s="1" t="str">
         <f t="shared" si="31"/>
@@ -8131,7 +8140,7 @@
         <v>0.5</v>
       </c>
       <c r="M129" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N129" s="1" t="str">
         <f t="shared" si="31"/>
@@ -8176,7 +8185,7 @@
         <v>0.5</v>
       </c>
       <c r="M130" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N130" s="1" t="str">
         <f t="shared" si="31"/>
@@ -8221,7 +8230,7 @@
         <v>0.5</v>
       </c>
       <c r="M131" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N131" s="1" t="str">
         <f t="shared" si="31"/>
@@ -8269,10 +8278,10 @@
         <v>119</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="M132" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N132" s="1" t="str">
         <f t="shared" si="31"/>
@@ -8320,10 +8329,10 @@
         <v>120</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="M133" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N133" s="1" t="str">
         <f t="shared" si="31"/>
@@ -8371,10 +8380,10 @@
         <v>121</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="M134" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N134" s="1" t="str">
         <f t="shared" ref="N134:P153" si="34">_xlfn.LET(_xlpm.a,($E134+N$3*$G134)*(1+N$2),_xlpm.b,($F134+N$3*$H134)*(1+N$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
@@ -8422,10 +8431,10 @@
         <v>122</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N135" s="1" t="str">
         <f t="shared" si="34"/>
@@ -8473,10 +8482,10 @@
         <v>123</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="M136" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="N136" s="1" t="str">
         <f t="shared" si="34"/>
@@ -8524,10 +8533,10 @@
         <v>124</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="M137" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="N137" s="1" t="str">
         <f t="shared" si="34"/>
@@ -8575,10 +8584,10 @@
         <v>125</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="M138" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="N138" s="1" t="str">
         <f t="shared" si="34"/>
@@ -8626,10 +8635,10 @@
         <v>126</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="M139" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="N139" s="1" t="str">
         <f t="shared" si="34"/>
@@ -8650,16 +8659,16 @@
     </row>
     <row r="140" spans="1:17">
       <c r="A140" s="1" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="E140" s="1">
         <v>1</v>
@@ -8674,13 +8683,13 @@
         <v>2</v>
       </c>
       <c r="K140" s="1" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="M140" s="1" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="N140" s="1" t="str">
         <f t="shared" si="34"/>
@@ -8701,16 +8710,16 @@
     </row>
     <row r="141" spans="1:17">
       <c r="A141" s="1" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="E141" s="1">
         <v>1</v>
@@ -8725,13 +8734,13 @@
         <v>2</v>
       </c>
       <c r="K141" s="1" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="M141" s="1" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="N141" s="1" t="str">
         <f t="shared" si="34"/>
@@ -8752,16 +8761,16 @@
     </row>
     <row r="142" spans="1:17">
       <c r="A142" s="1" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="E142" s="1">
         <v>1</v>
@@ -8776,13 +8785,13 @@
         <v>2</v>
       </c>
       <c r="K142" s="1" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="M142" s="1" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="N142" s="1" t="str">
         <f t="shared" si="34"/>
@@ -8803,16 +8812,16 @@
     </row>
     <row r="143" spans="1:17">
       <c r="A143" s="1" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="E143" s="1">
         <v>1</v>
@@ -8827,13 +8836,13 @@
         <v>2</v>
       </c>
       <c r="K143" s="1" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="M143" s="1" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="N143" s="1" t="str">
         <f t="shared" si="34"/>
@@ -8878,7 +8887,7 @@
         <v>1.25</v>
       </c>
       <c r="M144" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N144" s="1" t="str">
         <f t="shared" si="34"/>
@@ -8923,7 +8932,7 @@
         <v>1.25</v>
       </c>
       <c r="M145" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N145" s="1" t="str">
         <f t="shared" si="34"/>
@@ -8968,7 +8977,7 @@
         <v>0.25</v>
       </c>
       <c r="M146" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="N146" s="1" t="str">
         <f t="shared" si="34"/>

--- a/configs/Affix.xlsx
+++ b/configs/Affix.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DC5CF8-E5F6-4E5B-94D8-12EB64E46466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99A0C9F-5D2D-48A9-A948-0ACD8A6E2289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$Q$210</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -11693,6 +11696,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:Q210" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="17" priority="18"/>

--- a/configs/Affix.xlsx
+++ b/configs/Affix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E46AC8-53B2-4B10-B33F-D1CBF599CBBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B88FDC-2123-4351-883F-E99792C1F9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2197" uniqueCount="947">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2207" uniqueCount="947">
   <si>
     <t>id</t>
   </si>
@@ -2340,9 +2340,6 @@
     <t>分组</t>
   </si>
   <si>
-    <t>boolean</t>
-  </si>
-  <si>
     <t>groupExclusive</t>
   </si>
   <si>
@@ -2911,6 +2908,9 @@
   </si>
   <si>
     <t>belt,necklace,ring,sword,woodsword,sword2h,ugs,dao,katana,dao2h,axe,axe2h,mace,mace2h,dagger,staff,magestaff,polearm,instrument</t>
+  </si>
+  <si>
+    <t>socket</t>
   </si>
 </sst>
 </file>
@@ -3351,7 +3351,7 @@
         <v>754</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>594</v>
@@ -3404,10 +3404,10 @@
         <v>110</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>756</v>
+        <v>806</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>133</v>
@@ -3489,7 +3489,7 @@
         <v>755</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>595</v>
@@ -3527,7 +3527,7 @@
         <v>0.4</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="R5" s="1">
         <v>100</v>
@@ -3575,7 +3575,7 @@
         <v>0.4</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="R6" s="1">
         <v>100</v>
@@ -3626,7 +3626,7 @@
         <v>0.15</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="R7" s="1">
         <v>100</v>
@@ -3685,7 +3685,7 @@
         <v>0.15</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="R8" s="1">
         <v>100</v>
@@ -3736,7 +3736,7 @@
         <v>0.15</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="R9" s="1">
         <v>100</v>
@@ -3787,7 +3787,7 @@
         <v>0.15</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="R10" s="1">
         <v>100</v>
@@ -3838,7 +3838,7 @@
         <v>0.15</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="R11" s="1">
         <v>100</v>
@@ -4111,7 +4111,7 @@
         <v>21</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="R17" s="1">
         <v>100</v>
@@ -4159,7 +4159,7 @@
         <v>21</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="R18" s="1">
         <v>100</v>
@@ -4207,7 +4207,7 @@
         <v>21</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="R19" s="1">
         <v>100</v>
@@ -4255,7 +4255,7 @@
         <v>21</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="R20" s="1">
         <v>100</v>
@@ -4303,7 +4303,7 @@
         <v>21</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="R21" s="1">
         <v>100</v>
@@ -4351,7 +4351,7 @@
         <v>21</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="R22" s="1">
         <v>100</v>
@@ -4399,7 +4399,7 @@
         <v>21</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="R23" s="1">
         <v>100</v>
@@ -4447,7 +4447,7 @@
         <v>21</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="R24" s="1">
         <v>100</v>
@@ -4495,7 +4495,7 @@
         <v>21</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="R25" s="1">
         <v>100</v>
@@ -4543,7 +4543,7 @@
         <v>21</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="R26" s="1">
         <v>100</v>
@@ -4591,7 +4591,7 @@
         <v>75</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="R27" s="1">
         <v>100</v>
@@ -4639,7 +4639,7 @@
         <v>75</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="R28" s="1">
         <v>100</v>
@@ -4687,7 +4687,7 @@
         <v>75</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="R29" s="1">
         <v>100</v>
@@ -4735,7 +4735,7 @@
         <v>75</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="R30" s="1">
         <v>100</v>
@@ -4783,7 +4783,7 @@
         <v>75</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="R31" s="1">
         <v>100</v>
@@ -4992,7 +4992,7 @@
         <v>75</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="R37" s="1">
         <v>120</v>
@@ -5040,7 +5040,7 @@
         <v>75</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="R38" s="1">
         <v>120</v>
@@ -5088,7 +5088,7 @@
         <v>75</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="R39" s="1">
         <v>120</v>
@@ -5136,7 +5136,7 @@
         <v>75</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="R40" s="1">
         <v>120</v>
@@ -5184,7 +5184,7 @@
         <v>75</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="R41" s="1">
         <v>120</v>
@@ -5208,16 +5208,16 @@
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="E42" s="1">
         <v>10</v>
@@ -5232,7 +5232,7 @@
         <v>75</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="R42" s="1">
         <v>120</v>
@@ -5240,16 +5240,16 @@
     </row>
     <row r="43" spans="1:22">
       <c r="A43" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E43" s="1">
         <v>10</v>
@@ -5264,7 +5264,7 @@
         <v>75</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="R43" s="1">
         <v>120</v>
@@ -5272,16 +5272,16 @@
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E44" s="1">
         <v>10</v>
@@ -5296,7 +5296,7 @@
         <v>75</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="R44" s="1">
         <v>120</v>
@@ -5331,7 +5331,7 @@
         <v>0.15</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="R45" s="1">
         <v>100</v>
@@ -5382,7 +5382,7 @@
         <v>0.15</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="R46" s="1">
         <v>100</v>
@@ -5433,7 +5433,7 @@
         <v>0.15</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="R47" s="1">
         <v>100</v>
@@ -5484,7 +5484,7 @@
         <v>0.15</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="R48" s="1">
         <v>100</v>
@@ -5535,7 +5535,7 @@
         <v>0.15</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="R49" s="1">
         <v>100</v>
@@ -5812,7 +5812,7 @@
         <v>3.15</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="R55" s="1">
         <v>100</v>
@@ -5864,7 +5864,7 @@
         <v>2.4</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="R56" s="1">
         <v>100</v>
@@ -5916,7 +5916,7 @@
         <v>3.75</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="R57" s="1">
         <v>100</v>
@@ -5968,7 +5968,7 @@
         <v>1.75</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="R58" s="1">
         <v>100</v>
@@ -6020,7 +6020,7 @@
         <v>4.2</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="R59" s="1">
         <v>100</v>
@@ -6068,7 +6068,7 @@
         <v>20</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="R60" s="1">
         <v>100</v>
@@ -6116,7 +6116,7 @@
         <v>20</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="R61" s="1">
         <v>100</v>
@@ -6164,7 +6164,7 @@
         <v>22.5</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="R62" s="1">
         <v>100</v>
@@ -6212,7 +6212,7 @@
         <v>2.4</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="R63" s="1">
         <v>100</v>
@@ -6260,7 +6260,7 @@
         <v>5</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="R64" s="1">
         <v>100</v>
@@ -6308,7 +6308,7 @@
         <v>5</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="R65" s="1">
         <v>100</v>
@@ -6356,7 +6356,7 @@
         <v>5</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="R66" s="1">
         <v>100</v>
@@ -6404,7 +6404,7 @@
         <v>5</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="R67" s="1">
         <v>100</v>
@@ -6887,7 +6887,7 @@
         <v>2</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="R78" s="1">
         <v>120</v>
@@ -6935,7 +6935,7 @@
         <v>2</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="R79" s="1">
         <v>120</v>
@@ -6983,7 +6983,7 @@
         <v>2</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="R80" s="1">
         <v>100</v>
@@ -7031,7 +7031,7 @@
         <v>2</v>
       </c>
       <c r="M81" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="R81" s="1">
         <v>100</v>
@@ -7079,7 +7079,7 @@
         <v>2</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="R82" s="1">
         <v>100</v>
@@ -7127,7 +7127,7 @@
         <v>2</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="R83" s="1">
         <v>100</v>
@@ -7175,7 +7175,7 @@
         <v>4</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="R84" s="1">
         <v>100</v>
@@ -7223,10 +7223,10 @@
         <v>0</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="O85" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="P85" s="3">
         <v>12</v>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="N86" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="O86" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="P86" s="3">
         <v>12</v>
@@ -7331,10 +7331,10 @@
         <v>0</v>
       </c>
       <c r="N87" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="O87" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="P87" s="3">
         <v>12</v>
@@ -7388,13 +7388,13 @@
         <v>0</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="N88" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="P88" s="3">
         <v>12</v>
@@ -7448,13 +7448,13 @@
         <v>0</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="N89" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="O89" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="P89" s="3">
         <v>12</v>
@@ -7508,13 +7508,13 @@
         <v>0</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="N90" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="O90" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="P90" s="3">
         <v>12</v>
@@ -7568,10 +7568,10 @@
         <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="O91" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="P91" s="3">
         <v>12</v>
@@ -7622,10 +7622,10 @@
         <v>0</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="O92" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="P92" s="3">
         <v>12</v>
@@ -7676,10 +7676,10 @@
         <v>0</v>
       </c>
       <c r="N93" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="O93" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="P93" s="3">
         <v>12</v>
@@ -7733,13 +7733,13 @@
         <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="N94" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="O94" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="P94" s="3">
         <v>12</v>
@@ -7793,13 +7793,13 @@
         <v>0</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="N95" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="O95" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="P95" s="3">
         <v>12</v>
@@ -7853,13 +7853,13 @@
         <v>0</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="N96" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="P96" s="3">
         <v>12</v>
@@ -7913,10 +7913,10 @@
         <v>0</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="O97" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="P97" s="3">
         <v>12</v>
@@ -7967,10 +7967,10 @@
         <v>0</v>
       </c>
       <c r="N98" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="O98" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="P98" s="3">
         <v>12</v>
@@ -8021,10 +8021,10 @@
         <v>0</v>
       </c>
       <c r="N99" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="O99" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="P99" s="3">
         <v>12</v>
@@ -8078,13 +8078,13 @@
         <v>0</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="N100" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="O100" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="P100" s="3">
         <v>12</v>
@@ -8138,13 +8138,13 @@
         <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="N101" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="O101" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="P101" s="3">
         <v>12</v>
@@ -8198,13 +8198,13 @@
         <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="N102" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="O102" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="P102" s="3">
         <v>12</v>
@@ -8258,13 +8258,13 @@
         <v>0</v>
       </c>
       <c r="M103" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="N103" s="3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="O103" s="3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="P103" s="3">
         <v>12</v>
@@ -8318,13 +8318,13 @@
         <v>0</v>
       </c>
       <c r="M104" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="N104" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="O104" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="P104" s="3">
         <v>12</v>
@@ -8378,13 +8378,13 @@
         <v>0</v>
       </c>
       <c r="M105" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="N105" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="O105" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="P105" s="3">
         <v>12</v>
@@ -8438,10 +8438,10 @@
         <v>0.25</v>
       </c>
       <c r="N106" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="O106" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="P106" s="3">
         <v>25</v>
@@ -8492,10 +8492,10 @@
         <v>0.25</v>
       </c>
       <c r="N107" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="O107" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="P107" s="3">
         <v>25</v>
@@ -8546,10 +8546,10 @@
         <v>0.25</v>
       </c>
       <c r="N108" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="O108" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="P108" s="3">
         <v>12</v>
@@ -8603,13 +8603,13 @@
         <v>0.25</v>
       </c>
       <c r="M109" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="N109" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="O109" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="P109" s="3">
         <v>25</v>
@@ -8663,13 +8663,13 @@
         <v>0.25</v>
       </c>
       <c r="M110" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="N110" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="O110" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="P110" s="3">
         <v>25</v>
@@ -8723,13 +8723,13 @@
         <v>0.25</v>
       </c>
       <c r="M111" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="N111" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="O111" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="P111" s="3">
         <v>25</v>
@@ -8783,10 +8783,10 @@
         <v>0.25</v>
       </c>
       <c r="N112" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="O112" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="P112" s="3">
         <v>25</v>
@@ -8837,10 +8837,10 @@
         <v>0.25</v>
       </c>
       <c r="N113" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="O113" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="P113" s="3">
         <v>25</v>
@@ -8891,10 +8891,10 @@
         <v>0.25</v>
       </c>
       <c r="N114" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="O114" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="P114" s="3">
         <v>12</v>
@@ -8948,13 +8948,13 @@
         <v>0.25</v>
       </c>
       <c r="M115" s="3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="N115" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="O115" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="P115" s="3">
         <v>25</v>
@@ -9008,13 +9008,13 @@
         <v>0.25</v>
       </c>
       <c r="M116" s="3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="N116" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="O116" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="P116" s="3">
         <v>25</v>
@@ -9068,13 +9068,13 @@
         <v>0.25</v>
       </c>
       <c r="M117" s="3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="N117" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="O117" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="P117" s="3">
         <v>25</v>
@@ -9128,10 +9128,10 @@
         <v>0.25</v>
       </c>
       <c r="N118" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="O118" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="P118" s="3">
         <v>25</v>
@@ -9182,10 +9182,10 @@
         <v>0.25</v>
       </c>
       <c r="N119" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="O119" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="P119" s="3">
         <v>25</v>
@@ -9236,10 +9236,10 @@
         <v>0.25</v>
       </c>
       <c r="N120" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="O120" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="P120" s="3">
         <v>12</v>
@@ -9293,13 +9293,13 @@
         <v>0.25</v>
       </c>
       <c r="M121" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="N121" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="O121" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="P121" s="3">
         <v>25</v>
@@ -9353,13 +9353,13 @@
         <v>0.25</v>
       </c>
       <c r="M122" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="N122" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="O122" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="P122" s="3">
         <v>25</v>
@@ -9413,13 +9413,13 @@
         <v>0.25</v>
       </c>
       <c r="M123" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="N123" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="O123" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="P123" s="3">
         <v>25</v>
@@ -9473,13 +9473,13 @@
         <v>0.25</v>
       </c>
       <c r="M124" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="N124" s="3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="O124" s="3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="P124" s="3">
         <v>25</v>
@@ -9533,13 +9533,13 @@
         <v>0.25</v>
       </c>
       <c r="M125" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="N125" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="O125" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="P125" s="3">
         <v>25</v>
@@ -9593,13 +9593,13 @@
         <v>0.25</v>
       </c>
       <c r="M126" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="N126" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="O126" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="P126" s="3">
         <v>25</v>
@@ -9653,10 +9653,10 @@
         <v>0.5</v>
       </c>
       <c r="N127" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="O127" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="P127" s="3">
         <v>31</v>
@@ -9707,10 +9707,10 @@
         <v>0.5</v>
       </c>
       <c r="N128" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="O128" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="P128" s="3">
         <v>31</v>
@@ -9761,10 +9761,10 @@
         <v>0.5</v>
       </c>
       <c r="N129" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="O129" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="P129" s="3">
         <v>12</v>
@@ -9818,13 +9818,13 @@
         <v>0.5</v>
       </c>
       <c r="M130" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="N130" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="O130" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="P130" s="3">
         <v>31</v>
@@ -9878,13 +9878,13 @@
         <v>0.5</v>
       </c>
       <c r="M131" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="N131" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="O131" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="P131" s="3">
         <v>31</v>
@@ -9938,13 +9938,13 @@
         <v>0.5</v>
       </c>
       <c r="M132" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="N132" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="O132" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="P132" s="3">
         <v>31</v>
@@ -9998,10 +9998,10 @@
         <v>0.5</v>
       </c>
       <c r="N133" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="O133" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="P133" s="3">
         <v>31</v>
@@ -10052,10 +10052,10 @@
         <v>0.5</v>
       </c>
       <c r="N134" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="O134" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="P134" s="3">
         <v>31</v>
@@ -10106,10 +10106,10 @@
         <v>0.5</v>
       </c>
       <c r="N135" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="O135" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="P135" s="3">
         <v>12</v>
@@ -10163,13 +10163,13 @@
         <v>0.5</v>
       </c>
       <c r="M136" s="3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="N136" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="O136" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="P136" s="3">
         <v>31</v>
@@ -10223,13 +10223,13 @@
         <v>0.5</v>
       </c>
       <c r="M137" s="3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="N137" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="O137" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="P137" s="3">
         <v>31</v>
@@ -10283,13 +10283,13 @@
         <v>0.5</v>
       </c>
       <c r="M138" s="3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="N138" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="O138" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="P138" s="3">
         <v>31</v>
@@ -10343,10 +10343,10 @@
         <v>0.5</v>
       </c>
       <c r="N139" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="O139" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="P139" s="3">
         <v>31</v>
@@ -10397,10 +10397,10 @@
         <v>0.5</v>
       </c>
       <c r="N140" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="O140" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="P140" s="3">
         <v>31</v>
@@ -10451,10 +10451,10 @@
         <v>0.5</v>
       </c>
       <c r="N141" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="O141" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="P141" s="3">
         <v>12</v>
@@ -10508,13 +10508,13 @@
         <v>0.5</v>
       </c>
       <c r="M142" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="N142" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="O142" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="P142" s="3">
         <v>31</v>
@@ -10568,13 +10568,13 @@
         <v>0.5</v>
       </c>
       <c r="M143" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="N143" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="O143" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="P143" s="3">
         <v>31</v>
@@ -10628,13 +10628,13 @@
         <v>0.5</v>
       </c>
       <c r="M144" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="N144" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="O144" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="P144" s="3">
         <v>31</v>
@@ -10688,13 +10688,13 @@
         <v>0.5</v>
       </c>
       <c r="M145" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="N145" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="O145" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="P145" s="3">
         <v>31</v>
@@ -10748,13 +10748,13 @@
         <v>0.5</v>
       </c>
       <c r="M146" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="N146" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="O146" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="P146" s="3">
         <v>31</v>
@@ -10808,7 +10808,7 @@
         <v>7.5</v>
       </c>
       <c r="M147" s="1" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="R147" s="1">
         <v>100</v>
@@ -10856,7 +10856,7 @@
         <v>20</v>
       </c>
       <c r="M148" s="1" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="R148" s="1">
         <v>100</v>
@@ -10880,16 +10880,16 @@
     </row>
     <row r="149" spans="1:22">
       <c r="A149" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>808</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>809</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E149" s="1">
         <v>1</v>
@@ -10904,7 +10904,7 @@
         <v>4</v>
       </c>
       <c r="M149" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="R149" s="1">
         <v>100</v>
@@ -10928,16 +10928,16 @@
     </row>
     <row r="150" spans="1:22">
       <c r="A150" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>833</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>834</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="E150" s="1">
         <v>1</v>
@@ -10952,7 +10952,7 @@
         <v>2</v>
       </c>
       <c r="M150" s="1" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="R150" s="1">
         <v>100</v>
@@ -11000,7 +11000,13 @@
         <v>0</v>
       </c>
       <c r="M151" s="1" t="s">
-        <v>869</v>
+        <v>868</v>
+      </c>
+      <c r="N151" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="O151" s="1" t="s">
+        <v>946</v>
       </c>
       <c r="P151" s="1">
         <v>7</v>
@@ -11051,7 +11057,13 @@
         <v>0.25</v>
       </c>
       <c r="M152" s="1" t="s">
-        <v>870</v>
+        <v>869</v>
+      </c>
+      <c r="N152" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="O152" s="1" t="s">
+        <v>946</v>
       </c>
       <c r="P152" s="1">
         <v>14</v>
@@ -11102,7 +11114,13 @@
         <v>0.5</v>
       </c>
       <c r="M153" s="1" t="s">
-        <v>871</v>
+        <v>870</v>
+      </c>
+      <c r="N153" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="O153" s="1" t="s">
+        <v>946</v>
       </c>
       <c r="P153" s="1">
         <v>21</v>
@@ -11153,7 +11171,13 @@
         <v>0.75</v>
       </c>
       <c r="M154" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
+      </c>
+      <c r="N154" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="O154" s="1" t="s">
+        <v>946</v>
       </c>
       <c r="P154" s="1">
         <v>28</v>
@@ -11204,7 +11228,13 @@
         <v>1</v>
       </c>
       <c r="M155" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
+      </c>
+      <c r="N155" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="O155" s="1" t="s">
+        <v>946</v>
       </c>
       <c r="P155" s="1">
         <v>35</v>
@@ -11297,7 +11327,7 @@
         <v>5</v>
       </c>
       <c r="M157" s="1" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="R157" s="1">
         <v>100</v>
@@ -11321,7 +11351,7 @@
     </row>
     <row r="158" spans="1:22">
       <c r="A158" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>473</v>
@@ -11345,7 +11375,7 @@
         <v>5</v>
       </c>
       <c r="M158" s="1" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="R158" s="1">
         <v>100</v>
@@ -11393,7 +11423,7 @@
         <v>6</v>
       </c>
       <c r="M159" s="1" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="R159" s="1">
         <v>100</v>
@@ -11441,7 +11471,7 @@
         <v>10</v>
       </c>
       <c r="M160" s="1" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="R160" s="1">
         <v>100</v>
@@ -11489,7 +11519,7 @@
         <v>0</v>
       </c>
       <c r="M161" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="R161" s="1">
         <v>70</v>
@@ -11537,7 +11567,7 @@
         <v>0.4</v>
       </c>
       <c r="M162" s="1" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="R162" s="1">
         <v>100</v>
@@ -11585,7 +11615,7 @@
         <v>0.4</v>
       </c>
       <c r="M163" s="1" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="R163" s="1">
         <v>100</v>
@@ -11633,7 +11663,7 @@
         <v>1.5</v>
       </c>
       <c r="M164" s="1" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="R164" s="1">
         <v>100</v>
@@ -11681,7 +11711,7 @@
         <v>50</v>
       </c>
       <c r="M165" s="1" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="R165" s="1">
         <v>100</v>
@@ -11729,7 +11759,7 @@
         <v>1.5</v>
       </c>
       <c r="M166" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="R166" s="1">
         <v>100</v>
@@ -11777,7 +11807,7 @@
         <v>50</v>
       </c>
       <c r="M167" s="1" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="R167" s="1">
         <v>100</v>
@@ -11801,16 +11831,16 @@
     </row>
     <row r="168" spans="1:22">
       <c r="A168" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>829</v>
       </c>
-      <c r="B168" s="1" t="s">
+      <c r="C168" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="C168" s="1" t="s">
+      <c r="D168" s="1" t="s">
         <v>831</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>832</v>
       </c>
       <c r="E168" s="1">
         <v>1</v>
@@ -11825,7 +11855,7 @@
         <v>1.5</v>
       </c>
       <c r="M168" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="R168" s="1">
         <v>100</v>
@@ -11873,7 +11903,7 @@
         <v>24</v>
       </c>
       <c r="M169" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="R169" s="1">
         <v>100</v>
@@ -11947,7 +11977,7 @@
         <v>24</v>
       </c>
       <c r="M171" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="R171" s="1">
         <v>100</v>
@@ -11995,7 +12025,7 @@
         <v>24</v>
       </c>
       <c r="M172" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="R172" s="1">
         <v>100</v>
@@ -12043,7 +12073,7 @@
         <v>24</v>
       </c>
       <c r="M173" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="R173" s="1">
         <v>100</v>
@@ -12133,7 +12163,7 @@
         <v>1</v>
       </c>
       <c r="M175" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="P175" s="1">
         <v>12</v>
@@ -12184,7 +12214,7 @@
         <v>1</v>
       </c>
       <c r="M176" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="P176" s="1">
         <v>12</v>
@@ -12211,16 +12241,16 @@
     </row>
     <row r="177" spans="1:22">
       <c r="A177" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>811</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>812</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="E177" s="1">
         <v>1</v>
@@ -12235,7 +12265,7 @@
         <v>3</v>
       </c>
       <c r="M177" s="1" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="R177" s="1">
         <v>100</v>
@@ -12259,16 +12289,16 @@
     </row>
     <row r="178" spans="1:22">
       <c r="A178" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E178" s="1">
         <v>3</v>
@@ -12283,7 +12313,7 @@
         <v>20</v>
       </c>
       <c r="M178" s="1" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="S178" s="1" t="str">
         <f t="shared" si="25"/>
@@ -12304,16 +12334,16 @@
     </row>
     <row r="179" spans="1:22">
       <c r="A179" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E179" s="1">
         <v>3</v>
@@ -12328,7 +12358,7 @@
         <v>20</v>
       </c>
       <c r="M179" s="1" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="S179" s="1" t="str">
         <f t="shared" si="25"/>
@@ -12349,16 +12379,16 @@
     </row>
     <row r="180" spans="1:22">
       <c r="A180" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>836</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>837</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="E180" s="1">
         <v>1</v>
@@ -12373,7 +12403,7 @@
         <v>0.5</v>
       </c>
       <c r="M180" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="S180" s="1" t="str">
         <f t="shared" si="25"/>
@@ -12418,13 +12448,13 @@
         <v>0</v>
       </c>
       <c r="M181" s="1" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="N181" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="O181" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="P181" s="1">
         <v>1</v>
@@ -12478,13 +12508,13 @@
         <v>0</v>
       </c>
       <c r="M182" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="N182" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="O182" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="P182" s="1">
         <v>6</v>
@@ -12538,13 +12568,13 @@
         <v>0</v>
       </c>
       <c r="M183" s="1" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="N183" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="O183" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="P183" s="1">
         <v>12</v>
@@ -12598,13 +12628,13 @@
         <v>0</v>
       </c>
       <c r="M184" s="1" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="N184" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="O184" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="P184" s="1">
         <v>19</v>
@@ -12658,13 +12688,13 @@
         <v>0</v>
       </c>
       <c r="M185" s="1" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="N185" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="O185" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="P185" s="1">
         <v>25</v>
@@ -12718,13 +12748,13 @@
         <v>0</v>
       </c>
       <c r="M186" s="1" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="N186" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="O186" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="P186" s="1">
         <v>31</v>
@@ -12778,13 +12808,13 @@
         <v>0</v>
       </c>
       <c r="M187" s="1" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="N187" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="O187" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="P187" s="1">
         <v>1</v>
@@ -12838,13 +12868,13 @@
         <v>0</v>
       </c>
       <c r="M188" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="N188" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="O188" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="P188" s="1">
         <v>6</v>
@@ -12898,13 +12928,13 @@
         <v>0</v>
       </c>
       <c r="M189" s="1" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="N189" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O189" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="P189" s="1">
         <v>12</v>
@@ -12958,13 +12988,13 @@
         <v>0</v>
       </c>
       <c r="M190" s="1" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="N190" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="O190" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="P190" s="1">
         <v>19</v>
@@ -13018,13 +13048,13 @@
         <v>0</v>
       </c>
       <c r="M191" s="1" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="N191" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="O191" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="P191" s="1">
         <v>25</v>
@@ -13078,13 +13108,13 @@
         <v>0</v>
       </c>
       <c r="M192" s="1" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="N192" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="O192" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="P192" s="1">
         <v>31</v>
@@ -13138,13 +13168,13 @@
         <v>0</v>
       </c>
       <c r="M193" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="N193" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="O193" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="P193" s="1">
         <v>1</v>
@@ -13198,13 +13228,13 @@
         <v>0</v>
       </c>
       <c r="M194" s="1" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="N194" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="O194" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="P194" s="1">
         <v>6</v>
@@ -13258,13 +13288,13 @@
         <v>0</v>
       </c>
       <c r="M195" s="1" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="N195" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="O195" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="P195" s="1">
         <v>12</v>
@@ -13318,13 +13348,13 @@
         <v>0</v>
       </c>
       <c r="M196" s="1" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="N196" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="O196" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="P196" s="1">
         <v>19</v>
@@ -13378,13 +13408,13 @@
         <v>0</v>
       </c>
       <c r="M197" s="1" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="N197" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="O197" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="P197" s="1">
         <v>25</v>
@@ -13438,13 +13468,13 @@
         <v>0</v>
       </c>
       <c r="M198" s="1" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="N198" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="O198" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="P198" s="1">
         <v>31</v>
@@ -13498,13 +13528,13 @@
         <v>0</v>
       </c>
       <c r="M199" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="N199" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="O199" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="P199" s="1">
         <v>1</v>
@@ -13558,13 +13588,13 @@
         <v>0</v>
       </c>
       <c r="M200" s="1" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="N200" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="O200" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="P200" s="1">
         <v>6</v>
@@ -13618,13 +13648,13 @@
         <v>0</v>
       </c>
       <c r="M201" s="1" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="N201" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="O201" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="P201" s="1">
         <v>12</v>
@@ -13678,13 +13708,13 @@
         <v>0</v>
       </c>
       <c r="M202" s="1" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="N202" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="O202" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="P202" s="1">
         <v>19</v>
@@ -13738,13 +13768,13 @@
         <v>0</v>
       </c>
       <c r="M203" s="1" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="N203" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="O203" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="P203" s="1">
         <v>25</v>
@@ -13798,13 +13828,13 @@
         <v>0</v>
       </c>
       <c r="M204" s="1" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="N204" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="O204" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="P204" s="1">
         <v>31</v>
@@ -13858,13 +13888,13 @@
         <v>0</v>
       </c>
       <c r="M205" s="1" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="N205" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="O205" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="P205" s="1">
         <v>1</v>
@@ -13918,13 +13948,13 @@
         <v>0</v>
       </c>
       <c r="M206" s="1" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="N206" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="O206" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="P206" s="1">
         <v>6</v>
@@ -13978,13 +14008,13 @@
         <v>0</v>
       </c>
       <c r="M207" s="1" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="N207" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O207" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="P207" s="1">
         <v>12</v>
@@ -14038,13 +14068,13 @@
         <v>0</v>
       </c>
       <c r="M208" s="1" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="N208" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="O208" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="P208" s="1">
         <v>19</v>
@@ -14098,13 +14128,13 @@
         <v>0</v>
       </c>
       <c r="M209" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="N209" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="O209" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="P209" s="1">
         <v>25</v>
@@ -14158,13 +14188,13 @@
         <v>0</v>
       </c>
       <c r="M210" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="N210" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="O210" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="P210" s="1">
         <v>31</v>
@@ -14218,13 +14248,13 @@
         <v>0</v>
       </c>
       <c r="M211" s="1" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="N211" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="O211" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="P211" s="1">
         <v>1</v>
@@ -14278,13 +14308,13 @@
         <v>0</v>
       </c>
       <c r="M212" s="1" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="N212" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="O212" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="P212" s="1">
         <v>6</v>
@@ -14338,13 +14368,13 @@
         <v>0</v>
       </c>
       <c r="M213" s="1" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="N213" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="O213" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="P213" s="1">
         <v>12</v>
@@ -14398,13 +14428,13 @@
         <v>0</v>
       </c>
       <c r="M214" s="1" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="N214" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="O214" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="P214" s="1">
         <v>19</v>
@@ -14458,13 +14488,13 @@
         <v>0</v>
       </c>
       <c r="M215" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="N215" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="O215" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="P215" s="1">
         <v>25</v>
@@ -14518,13 +14548,13 @@
         <v>0</v>
       </c>
       <c r="M216" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="N216" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="O216" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="P216" s="1">
         <v>31</v>
@@ -14578,13 +14608,13 @@
         <v>0.25</v>
       </c>
       <c r="M217" s="1" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="N217" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="O217" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="P217" s="1">
         <v>1</v>
@@ -14638,13 +14668,13 @@
         <v>0.25</v>
       </c>
       <c r="M218" s="1" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="N218" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="O218" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="P218" s="1">
         <v>6</v>
@@ -14698,13 +14728,13 @@
         <v>0.25</v>
       </c>
       <c r="M219" s="1" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="N219" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="O219" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="P219" s="1">
         <v>12</v>
@@ -14758,13 +14788,13 @@
         <v>0.25</v>
       </c>
       <c r="M220" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="N220" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="O220" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="P220" s="1">
         <v>19</v>
@@ -14818,13 +14848,13 @@
         <v>0.25</v>
       </c>
       <c r="M221" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="N221" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="O221" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="P221" s="1">
         <v>25</v>
@@ -14878,13 +14908,13 @@
         <v>0.25</v>
       </c>
       <c r="M222" s="1" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="N222" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="O222" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="P222" s="1">
         <v>31</v>
@@ -14938,13 +14968,13 @@
         <v>0.25</v>
       </c>
       <c r="M223" s="1" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="N223" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="O223" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="P223" s="1">
         <v>1</v>
@@ -14998,13 +15028,13 @@
         <v>0.25</v>
       </c>
       <c r="M224" s="1" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="N224" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="O224" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="P224" s="1">
         <v>6</v>
@@ -15058,13 +15088,13 @@
         <v>0.25</v>
       </c>
       <c r="M225" s="1" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="N225" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O225" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="P225" s="1">
         <v>12</v>
@@ -15118,13 +15148,13 @@
         <v>0.25</v>
       </c>
       <c r="M226" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="N226" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="O226" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="P226" s="1">
         <v>19</v>
@@ -15178,13 +15208,13 @@
         <v>0.25</v>
       </c>
       <c r="M227" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="N227" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="O227" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="P227" s="1">
         <v>25</v>
@@ -15238,13 +15268,13 @@
         <v>0.25</v>
       </c>
       <c r="M228" s="1" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="N228" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="O228" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="P228" s="1">
         <v>31</v>
@@ -15298,13 +15328,13 @@
         <v>0.25</v>
       </c>
       <c r="M229" s="1" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="N229" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="O229" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="P229" s="1">
         <v>1</v>
@@ -15358,13 +15388,13 @@
         <v>0.25</v>
       </c>
       <c r="M230" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="N230" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="O230" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="P230" s="1">
         <v>6</v>
@@ -15418,13 +15448,13 @@
         <v>0.25</v>
       </c>
       <c r="M231" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="N231" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="O231" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="P231" s="1">
         <v>12</v>
@@ -15478,13 +15508,13 @@
         <v>0.25</v>
       </c>
       <c r="M232" s="1" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="N232" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="O232" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="P232" s="1">
         <v>19</v>
@@ -15538,13 +15568,13 @@
         <v>0.25</v>
       </c>
       <c r="M233" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="N233" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="O233" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="P233" s="1">
         <v>25</v>
@@ -15598,13 +15628,13 @@
         <v>0.25</v>
       </c>
       <c r="M234" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="N234" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="O234" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="P234" s="1">
         <v>31</v>
@@ -15658,13 +15688,13 @@
         <v>0.25</v>
       </c>
       <c r="M235" s="1" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="N235" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="O235" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="P235" s="1">
         <v>1</v>
@@ -15718,13 +15748,13 @@
         <v>0.25</v>
       </c>
       <c r="M236" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="N236" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="O236" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="P236" s="1">
         <v>6</v>
@@ -15778,13 +15808,13 @@
         <v>0.25</v>
       </c>
       <c r="M237" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="N237" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="O237" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="P237" s="1">
         <v>12</v>
@@ -15838,13 +15868,13 @@
         <v>0.25</v>
       </c>
       <c r="M238" s="1" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="N238" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="O238" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="P238" s="1">
         <v>19</v>
@@ -15898,13 +15928,13 @@
         <v>0.25</v>
       </c>
       <c r="M239" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="N239" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="O239" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="P239" s="1">
         <v>25</v>
@@ -15958,13 +15988,13 @@
         <v>0.25</v>
       </c>
       <c r="M240" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="N240" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="O240" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="P240" s="1">
         <v>31</v>
@@ -16018,13 +16048,13 @@
         <v>0.25</v>
       </c>
       <c r="M241" s="1" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="N241" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="O241" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="P241" s="1">
         <v>1</v>
@@ -16078,13 +16108,13 @@
         <v>0.25</v>
       </c>
       <c r="M242" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="N242" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="O242" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="P242" s="1">
         <v>6</v>
@@ -16138,13 +16168,13 @@
         <v>0.25</v>
       </c>
       <c r="M243" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="N243" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O243" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="P243" s="1">
         <v>12</v>
@@ -16198,13 +16228,13 @@
         <v>0.25</v>
       </c>
       <c r="M244" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="N244" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="O244" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="P244" s="1">
         <v>19</v>
@@ -16258,13 +16288,13 @@
         <v>0.25</v>
       </c>
       <c r="M245" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="N245" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="O245" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="P245" s="1">
         <v>25</v>
@@ -16318,13 +16348,13 @@
         <v>0.25</v>
       </c>
       <c r="M246" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="N246" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="O246" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="P246" s="1">
         <v>31</v>
@@ -16378,13 +16408,13 @@
         <v>0.25</v>
       </c>
       <c r="M247" s="1" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="N247" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="O247" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="P247" s="1">
         <v>1</v>
@@ -16438,13 +16468,13 @@
         <v>0.25</v>
       </c>
       <c r="M248" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="N248" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="O248" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="P248" s="1">
         <v>6</v>
@@ -16498,13 +16528,13 @@
         <v>0.25</v>
       </c>
       <c r="M249" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="N249" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="O249" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="P249" s="1">
         <v>12</v>
@@ -16558,13 +16588,13 @@
         <v>0.25</v>
       </c>
       <c r="M250" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="N250" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="O250" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="P250" s="1">
         <v>19</v>
@@ -16618,13 +16648,13 @@
         <v>0.25</v>
       </c>
       <c r="M251" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="N251" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="O251" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="P251" s="1">
         <v>25</v>
@@ -16678,13 +16708,13 @@
         <v>0.25</v>
       </c>
       <c r="M252" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="N252" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="O252" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="P252" s="1">
         <v>31</v>
@@ -16738,13 +16768,13 @@
         <v>0.5</v>
       </c>
       <c r="M253" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="N253" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="O253" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="P253" s="1">
         <v>1</v>
@@ -16798,13 +16828,13 @@
         <v>0.5</v>
       </c>
       <c r="M254" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="N254" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="O254" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="P254" s="1">
         <v>6</v>
@@ -16858,13 +16888,13 @@
         <v>0.5</v>
       </c>
       <c r="M255" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="N255" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="O255" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="P255" s="1">
         <v>12</v>
@@ -16918,13 +16948,13 @@
         <v>0.5</v>
       </c>
       <c r="M256" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="N256" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="O256" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="P256" s="1">
         <v>19</v>
@@ -16978,13 +17008,13 @@
         <v>0.5</v>
       </c>
       <c r="M257" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="N257" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="O257" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="P257" s="1">
         <v>25</v>
@@ -17038,13 +17068,13 @@
         <v>0.5</v>
       </c>
       <c r="M258" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="N258" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="O258" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="P258" s="1">
         <v>31</v>
@@ -17098,13 +17128,13 @@
         <v>0.5</v>
       </c>
       <c r="M259" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="N259" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="O259" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="P259" s="1">
         <v>1</v>
@@ -17158,13 +17188,13 @@
         <v>0.5</v>
       </c>
       <c r="M260" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="N260" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="O260" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="P260" s="1">
         <v>6</v>
@@ -17218,13 +17248,13 @@
         <v>0.5</v>
       </c>
       <c r="M261" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="N261" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O261" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="P261" s="1">
         <v>12</v>
@@ -17278,13 +17308,13 @@
         <v>0.5</v>
       </c>
       <c r="M262" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="N262" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="O262" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="P262" s="1">
         <v>19</v>
@@ -17338,13 +17368,13 @@
         <v>0.5</v>
       </c>
       <c r="M263" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="N263" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="O263" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="P263" s="1">
         <v>25</v>
@@ -17398,13 +17428,13 @@
         <v>0.5</v>
       </c>
       <c r="M264" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="N264" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="O264" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="P264" s="1">
         <v>31</v>
@@ -17458,13 +17488,13 @@
         <v>0.5</v>
       </c>
       <c r="M265" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="N265" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="O265" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="P265" s="1">
         <v>1</v>
@@ -17518,13 +17548,13 @@
         <v>0.5</v>
       </c>
       <c r="M266" s="1" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="N266" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="O266" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="P266" s="1">
         <v>6</v>
@@ -17578,13 +17608,13 @@
         <v>0.5</v>
       </c>
       <c r="M267" s="1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="N267" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="O267" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="P267" s="1">
         <v>12</v>
@@ -17638,13 +17668,13 @@
         <v>0.5</v>
       </c>
       <c r="M268" s="1" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="N268" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="O268" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="P268" s="1">
         <v>19</v>
@@ -17698,13 +17728,13 @@
         <v>0.5</v>
       </c>
       <c r="M269" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="N269" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="O269" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="P269" s="1">
         <v>25</v>
@@ -17758,13 +17788,13 @@
         <v>0.5</v>
       </c>
       <c r="M270" s="1" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="N270" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="O270" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="P270" s="1">
         <v>31</v>
@@ -17818,13 +17848,13 @@
         <v>0.5</v>
       </c>
       <c r="M271" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="N271" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="O271" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="P271" s="1">
         <v>1</v>
@@ -17878,13 +17908,13 @@
         <v>0.5</v>
       </c>
       <c r="M272" s="1" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="N272" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="O272" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="P272" s="1">
         <v>6</v>
@@ -17938,13 +17968,13 @@
         <v>0.5</v>
       </c>
       <c r="M273" s="1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="N273" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="O273" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="P273" s="1">
         <v>12</v>
@@ -17998,13 +18028,13 @@
         <v>0.5</v>
       </c>
       <c r="M274" s="1" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="N274" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="O274" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="P274" s="1">
         <v>19</v>
@@ -18058,13 +18088,13 @@
         <v>0.5</v>
       </c>
       <c r="M275" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="N275" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="O275" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="P275" s="1">
         <v>25</v>
@@ -18118,13 +18148,13 @@
         <v>0.5</v>
       </c>
       <c r="M276" s="1" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="N276" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="O276" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="P276" s="1">
         <v>31</v>
@@ -18178,13 +18208,13 @@
         <v>0.5</v>
       </c>
       <c r="M277" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="N277" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="O277" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="P277" s="1">
         <v>1</v>
@@ -18238,13 +18268,13 @@
         <v>0.5</v>
       </c>
       <c r="M278" s="1" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="N278" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="O278" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="P278" s="1">
         <v>6</v>
@@ -18298,13 +18328,13 @@
         <v>0.5</v>
       </c>
       <c r="M279" s="1" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="N279" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O279" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="P279" s="1">
         <v>12</v>
@@ -18358,13 +18388,13 @@
         <v>0.5</v>
       </c>
       <c r="M280" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="N280" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="O280" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="P280" s="1">
         <v>19</v>
@@ -18418,13 +18448,13 @@
         <v>0.5</v>
       </c>
       <c r="M281" s="1" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="N281" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="O281" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="P281" s="1">
         <v>25</v>
@@ -18478,13 +18508,13 @@
         <v>0.5</v>
       </c>
       <c r="M282" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="N282" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="O282" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="P282" s="1">
         <v>31</v>
@@ -18538,13 +18568,13 @@
         <v>0.5</v>
       </c>
       <c r="M283" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="N283" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="O283" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="P283" s="1">
         <v>1</v>
@@ -18598,13 +18628,13 @@
         <v>0.5</v>
       </c>
       <c r="M284" s="1" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="N284" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="O284" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="P284" s="1">
         <v>6</v>
@@ -18658,13 +18688,13 @@
         <v>0.5</v>
       </c>
       <c r="M285" s="1" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="N285" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="O285" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="P285" s="1">
         <v>12</v>
@@ -18718,13 +18748,13 @@
         <v>0.5</v>
       </c>
       <c r="M286" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="N286" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="O286" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="P286" s="1">
         <v>19</v>
@@ -18778,13 +18808,13 @@
         <v>0.5</v>
       </c>
       <c r="M287" s="1" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="N287" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="O287" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="P287" s="1">
         <v>25</v>
@@ -18838,13 +18868,13 @@
         <v>0.5</v>
       </c>
       <c r="M288" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="N288" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="O288" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="P288" s="1">
         <v>31</v>
@@ -18898,10 +18928,10 @@
         <v>0.5</v>
       </c>
       <c r="N289" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="O289" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="P289" s="1">
         <v>1</v>
@@ -18952,10 +18982,10 @@
         <v>0.5</v>
       </c>
       <c r="N290" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="O290" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="P290" s="1">
         <v>6</v>
@@ -19006,10 +19036,10 @@
         <v>0.5</v>
       </c>
       <c r="N291" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="O291" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="P291" s="1">
         <v>12</v>
@@ -19060,10 +19090,10 @@
         <v>0.5</v>
       </c>
       <c r="N292" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="O292" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="P292" s="1">
         <v>19</v>
@@ -19114,10 +19144,10 @@
         <v>0.5</v>
       </c>
       <c r="N293" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="O293" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="P293" s="1">
         <v>25</v>
@@ -19168,10 +19198,10 @@
         <v>0.5</v>
       </c>
       <c r="N294" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="O294" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="P294" s="1">
         <v>31</v>
@@ -19222,10 +19252,10 @@
         <v>0.5</v>
       </c>
       <c r="N295" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="O295" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="P295" s="1">
         <v>1</v>
@@ -19276,10 +19306,10 @@
         <v>0.5</v>
       </c>
       <c r="N296" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="O296" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="P296" s="1">
         <v>6</v>
@@ -19330,10 +19360,10 @@
         <v>0.5</v>
       </c>
       <c r="N297" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O297" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="P297" s="1">
         <v>12</v>
@@ -19384,10 +19414,10 @@
         <v>0.5</v>
       </c>
       <c r="N298" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="O298" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="P298" s="1">
         <v>19</v>
@@ -19438,10 +19468,10 @@
         <v>0.5</v>
       </c>
       <c r="N299" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="O299" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="P299" s="1">
         <v>25</v>
@@ -19492,10 +19522,10 @@
         <v>0.5</v>
       </c>
       <c r="N300" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="O300" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="P300" s="1">
         <v>31</v>
@@ -19546,10 +19576,10 @@
         <v>0.5</v>
       </c>
       <c r="N301" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="O301" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="P301" s="1">
         <v>1</v>
@@ -19600,10 +19630,10 @@
         <v>0.5</v>
       </c>
       <c r="N302" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="O302" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="P302" s="1">
         <v>6</v>
@@ -19654,10 +19684,10 @@
         <v>0.5</v>
       </c>
       <c r="N303" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="O303" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="P303" s="1">
         <v>12</v>
@@ -19708,10 +19738,10 @@
         <v>0.5</v>
       </c>
       <c r="N304" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="O304" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="P304" s="1">
         <v>19</v>
@@ -19762,10 +19792,10 @@
         <v>0.5</v>
       </c>
       <c r="N305" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="O305" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="P305" s="1">
         <v>25</v>
@@ -19816,10 +19846,10 @@
         <v>0.5</v>
       </c>
       <c r="N306" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="O306" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="P306" s="1">
         <v>31</v>
@@ -19870,10 +19900,10 @@
         <v>0.5</v>
       </c>
       <c r="N307" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="O307" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="P307" s="1">
         <v>1</v>
@@ -19924,10 +19954,10 @@
         <v>0.5</v>
       </c>
       <c r="N308" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="O308" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="P308" s="1">
         <v>6</v>
@@ -19978,10 +20008,10 @@
         <v>0.5</v>
       </c>
       <c r="N309" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="O309" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="P309" s="1">
         <v>12</v>
@@ -20032,10 +20062,10 @@
         <v>0.5</v>
       </c>
       <c r="N310" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="O310" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="P310" s="1">
         <v>19</v>
@@ -20086,10 +20116,10 @@
         <v>0.5</v>
       </c>
       <c r="N311" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="O311" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="P311" s="1">
         <v>25</v>
@@ -20140,10 +20170,10 @@
         <v>0.5</v>
       </c>
       <c r="N312" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="O312" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="P312" s="1">
         <v>31</v>
@@ -20194,10 +20224,10 @@
         <v>0.5</v>
       </c>
       <c r="N313" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="O313" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="P313" s="1">
         <v>1</v>
@@ -20248,10 +20278,10 @@
         <v>0.5</v>
       </c>
       <c r="N314" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="O314" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="P314" s="1">
         <v>6</v>
@@ -20302,10 +20332,10 @@
         <v>0.5</v>
       </c>
       <c r="N315" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O315" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="P315" s="1">
         <v>12</v>
@@ -20356,10 +20386,10 @@
         <v>0.5</v>
       </c>
       <c r="N316" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="O316" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="P316" s="1">
         <v>19</v>
@@ -20410,10 +20440,10 @@
         <v>0.5</v>
       </c>
       <c r="N317" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="O317" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="P317" s="1">
         <v>25</v>
@@ -20464,10 +20494,10 @@
         <v>0.5</v>
       </c>
       <c r="N318" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="O318" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="P318" s="1">
         <v>31</v>
@@ -20518,10 +20548,10 @@
         <v>0.5</v>
       </c>
       <c r="N319" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="O319" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="P319" s="1">
         <v>1</v>
@@ -20572,10 +20602,10 @@
         <v>0.5</v>
       </c>
       <c r="N320" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="O320" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="P320" s="1">
         <v>6</v>
@@ -20626,10 +20656,10 @@
         <v>0.5</v>
       </c>
       <c r="N321" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="O321" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="P321" s="1">
         <v>12</v>
@@ -20680,10 +20710,10 @@
         <v>0.5</v>
       </c>
       <c r="N322" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="O322" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="P322" s="1">
         <v>19</v>
@@ -20734,10 +20764,10 @@
         <v>0.5</v>
       </c>
       <c r="N323" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="O323" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="P323" s="1">
         <v>25</v>
@@ -20788,10 +20818,10 @@
         <v>0.5</v>
       </c>
       <c r="N324" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="O324" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="P324" s="1">
         <v>31</v>
@@ -20848,7 +20878,7 @@
         <v>546</v>
       </c>
       <c r="M325" s="1" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="P325" s="1">
         <v>6</v>
@@ -20908,7 +20938,7 @@
         <v>546</v>
       </c>
       <c r="M326" s="1" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="P326" s="1">
         <v>25</v>
@@ -20968,7 +20998,7 @@
         <v>546</v>
       </c>
       <c r="M327" s="1" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="P327" s="1">
         <v>12</v>
@@ -21028,7 +21058,7 @@
         <v>546</v>
       </c>
       <c r="M328" s="1" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="P328" s="1">
         <v>31</v>
@@ -21088,7 +21118,7 @@
         <v>546</v>
       </c>
       <c r="M329" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="P329" s="1">
         <v>12</v>
@@ -21118,7 +21148,7 @@
     </row>
     <row r="330" spans="1:22">
       <c r="A330" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B330" s="1" t="s">
         <v>530</v>
@@ -21148,7 +21178,7 @@
         <v>546</v>
       </c>
       <c r="M330" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="P330" s="1">
         <v>25</v>
@@ -21178,7 +21208,7 @@
     </row>
     <row r="331" spans="1:22">
       <c r="A331" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B331" s="1" t="s">
         <v>531</v>
@@ -21208,7 +21238,7 @@
         <v>546</v>
       </c>
       <c r="M331" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="P331" s="1">
         <v>6</v>
@@ -21268,7 +21298,7 @@
         <v>546</v>
       </c>
       <c r="M332" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="P332" s="1">
         <v>19</v>
@@ -21328,7 +21358,7 @@
         <v>546</v>
       </c>
       <c r="M333" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="P333" s="1">
         <v>37</v>
@@ -21388,7 +21418,7 @@
         <v>546</v>
       </c>
       <c r="M334" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="P334" s="1">
         <v>25</v>
@@ -21448,7 +21478,7 @@
         <v>546</v>
       </c>
       <c r="M335" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="P335" s="1">
         <v>19</v>
@@ -21508,7 +21538,7 @@
         <v>546</v>
       </c>
       <c r="M336" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="P336" s="1">
         <v>19</v>
@@ -21562,7 +21592,7 @@
         <v>1.25</v>
       </c>
       <c r="M337" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R337" s="1">
         <v>100</v>
@@ -21610,7 +21640,7 @@
         <v>1.25</v>
       </c>
       <c r="M338" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R338" s="1">
         <v>100</v>
@@ -21658,7 +21688,7 @@
         <v>0.25</v>
       </c>
       <c r="M339" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="R339" s="1">
         <v>100</v>
@@ -21754,7 +21784,7 @@
         <v>8.75</v>
       </c>
       <c r="M341" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="P341" s="1">
         <v>30</v>

--- a/configs/Affix.xlsx
+++ b/configs/Affix.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B88FDC-2123-4351-883F-E99792C1F9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA0EB280-3D63-4229-A96C-D7A89A5392E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2207" uniqueCount="947">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2213" uniqueCount="949">
   <si>
     <t>id</t>
   </si>
@@ -2911,23 +2911,31 @@
   </si>
   <si>
     <t>socket</t>
+  </si>
+  <si>
+    <t>killtltn1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tltn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2985,9 +2993,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3294,20 +3312,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X369"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:X370"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.75" style="1" customWidth="1"/>
     <col min="4" max="4" width="8" style="1" customWidth="1"/>
-    <col min="5" max="8" width="6.42578125" style="1" customWidth="1"/>
-    <col min="9" max="12" width="7.28515625" style="1" customWidth="1"/>
-    <col min="13" max="22" width="7.85546875" style="1" customWidth="1"/>
+    <col min="5" max="8" width="6.375" style="1" customWidth="1"/>
+    <col min="9" max="12" width="7.25" style="1" customWidth="1"/>
+    <col min="13" max="22" width="7.875" style="1" customWidth="1"/>
     <col min="23" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3363,7 +3381,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -3428,7 +3446,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -3445,7 +3463,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>40</v>
       </c>
@@ -3501,7 +3519,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -3549,7 +3567,7 @@
         <v>10.74</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>41</v>
       </c>
@@ -3597,7 +3615,7 @@
         <v>10.74</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -3656,7 +3674,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -3707,7 +3725,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -3758,7 +3776,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -3809,7 +3827,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -3860,7 +3878,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>598</v>
       </c>
@@ -3905,7 +3923,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>599</v>
       </c>
@@ -3950,7 +3968,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>600</v>
       </c>
@@ -3995,7 +4013,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>601</v>
       </c>
@@ -4040,7 +4058,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>602</v>
       </c>
@@ -4085,7 +4103,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>564</v>
       </c>
@@ -4133,7 +4151,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>565</v>
       </c>
@@ -4181,7 +4199,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>566</v>
       </c>
@@ -4229,7 +4247,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>567</v>
       </c>
@@ -4277,7 +4295,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>568</v>
       </c>
@@ -4325,7 +4343,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>569</v>
       </c>
@@ -4373,7 +4391,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>570</v>
       </c>
@@ -4421,7 +4439,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>571</v>
       </c>
@@ -4469,7 +4487,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>572</v>
       </c>
@@ -4517,7 +4535,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>573</v>
       </c>
@@ -4565,7 +4583,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>15</v>
       </c>
@@ -4613,7 +4631,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>16</v>
       </c>
@@ -4661,7 +4679,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>17</v>
       </c>
@@ -4709,7 +4727,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>18</v>
       </c>
@@ -4757,7 +4775,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>19</v>
       </c>
@@ -4805,7 +4823,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>563</v>
       </c>
@@ -4850,7 +4868,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>610</v>
       </c>
@@ -4879,7 +4897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>611</v>
       </c>
@@ -4908,7 +4926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>612</v>
       </c>
@@ -4937,7 +4955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>613</v>
       </c>
@@ -4966,7 +4984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>20</v>
       </c>
@@ -5014,7 +5032,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="38" spans="1:22">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>21</v>
       </c>
@@ -5062,7 +5080,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>22</v>
       </c>
@@ -5110,7 +5128,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>23</v>
       </c>
@@ -5158,7 +5176,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="41" spans="1:22">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>24</v>
       </c>
@@ -5206,7 +5224,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="42" spans="1:22">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>813</v>
       </c>
@@ -5238,7 +5256,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="43" spans="1:22">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>814</v>
       </c>
@@ -5270,7 +5288,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>815</v>
       </c>
@@ -5302,7 +5320,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>25</v>
       </c>
@@ -5353,7 +5371,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="46" spans="1:22">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>26</v>
       </c>
@@ -5404,7 +5422,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="47" spans="1:22">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>27</v>
       </c>
@@ -5455,7 +5473,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="48" spans="1:22">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>28</v>
       </c>
@@ -5506,7 +5524,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>29</v>
       </c>
@@ -5557,7 +5575,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>605</v>
       </c>
@@ -5602,7 +5620,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>606</v>
       </c>
@@ -5647,7 +5665,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>607</v>
       </c>
@@ -5692,7 +5710,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="53" spans="1:22">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>608</v>
       </c>
@@ -5737,7 +5755,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>609</v>
       </c>
@@ -5782,7 +5800,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>282</v>
       </c>
@@ -5834,7 +5852,7 @@
         <v>50.25</v>
       </c>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>283</v>
       </c>
@@ -5886,7 +5904,7 @@
         <v>47.1</v>
       </c>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>284</v>
       </c>
@@ -5938,7 +5956,7 @@
         <v>52.95</v>
       </c>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>285</v>
       </c>
@@ -5990,7 +6008,7 @@
         <v>45.75</v>
       </c>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>286</v>
       </c>
@@ -6042,7 +6060,7 @@
         <v>54.900000000000006</v>
       </c>
     </row>
-    <row r="60" spans="1:22">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>30</v>
       </c>
@@ -6090,7 +6108,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="61" spans="1:22">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>31</v>
       </c>
@@ -6138,7 +6156,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="62" spans="1:22">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>293</v>
       </c>
@@ -6186,7 +6204,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="63" spans="1:22">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>32</v>
       </c>
@@ -6234,7 +6252,7 @@
         <v>88.2</v>
       </c>
     </row>
-    <row r="64" spans="1:22">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>33</v>
       </c>
@@ -6282,7 +6300,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="65" spans="1:22">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>34</v>
       </c>
@@ -6330,7 +6348,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="66" spans="1:22">
+    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>35</v>
       </c>
@@ -6378,7 +6396,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="67" spans="1:22">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>36</v>
       </c>
@@ -6426,7 +6444,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="68" spans="1:22">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>614</v>
       </c>
@@ -6471,7 +6489,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="69" spans="1:22">
+    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>615</v>
       </c>
@@ -6516,7 +6534,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="70" spans="1:22">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>616</v>
       </c>
@@ -6561,7 +6579,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="71" spans="1:22">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>617</v>
       </c>
@@ -6606,7 +6624,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="72" spans="1:22">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>618</v>
       </c>
@@ -6651,7 +6669,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="73" spans="1:22">
+    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>246</v>
       </c>
@@ -6693,7 +6711,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:22">
+    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>248</v>
       </c>
@@ -6735,7 +6753,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:22">
+    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>249</v>
       </c>
@@ -6777,7 +6795,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:22">
+    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>250</v>
       </c>
@@ -6819,7 +6837,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:22">
+    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>251</v>
       </c>
@@ -6861,7 +6879,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:22">
+    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>262</v>
       </c>
@@ -6909,7 +6927,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="1:22">
+    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>263</v>
       </c>
@@ -6957,7 +6975,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="80" spans="1:22">
+    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>264</v>
       </c>
@@ -7005,7 +7023,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="81" spans="1:22">
+    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>265</v>
       </c>
@@ -7053,7 +7071,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="82" spans="1:22">
+    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>266</v>
       </c>
@@ -7101,7 +7119,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="83" spans="1:22">
+    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>267</v>
       </c>
@@ -7149,7 +7167,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="84" spans="1:22">
+    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>268</v>
       </c>
@@ -7197,7 +7215,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="85" spans="1:22" s="3" customFormat="1">
+    <row r="85" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>42</v>
       </c>
@@ -7251,7 +7269,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:22" s="3" customFormat="1">
+    <row r="86" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>43</v>
       </c>
@@ -7305,7 +7323,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:22" s="3" customFormat="1">
+    <row r="87" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>744</v>
       </c>
@@ -7362,7 +7380,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:22" s="3" customFormat="1">
+    <row r="88" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>440</v>
       </c>
@@ -7422,7 +7440,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:22" s="3" customFormat="1">
+    <row r="89" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>441</v>
       </c>
@@ -7482,7 +7500,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:22" s="3" customFormat="1">
+    <row r="90" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>44</v>
       </c>
@@ -7542,7 +7560,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:22" s="3" customFormat="1">
+    <row r="91" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>45</v>
       </c>
@@ -7596,7 +7614,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:22" s="3" customFormat="1">
+    <row r="92" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>46</v>
       </c>
@@ -7650,7 +7668,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:22" s="3" customFormat="1">
+    <row r="93" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>743</v>
       </c>
@@ -7707,7 +7725,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:22" s="3" customFormat="1">
+    <row r="94" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>442</v>
       </c>
@@ -7767,7 +7785,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:22" s="3" customFormat="1">
+    <row r="95" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>443</v>
       </c>
@@ -7827,7 +7845,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:22" s="3" customFormat="1">
+    <row r="96" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>47</v>
       </c>
@@ -7887,7 +7905,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:22" s="3" customFormat="1">
+    <row r="97" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>48</v>
       </c>
@@ -7941,7 +7959,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:22" s="3" customFormat="1">
+    <row r="98" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>49</v>
       </c>
@@ -7995,7 +8013,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:22" s="3" customFormat="1">
+    <row r="99" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>746</v>
       </c>
@@ -8052,7 +8070,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:22" s="3" customFormat="1">
+    <row r="100" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>444</v>
       </c>
@@ -8112,7 +8130,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:22" s="3" customFormat="1">
+    <row r="101" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>445</v>
       </c>
@@ -8172,7 +8190,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:22" s="3" customFormat="1">
+    <row r="102" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>50</v>
       </c>
@@ -8232,7 +8250,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:22" s="3" customFormat="1">
+    <row r="103" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
         <v>51</v>
       </c>
@@ -8292,7 +8310,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:22" s="3" customFormat="1">
+    <row r="104" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
         <v>52</v>
       </c>
@@ -8352,7 +8370,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:22" s="3" customFormat="1">
+    <row r="105" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
         <v>53</v>
       </c>
@@ -8412,7 +8430,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:22" s="3" customFormat="1">
+    <row r="106" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>624</v>
       </c>
@@ -8466,7 +8484,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:22" s="3" customFormat="1">
+    <row r="107" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>625</v>
       </c>
@@ -8520,7 +8538,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:22" s="3" customFormat="1">
+    <row r="108" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>748</v>
       </c>
@@ -8577,7 +8595,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:22" s="3" customFormat="1">
+    <row r="109" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>626</v>
       </c>
@@ -8637,7 +8655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:22" s="3" customFormat="1">
+    <row r="110" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>627</v>
       </c>
@@ -8697,7 +8715,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:22" s="3" customFormat="1">
+    <row r="111" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>628</v>
       </c>
@@ -8757,7 +8775,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="112" spans="1:22" s="3" customFormat="1">
+    <row r="112" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>629</v>
       </c>
@@ -8811,7 +8829,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="113" spans="1:22" s="3" customFormat="1">
+    <row r="113" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>630</v>
       </c>
@@ -8865,7 +8883,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:22" s="3" customFormat="1">
+    <row r="114" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>749</v>
       </c>
@@ -8922,7 +8940,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:22" s="3" customFormat="1">
+    <row r="115" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
         <v>631</v>
       </c>
@@ -8982,7 +9000,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:22" s="3" customFormat="1">
+    <row r="116" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>632</v>
       </c>
@@ -9042,7 +9060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="117" spans="1:22" s="3" customFormat="1">
+    <row r="117" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
         <v>633</v>
       </c>
@@ -9102,7 +9120,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:22" s="3" customFormat="1">
+    <row r="118" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>634</v>
       </c>
@@ -9156,7 +9174,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="119" spans="1:22" s="3" customFormat="1">
+    <row r="119" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>635</v>
       </c>
@@ -9210,7 +9228,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:22" s="3" customFormat="1">
+    <row r="120" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>750</v>
       </c>
@@ -9267,7 +9285,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="121" spans="1:22" s="3" customFormat="1">
+    <row r="121" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>636</v>
       </c>
@@ -9327,7 +9345,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:22" s="3" customFormat="1">
+    <row r="122" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>637</v>
       </c>
@@ -9387,7 +9405,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:22" s="3" customFormat="1">
+    <row r="123" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
         <v>638</v>
       </c>
@@ -9447,7 +9465,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:22" s="3" customFormat="1">
+    <row r="124" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>639</v>
       </c>
@@ -9507,7 +9525,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:22" s="3" customFormat="1">
+    <row r="125" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>640</v>
       </c>
@@ -9567,7 +9585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:22" s="3" customFormat="1">
+    <row r="126" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>641</v>
       </c>
@@ -9627,7 +9645,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="127" spans="1:22" s="3" customFormat="1">
+    <row r="127" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>642</v>
       </c>
@@ -9681,7 +9699,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="128" spans="1:22" s="3" customFormat="1">
+    <row r="128" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>643</v>
       </c>
@@ -9735,7 +9753,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="129" spans="1:22" s="3" customFormat="1">
+    <row r="129" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
         <v>751</v>
       </c>
@@ -9792,7 +9810,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="130" spans="1:22" s="3" customFormat="1">
+    <row r="130" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>644</v>
       </c>
@@ -9852,7 +9870,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="131" spans="1:22" s="3" customFormat="1">
+    <row r="131" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
         <v>645</v>
       </c>
@@ -9912,7 +9930,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="1:22" s="3" customFormat="1">
+    <row r="132" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>646</v>
       </c>
@@ -9972,7 +9990,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:22" s="3" customFormat="1">
+    <row r="133" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>647</v>
       </c>
@@ -10026,7 +10044,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="134" spans="1:22" s="3" customFormat="1">
+    <row r="134" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>648</v>
       </c>
@@ -10080,7 +10098,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="135" spans="1:22" s="3" customFormat="1">
+    <row r="135" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>752</v>
       </c>
@@ -10137,7 +10155,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="136" spans="1:22" s="3" customFormat="1">
+    <row r="136" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>649</v>
       </c>
@@ -10197,7 +10215,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="137" spans="1:22" s="3" customFormat="1">
+    <row r="137" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>650</v>
       </c>
@@ -10257,7 +10275,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="138" spans="1:22" s="3" customFormat="1">
+    <row r="138" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>651</v>
       </c>
@@ -10317,7 +10335,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="139" spans="1:22" s="3" customFormat="1">
+    <row r="139" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>652</v>
       </c>
@@ -10371,7 +10389,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:22" s="3" customFormat="1">
+    <row r="140" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>653</v>
       </c>
@@ -10425,7 +10443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="141" spans="1:22" s="3" customFormat="1">
+    <row r="141" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>753</v>
       </c>
@@ -10482,7 +10500,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:22" s="3" customFormat="1">
+    <row r="142" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>654</v>
       </c>
@@ -10542,7 +10560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="143" spans="1:22" s="3" customFormat="1">
+    <row r="143" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
         <v>655</v>
       </c>
@@ -10602,7 +10620,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="144" spans="1:22" s="3" customFormat="1">
+    <row r="144" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
         <v>656</v>
       </c>
@@ -10662,7 +10680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="145" spans="1:22" s="3" customFormat="1">
+    <row r="145" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
         <v>657</v>
       </c>
@@ -10722,7 +10740,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="146" spans="1:22" s="3" customFormat="1">
+    <row r="146" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
         <v>658</v>
       </c>
@@ -10782,7 +10800,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="147" spans="1:22">
+    <row r="147" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>37</v>
       </c>
@@ -10830,7 +10848,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="148" spans="1:22">
+    <row r="148" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>38</v>
       </c>
@@ -10878,7 +10896,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="149" spans="1:22">
+    <row r="149" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>807</v>
       </c>
@@ -10926,7 +10944,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="150" spans="1:22">
+    <row r="150" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>832</v>
       </c>
@@ -10974,7 +10992,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="151" spans="1:22">
+    <row r="151" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>391</v>
       </c>
@@ -11031,7 +11049,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="152" spans="1:22">
+    <row r="152" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>190</v>
       </c>
@@ -11088,7 +11106,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:22">
+    <row r="153" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>191</v>
       </c>
@@ -11145,7 +11163,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="154" spans="1:22">
+    <row r="154" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>192</v>
       </c>
@@ -11202,7 +11220,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="155" spans="1:22">
+    <row r="155" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>193</v>
       </c>
@@ -11259,7 +11277,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="156" spans="1:22">
+    <row r="156" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>90</v>
       </c>
@@ -11301,7 +11319,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="1:22">
+    <row r="157" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>91</v>
       </c>
@@ -11349,7 +11367,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="158" spans="1:22">
+    <row r="158" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>843</v>
       </c>
@@ -11397,7 +11415,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="159" spans="1:22">
+    <row r="159" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>92</v>
       </c>
@@ -11445,7 +11463,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="160" spans="1:22">
+    <row r="160" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>93</v>
       </c>
@@ -11493,7 +11511,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="161" spans="1:22">
+    <row r="161" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>94</v>
       </c>
@@ -11541,7 +11559,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="162" spans="1:22">
+    <row r="162" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>95</v>
       </c>
@@ -11589,7 +11607,7 @@
         <v>10.74</v>
       </c>
     </row>
-    <row r="163" spans="1:22">
+    <row r="163" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>96</v>
       </c>
@@ -11637,7 +11655,7 @@
         <v>10.74</v>
       </c>
     </row>
-    <row r="164" spans="1:22">
+    <row r="164" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>97</v>
       </c>
@@ -11685,7 +11703,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="165" spans="1:22">
+    <row r="165" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>98</v>
       </c>
@@ -11733,7 +11751,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="166" spans="1:22">
+    <row r="166" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>99</v>
       </c>
@@ -11781,7 +11799,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="167" spans="1:22">
+    <row r="167" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>100</v>
       </c>
@@ -11829,7 +11847,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="168" spans="1:22">
+    <row r="168" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>828</v>
       </c>
@@ -11877,7 +11895,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="169" spans="1:22">
+    <row r="169" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>231</v>
       </c>
@@ -11925,7 +11943,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="170" spans="1:22">
+    <row r="170" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>562</v>
       </c>
@@ -11951,7 +11969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:22">
+    <row r="171" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>232</v>
       </c>
@@ -11999,7 +12017,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="172" spans="1:22">
+    <row r="172" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>233</v>
       </c>
@@ -12047,7 +12065,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="173" spans="1:22">
+    <row r="173" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>234</v>
       </c>
@@ -12095,7 +12113,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="174" spans="1:22">
+    <row r="174" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>561</v>
       </c>
@@ -12137,7 +12155,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="175" spans="1:22">
+    <row r="175" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>101</v>
       </c>
@@ -12188,7 +12206,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="176" spans="1:22">
+    <row r="176" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>102</v>
       </c>
@@ -12239,7 +12257,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="177" spans="1:22">
+    <row r="177" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>810</v>
       </c>
@@ -12287,7 +12305,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="178" spans="1:22">
+    <row r="178" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>822</v>
       </c>
@@ -12332,7 +12350,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="179" spans="1:22">
+    <row r="179" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>823</v>
       </c>
@@ -12377,7 +12395,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="180" spans="1:22">
+    <row r="180" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>835</v>
       </c>
@@ -12422,7 +12440,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="181" spans="1:22">
+    <row r="181" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>54</v>
       </c>
@@ -12482,7 +12500,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="182" spans="1:22">
+    <row r="182" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>55</v>
       </c>
@@ -12542,7 +12560,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="183" spans="1:22">
+    <row r="183" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>56</v>
       </c>
@@ -12602,7 +12620,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="184" spans="1:22">
+    <row r="184" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>57</v>
       </c>
@@ -12662,7 +12680,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="185" spans="1:22">
+    <row r="185" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>58</v>
       </c>
@@ -12722,7 +12740,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:22">
+    <row r="186" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>59</v>
       </c>
@@ -12782,7 +12800,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="187" spans="1:22">
+    <row r="187" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>60</v>
       </c>
@@ -12842,7 +12860,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="188" spans="1:22">
+    <row r="188" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>61</v>
       </c>
@@ -12902,7 +12920,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="189" spans="1:22">
+    <row r="189" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>62</v>
       </c>
@@ -12962,7 +12980,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="190" spans="1:22">
+    <row r="190" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>63</v>
       </c>
@@ -13022,7 +13040,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="191" spans="1:22">
+    <row r="191" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>64</v>
       </c>
@@ -13082,7 +13100,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="192" spans="1:22">
+    <row r="192" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>65</v>
       </c>
@@ -13142,7 +13160,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="193" spans="1:22">
+    <row r="193" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>66</v>
       </c>
@@ -13202,7 +13220,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="194" spans="1:22">
+    <row r="194" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>67</v>
       </c>
@@ -13262,7 +13280,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="195" spans="1:22">
+    <row r="195" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>68</v>
       </c>
@@ -13322,7 +13340,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:22">
+    <row r="196" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>69</v>
       </c>
@@ -13382,7 +13400,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="197" spans="1:22">
+    <row r="197" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>70</v>
       </c>
@@ -13442,7 +13460,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="198" spans="1:22">
+    <row r="198" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>71</v>
       </c>
@@ -13502,7 +13520,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="199" spans="1:22">
+    <row r="199" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>72</v>
       </c>
@@ -13562,7 +13580,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="200" spans="1:22">
+    <row r="200" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>73</v>
       </c>
@@ -13622,7 +13640,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="201" spans="1:22">
+    <row r="201" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>74</v>
       </c>
@@ -13682,7 +13700,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="202" spans="1:22">
+    <row r="202" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>75</v>
       </c>
@@ -13742,7 +13760,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="203" spans="1:22">
+    <row r="203" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>76</v>
       </c>
@@ -13802,7 +13820,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="204" spans="1:22">
+    <row r="204" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>77</v>
       </c>
@@ -13862,7 +13880,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="205" spans="1:22">
+    <row r="205" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>78</v>
       </c>
@@ -13922,7 +13940,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="206" spans="1:22">
+    <row r="206" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>79</v>
       </c>
@@ -13982,7 +14000,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="207" spans="1:22">
+    <row r="207" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>80</v>
       </c>
@@ -14042,7 +14060,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="208" spans="1:22">
+    <row r="208" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>81</v>
       </c>
@@ -14102,7 +14120,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="209" spans="1:22">
+    <row r="209" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>82</v>
       </c>
@@ -14162,7 +14180,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="210" spans="1:22">
+    <row r="210" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>83</v>
       </c>
@@ -14222,7 +14240,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="211" spans="1:22">
+    <row r="211" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>84</v>
       </c>
@@ -14282,7 +14300,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="212" spans="1:22">
+    <row r="212" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>85</v>
       </c>
@@ -14342,7 +14360,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="213" spans="1:22">
+    <row r="213" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>86</v>
       </c>
@@ -14402,7 +14420,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="214" spans="1:22">
+    <row r="214" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>87</v>
       </c>
@@ -14462,7 +14480,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="215" spans="1:22">
+    <row r="215" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>88</v>
       </c>
@@ -14522,7 +14540,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="216" spans="1:22">
+    <row r="216" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>89</v>
       </c>
@@ -14582,7 +14600,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="217" spans="1:22">
+    <row r="217" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>659</v>
       </c>
@@ -14642,7 +14660,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="218" spans="1:22">
+    <row r="218" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>660</v>
       </c>
@@ -14702,7 +14720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="219" spans="1:22">
+    <row r="219" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>661</v>
       </c>
@@ -14762,7 +14780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="220" spans="1:22">
+    <row r="220" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>662</v>
       </c>
@@ -14822,7 +14840,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="221" spans="1:22">
+    <row r="221" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>663</v>
       </c>
@@ -14882,7 +14900,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="222" spans="1:22">
+    <row r="222" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>664</v>
       </c>
@@ -14942,7 +14960,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="223" spans="1:22">
+    <row r="223" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>665</v>
       </c>
@@ -15002,7 +15020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="224" spans="1:22">
+    <row r="224" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>666</v>
       </c>
@@ -15062,7 +15080,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="225" spans="1:22">
+    <row r="225" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>667</v>
       </c>
@@ -15122,7 +15140,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="226" spans="1:22">
+    <row r="226" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>668</v>
       </c>
@@ -15182,7 +15200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="227" spans="1:22">
+    <row r="227" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>669</v>
       </c>
@@ -15242,7 +15260,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="228" spans="1:22">
+    <row r="228" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>670</v>
       </c>
@@ -15302,7 +15320,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="229" spans="1:22">
+    <row r="229" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>671</v>
       </c>
@@ -15362,7 +15380,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="230" spans="1:22">
+    <row r="230" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>672</v>
       </c>
@@ -15422,7 +15440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="231" spans="1:22">
+    <row r="231" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>673</v>
       </c>
@@ -15482,7 +15500,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="232" spans="1:22">
+    <row r="232" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>674</v>
       </c>
@@ -15542,7 +15560,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="233" spans="1:22">
+    <row r="233" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>675</v>
       </c>
@@ -15602,7 +15620,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="234" spans="1:22">
+    <row r="234" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>676</v>
       </c>
@@ -15662,7 +15680,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="235" spans="1:22">
+    <row r="235" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>677</v>
       </c>
@@ -15722,7 +15740,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="236" spans="1:22">
+    <row r="236" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>678</v>
       </c>
@@ -15782,7 +15800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="237" spans="1:22">
+    <row r="237" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>679</v>
       </c>
@@ -15842,7 +15860,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="238" spans="1:22">
+    <row r="238" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>680</v>
       </c>
@@ -15902,7 +15920,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="239" spans="1:22">
+    <row r="239" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>681</v>
       </c>
@@ -15962,7 +15980,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:22">
+    <row r="240" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>682</v>
       </c>
@@ -16022,7 +16040,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="241" spans="1:22">
+    <row r="241" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>683</v>
       </c>
@@ -16082,7 +16100,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="242" spans="1:22">
+    <row r="242" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>684</v>
       </c>
@@ -16142,7 +16160,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="243" spans="1:22">
+    <row r="243" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>685</v>
       </c>
@@ -16202,7 +16220,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="244" spans="1:22">
+    <row r="244" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>686</v>
       </c>
@@ -16262,7 +16280,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="245" spans="1:22">
+    <row r="245" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>687</v>
       </c>
@@ -16322,7 +16340,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="246" spans="1:22">
+    <row r="246" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>688</v>
       </c>
@@ -16382,7 +16400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="247" spans="1:22">
+    <row r="247" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>689</v>
       </c>
@@ -16442,7 +16460,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="248" spans="1:22">
+    <row r="248" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>690</v>
       </c>
@@ -16502,7 +16520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="249" spans="1:22">
+    <row r="249" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>691</v>
       </c>
@@ -16562,7 +16580,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="250" spans="1:22">
+    <row r="250" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>692</v>
       </c>
@@ -16622,7 +16640,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="251" spans="1:22">
+    <row r="251" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>693</v>
       </c>
@@ -16682,7 +16700,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="252" spans="1:22">
+    <row r="252" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>694</v>
       </c>
@@ -16742,7 +16760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="253" spans="1:22">
+    <row r="253" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>695</v>
       </c>
@@ -16802,7 +16820,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="254" spans="1:22">
+    <row r="254" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>696</v>
       </c>
@@ -16862,7 +16880,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="255" spans="1:22">
+    <row r="255" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>697</v>
       </c>
@@ -16922,7 +16940,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="256" spans="1:22">
+    <row r="256" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>698</v>
       </c>
@@ -16982,7 +17000,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="257" spans="1:22">
+    <row r="257" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>699</v>
       </c>
@@ -17042,7 +17060,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="258" spans="1:22">
+    <row r="258" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>700</v>
       </c>
@@ -17102,7 +17120,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="259" spans="1:22">
+    <row r="259" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>701</v>
       </c>
@@ -17162,7 +17180,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="260" spans="1:22">
+    <row r="260" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>702</v>
       </c>
@@ -17222,7 +17240,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="261" spans="1:22">
+    <row r="261" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>703</v>
       </c>
@@ -17282,7 +17300,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="262" spans="1:22">
+    <row r="262" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>704</v>
       </c>
@@ -17342,7 +17360,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="263" spans="1:22">
+    <row r="263" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>705</v>
       </c>
@@ -17402,7 +17420,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="264" spans="1:22">
+    <row r="264" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>706</v>
       </c>
@@ -17462,7 +17480,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="265" spans="1:22">
+    <row r="265" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>707</v>
       </c>
@@ -17522,7 +17540,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="266" spans="1:22">
+    <row r="266" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>708</v>
       </c>
@@ -17582,7 +17600,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="267" spans="1:22">
+    <row r="267" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>709</v>
       </c>
@@ -17642,7 +17660,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="268" spans="1:22">
+    <row r="268" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>710</v>
       </c>
@@ -17702,7 +17720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="269" spans="1:22">
+    <row r="269" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>711</v>
       </c>
@@ -17762,7 +17780,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="270" spans="1:22">
+    <row r="270" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>712</v>
       </c>
@@ -17822,7 +17840,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="271" spans="1:22">
+    <row r="271" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>713</v>
       </c>
@@ -17882,7 +17900,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="272" spans="1:22">
+    <row r="272" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>714</v>
       </c>
@@ -17942,7 +17960,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="273" spans="1:22">
+    <row r="273" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>715</v>
       </c>
@@ -18002,7 +18020,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="274" spans="1:22">
+    <row r="274" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>716</v>
       </c>
@@ -18062,7 +18080,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="275" spans="1:22">
+    <row r="275" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>717</v>
       </c>
@@ -18122,7 +18140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="276" spans="1:22">
+    <row r="276" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>718</v>
       </c>
@@ -18182,7 +18200,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="277" spans="1:22">
+    <row r="277" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>719</v>
       </c>
@@ -18242,7 +18260,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="278" spans="1:22">
+    <row r="278" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>720</v>
       </c>
@@ -18302,7 +18320,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="279" spans="1:22">
+    <row r="279" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>721</v>
       </c>
@@ -18362,7 +18380,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="280" spans="1:22">
+    <row r="280" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>722</v>
       </c>
@@ -18422,7 +18440,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="281" spans="1:22">
+    <row r="281" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>723</v>
       </c>
@@ -18482,7 +18500,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="282" spans="1:22">
+    <row r="282" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>724</v>
       </c>
@@ -18542,7 +18560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="283" spans="1:22">
+    <row r="283" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>725</v>
       </c>
@@ -18602,7 +18620,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="284" spans="1:22">
+    <row r="284" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>726</v>
       </c>
@@ -18662,7 +18680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="285" spans="1:22">
+    <row r="285" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>727</v>
       </c>
@@ -18722,7 +18740,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="286" spans="1:22">
+    <row r="286" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>728</v>
       </c>
@@ -18782,7 +18800,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="287" spans="1:22">
+    <row r="287" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>729</v>
       </c>
@@ -18842,7 +18860,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="288" spans="1:22">
+    <row r="288" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>730</v>
       </c>
@@ -18902,7 +18920,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="289" spans="1:22">
+    <row r="289" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>299</v>
       </c>
@@ -18956,7 +18974,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="290" spans="1:22">
+    <row r="290" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>301</v>
       </c>
@@ -19010,7 +19028,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="291" spans="1:22">
+    <row r="291" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>303</v>
       </c>
@@ -19064,7 +19082,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="292" spans="1:22">
+    <row r="292" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>305</v>
       </c>
@@ -19118,7 +19136,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="293" spans="1:22">
+    <row r="293" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>307</v>
       </c>
@@ -19172,7 +19190,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="294" spans="1:22">
+    <row r="294" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>309</v>
       </c>
@@ -19226,7 +19244,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="295" spans="1:22">
+    <row r="295" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>311</v>
       </c>
@@ -19280,7 +19298,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="296" spans="1:22">
+    <row r="296" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>313</v>
       </c>
@@ -19334,7 +19352,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="297" spans="1:22">
+    <row r="297" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>315</v>
       </c>
@@ -19388,7 +19406,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="298" spans="1:22">
+    <row r="298" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>317</v>
       </c>
@@ -19442,7 +19460,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="299" spans="1:22">
+    <row r="299" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>319</v>
       </c>
@@ -19496,7 +19514,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="300" spans="1:22">
+    <row r="300" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>321</v>
       </c>
@@ -19550,7 +19568,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="301" spans="1:22">
+    <row r="301" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>323</v>
       </c>
@@ -19604,7 +19622,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="302" spans="1:22">
+    <row r="302" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>325</v>
       </c>
@@ -19658,7 +19676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="303" spans="1:22">
+    <row r="303" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>327</v>
       </c>
@@ -19712,7 +19730,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="304" spans="1:22">
+    <row r="304" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>329</v>
       </c>
@@ -19766,7 +19784,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="305" spans="1:22">
+    <row r="305" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>331</v>
       </c>
@@ -19820,7 +19838,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="306" spans="1:22">
+    <row r="306" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>333</v>
       </c>
@@ -19874,7 +19892,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="307" spans="1:22">
+    <row r="307" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>335</v>
       </c>
@@ -19928,7 +19946,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="308" spans="1:22">
+    <row r="308" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>337</v>
       </c>
@@ -19982,7 +20000,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="309" spans="1:22">
+    <row r="309" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>339</v>
       </c>
@@ -20036,7 +20054,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="310" spans="1:22">
+    <row r="310" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>341</v>
       </c>
@@ -20090,7 +20108,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="311" spans="1:22">
+    <row r="311" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>343</v>
       </c>
@@ -20144,7 +20162,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="312" spans="1:22">
+    <row r="312" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>345</v>
       </c>
@@ -20198,7 +20216,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="313" spans="1:22">
+    <row r="313" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>347</v>
       </c>
@@ -20252,7 +20270,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="314" spans="1:22">
+    <row r="314" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>349</v>
       </c>
@@ -20306,7 +20324,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="315" spans="1:22">
+    <row r="315" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>351</v>
       </c>
@@ -20360,7 +20378,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="316" spans="1:22">
+    <row r="316" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>353</v>
       </c>
@@ -20414,7 +20432,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="317" spans="1:22">
+    <row r="317" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>355</v>
       </c>
@@ -20468,7 +20486,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="318" spans="1:22">
+    <row r="318" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>357</v>
       </c>
@@ -20522,7 +20540,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="319" spans="1:22">
+    <row r="319" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>359</v>
       </c>
@@ -20576,7 +20594,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="320" spans="1:22">
+    <row r="320" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>361</v>
       </c>
@@ -20630,7 +20648,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="321" spans="1:22">
+    <row r="321" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>363</v>
       </c>
@@ -20684,7 +20702,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="322" spans="1:22">
+    <row r="322" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>365</v>
       </c>
@@ -20738,7 +20756,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="323" spans="1:22">
+    <row r="323" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>367</v>
       </c>
@@ -20792,7 +20810,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="324" spans="1:22">
+    <row r="324" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>369</v>
       </c>
@@ -20846,7 +20864,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="325" spans="1:22">
+    <row r="325" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>103</v>
       </c>
@@ -20906,7 +20924,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="326" spans="1:22">
+    <row r="326" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>104</v>
       </c>
@@ -20966,7 +20984,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="327" spans="1:22">
+    <row r="327" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>105</v>
       </c>
@@ -21026,7 +21044,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="328" spans="1:22">
+    <row r="328" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>106</v>
       </c>
@@ -21086,7 +21104,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="329" spans="1:22">
+    <row r="329" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>107</v>
       </c>
@@ -21146,7 +21164,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="330" spans="1:22">
+    <row r="330" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>844</v>
       </c>
@@ -21206,7 +21224,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="331" spans="1:22">
+    <row r="331" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>845</v>
       </c>
@@ -21266,7 +21284,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="332" spans="1:22">
+    <row r="332" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>108</v>
       </c>
@@ -21326,7 +21344,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="333" spans="1:22">
+    <row r="333" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>549</v>
       </c>
@@ -21386,7 +21404,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="334" spans="1:22">
+    <row r="334" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>551</v>
       </c>
@@ -21446,7 +21464,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="335" spans="1:22">
+    <row r="335" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>553</v>
       </c>
@@ -21506,7 +21524,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="336" spans="1:22">
+    <row r="336" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>556</v>
       </c>
@@ -21566,7 +21584,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="337" spans="1:22">
+    <row r="337" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>113</v>
       </c>
@@ -21614,7 +21632,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="338" spans="1:22">
+    <row r="338" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>269</v>
       </c>
@@ -21662,7 +21680,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="339" spans="1:22">
+    <row r="339" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>271</v>
       </c>
@@ -21710,7 +21728,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="340" spans="1:22">
+    <row r="340" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>275</v>
       </c>
@@ -21758,7 +21776,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="341" spans="1:22">
+    <row r="341" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>276</v>
       </c>
@@ -21812,7 +21830,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="342" spans="1:22">
+    <row r="342" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>294</v>
       </c>
@@ -21860,7 +21878,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="343" spans="1:22">
+    <row r="343" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>295</v>
       </c>
@@ -21908,7 +21926,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="344" spans="1:22">
+    <row r="344" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>296</v>
       </c>
@@ -21956,7 +21974,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="345" spans="1:22">
+    <row r="345" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>297</v>
       </c>
@@ -22004,7 +22022,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="346" spans="1:22">
+    <row r="346" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>298</v>
       </c>
@@ -22052,7 +22070,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="347" spans="1:22">
+    <row r="347" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>619</v>
       </c>
@@ -22097,7 +22115,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="348" spans="1:22">
+    <row r="348" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>620</v>
       </c>
@@ -22142,7 +22160,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="349" spans="1:22">
+    <row r="349" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>621</v>
       </c>
@@ -22187,7 +22205,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="350" spans="1:22">
+    <row r="350" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>622</v>
       </c>
@@ -22232,7 +22250,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="351" spans="1:22">
+    <row r="351" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>623</v>
       </c>
@@ -22277,7 +22295,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="352" spans="1:22">
+    <row r="352" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>371</v>
       </c>
@@ -22319,7 +22337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="353" spans="1:22">
+    <row r="353" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>372</v>
       </c>
@@ -22357,11 +22375,11 @@
         <v>6-6</v>
       </c>
       <c r="V353" s="1">
-        <f t="shared" ref="V353:V369" si="53">_xlfn.LET(_xlpm.a,($E353+U$3*$G353)*(1+U$2),_xlpm.b,($F353+U$3*$H353)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <f t="shared" ref="V353:V370" si="53">_xlfn.LET(_xlpm.a,($E353+U$3*$G353)*(1+U$2),_xlpm.b,($F353+U$3*$H353)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="354" spans="1:22">
+    <row r="354" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>373</v>
       </c>
@@ -22403,7 +22421,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="355" spans="1:22">
+    <row r="355" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>374</v>
       </c>
@@ -22445,7 +22463,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="356" spans="1:22">
+    <row r="356" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>375</v>
       </c>
@@ -22487,7 +22505,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="357" spans="1:22">
+    <row r="357" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>376</v>
       </c>
@@ -22529,7 +22547,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="358" spans="1:22">
+    <row r="358" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>377</v>
       </c>
@@ -22571,7 +22589,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="359" spans="1:22">
+    <row r="359" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>378</v>
       </c>
@@ -22613,7 +22631,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="360" spans="1:22">
+    <row r="360" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>379</v>
       </c>
@@ -22655,7 +22673,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="361" spans="1:22">
+    <row r="361" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>380</v>
       </c>
@@ -22697,7 +22715,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="362" spans="1:22">
+    <row r="362" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>381</v>
       </c>
@@ -22739,7 +22757,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="363" spans="1:22">
+    <row r="363" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>382</v>
       </c>
@@ -22781,7 +22799,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="364" spans="1:22">
+    <row r="364" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>383</v>
       </c>
@@ -22823,7 +22841,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="365" spans="1:22">
+    <row r="365" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>384</v>
       </c>
@@ -22865,7 +22883,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="366" spans="1:22">
+    <row r="366" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>385</v>
       </c>
@@ -22907,7 +22925,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="367" spans="1:22">
+    <row r="367" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>386</v>
       </c>
@@ -22949,7 +22967,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="368" spans="1:22">
+    <row r="368" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>387</v>
       </c>
@@ -22991,7 +23009,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="369" spans="1:22">
+    <row r="369" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>388</v>
       </c>
@@ -23031,18 +23049,69 @@
       <c r="V369" s="1">
         <f t="shared" si="53"/>
         <v>6</v>
+      </c>
+    </row>
+    <row r="370" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A370" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="B370" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="C370" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D370" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="E370" s="1">
+        <v>1</v>
+      </c>
+      <c r="F370" s="1">
+        <v>1</v>
+      </c>
+      <c r="G370" s="1">
+        <v>0</v>
+      </c>
+      <c r="H370" s="1">
+        <v>2</v>
+      </c>
+      <c r="K370" s="1" t="s">
+        <v>948</v>
+      </c>
+      <c r="L370" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="S370" s="1" t="str">
+        <f t="shared" ref="S370:U370" si="55">_xlfn.LET(_xlpm.a,($E370+S$3*$G370)*(1+S$2),_xlpm.b,($F370+S$3*$H370)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
+        <v>1-1</v>
+      </c>
+      <c r="T370" s="1" t="str">
+        <f t="shared" si="55"/>
+        <v>1-9</v>
+      </c>
+      <c r="U370" s="1" t="str">
+        <f t="shared" si="55"/>
+        <v>6-54</v>
+      </c>
+      <c r="V370" s="1">
+        <f t="shared" si="53"/>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:V369" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B170">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B174">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B174">
+  <conditionalFormatting sqref="B370">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/configs/Affix.xlsx
+++ b/configs/Affix.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5DFFCB-672E-4871-8F7B-280D3EF9846D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2139B6-AA0F-47CD-8C21-1A9A45063DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$V$392</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$V$395</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2301" uniqueCount="971">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2313" uniqueCount="974">
   <si>
     <t>id</t>
   </si>
@@ -2985,23 +2985,35 @@
   </si>
   <si>
     <t>glvls</t>
+  </si>
+  <si>
+    <t>setheavy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>setsoul</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>setmagic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3066,9 +3078,69 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3405,20 +3477,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X392"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:X395"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.90625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.75" style="1" customWidth="1"/>
     <col min="4" max="4" width="8" style="1" customWidth="1"/>
-    <col min="5" max="8" width="6.36328125" style="1" customWidth="1"/>
-    <col min="9" max="12" width="7.26953125" style="1" customWidth="1"/>
-    <col min="13" max="22" width="7.90625" style="1" customWidth="1"/>
+    <col min="5" max="8" width="6.375" style="1" customWidth="1"/>
+    <col min="9" max="12" width="7.25" style="1" customWidth="1"/>
+    <col min="13" max="22" width="7.875" style="1" customWidth="1"/>
     <col min="23" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3474,7 +3546,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -3539,7 +3611,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -3556,7 +3628,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>40</v>
       </c>
@@ -3612,7 +3684,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -3660,7 +3732,7 @@
         <v>10.74</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>41</v>
       </c>
@@ -3708,7 +3780,7 @@
         <v>10.74</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -3767,7 +3839,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -3818,7 +3890,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -3869,7 +3941,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -3920,7 +3992,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -3971,7 +4043,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>598</v>
       </c>
@@ -4016,7 +4088,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>599</v>
       </c>
@@ -4061,7 +4133,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>600</v>
       </c>
@@ -4106,7 +4178,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>601</v>
       </c>
@@ -4151,7 +4223,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>602</v>
       </c>
@@ -4196,7 +4268,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>564</v>
       </c>
@@ -4244,7 +4316,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>565</v>
       </c>
@@ -4292,7 +4364,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>566</v>
       </c>
@@ -4340,7 +4412,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>567</v>
       </c>
@@ -4388,7 +4460,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>568</v>
       </c>
@@ -4436,7 +4508,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>569</v>
       </c>
@@ -4484,7 +4556,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>570</v>
       </c>
@@ -4532,7 +4604,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>571</v>
       </c>
@@ -4580,7 +4652,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>572</v>
       </c>
@@ -4628,7 +4700,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>573</v>
       </c>
@@ -4676,7 +4748,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>15</v>
       </c>
@@ -4724,7 +4796,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>16</v>
       </c>
@@ -4772,7 +4844,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>17</v>
       </c>
@@ -4820,7 +4892,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>18</v>
       </c>
@@ -4868,7 +4940,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>19</v>
       </c>
@@ -4916,7 +4988,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>563</v>
       </c>
@@ -4961,7 +5033,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>610</v>
       </c>
@@ -4990,7 +5062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>611</v>
       </c>
@@ -5019,7 +5091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>612</v>
       </c>
@@ -5048,7 +5120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>613</v>
       </c>
@@ -5077,7 +5149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>20</v>
       </c>
@@ -5125,7 +5197,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="38" spans="1:22">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>21</v>
       </c>
@@ -5173,7 +5245,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>22</v>
       </c>
@@ -5221,7 +5293,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>23</v>
       </c>
@@ -5269,7 +5341,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="41" spans="1:22">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>24</v>
       </c>
@@ -5317,7 +5389,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="42" spans="1:22">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>813</v>
       </c>
@@ -5349,7 +5421,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="43" spans="1:22">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>814</v>
       </c>
@@ -5381,7 +5453,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>815</v>
       </c>
@@ -5413,7 +5485,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>25</v>
       </c>
@@ -5464,7 +5536,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="46" spans="1:22">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>26</v>
       </c>
@@ -5515,7 +5587,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="47" spans="1:22">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>27</v>
       </c>
@@ -5566,7 +5638,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="48" spans="1:22">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>28</v>
       </c>
@@ -5617,7 +5689,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>29</v>
       </c>
@@ -5668,7 +5740,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>605</v>
       </c>
@@ -5713,7 +5785,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>606</v>
       </c>
@@ -5758,7 +5830,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>607</v>
       </c>
@@ -5803,7 +5875,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="53" spans="1:22">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>608</v>
       </c>
@@ -5848,7 +5920,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>609</v>
       </c>
@@ -5893,7 +5965,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>282</v>
       </c>
@@ -5945,7 +6017,7 @@
         <v>50.25</v>
       </c>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>283</v>
       </c>
@@ -5997,7 +6069,7 @@
         <v>47.1</v>
       </c>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>284</v>
       </c>
@@ -6049,7 +6121,7 @@
         <v>52.95</v>
       </c>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>285</v>
       </c>
@@ -6101,7 +6173,7 @@
         <v>45.75</v>
       </c>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>286</v>
       </c>
@@ -6153,7 +6225,7 @@
         <v>54.900000000000006</v>
       </c>
     </row>
-    <row r="60" spans="1:22">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>30</v>
       </c>
@@ -6201,7 +6273,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="61" spans="1:22">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>31</v>
       </c>
@@ -6249,7 +6321,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="62" spans="1:22">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>293</v>
       </c>
@@ -6297,7 +6369,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="63" spans="1:22">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>32</v>
       </c>
@@ -6345,7 +6417,7 @@
         <v>88.2</v>
       </c>
     </row>
-    <row r="64" spans="1:22">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>33</v>
       </c>
@@ -6393,7 +6465,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="65" spans="1:22">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>34</v>
       </c>
@@ -6441,7 +6513,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="66" spans="1:22">
+    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>35</v>
       </c>
@@ -6489,7 +6561,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="67" spans="1:22">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>36</v>
       </c>
@@ -6537,7 +6609,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="68" spans="1:22">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>614</v>
       </c>
@@ -6582,7 +6654,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="69" spans="1:22">
+    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>615</v>
       </c>
@@ -6627,7 +6699,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="70" spans="1:22">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>616</v>
       </c>
@@ -6672,7 +6744,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="71" spans="1:22">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>617</v>
       </c>
@@ -6717,7 +6789,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="72" spans="1:22">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>618</v>
       </c>
@@ -6762,7 +6834,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="73" spans="1:22">
+    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>246</v>
       </c>
@@ -6804,7 +6876,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:22">
+    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>248</v>
       </c>
@@ -6846,7 +6918,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:22">
+    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>249</v>
       </c>
@@ -6888,7 +6960,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:22">
+    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>250</v>
       </c>
@@ -6930,7 +7002,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:22">
+    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>251</v>
       </c>
@@ -6972,7 +7044,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:22">
+    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>262</v>
       </c>
@@ -7020,7 +7092,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="1:22">
+    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>263</v>
       </c>
@@ -7068,7 +7140,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="80" spans="1:22">
+    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>264</v>
       </c>
@@ -7116,7 +7188,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="81" spans="1:22">
+    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>265</v>
       </c>
@@ -7164,7 +7236,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="82" spans="1:22">
+    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>266</v>
       </c>
@@ -7212,7 +7284,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="83" spans="1:22">
+    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>267</v>
       </c>
@@ -7260,7 +7332,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="84" spans="1:22">
+    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>268</v>
       </c>
@@ -7308,7 +7380,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="85" spans="1:22" s="3" customFormat="1">
+    <row r="85" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>42</v>
       </c>
@@ -7362,7 +7434,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:22" s="3" customFormat="1">
+    <row r="86" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>43</v>
       </c>
@@ -7416,7 +7488,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:22" s="3" customFormat="1">
+    <row r="87" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>744</v>
       </c>
@@ -7473,7 +7545,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:22" s="3" customFormat="1">
+    <row r="88" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>440</v>
       </c>
@@ -7533,7 +7605,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:22" s="3" customFormat="1">
+    <row r="89" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>441</v>
       </c>
@@ -7593,7 +7665,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:22" s="3" customFormat="1">
+    <row r="90" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>44</v>
       </c>
@@ -7653,7 +7725,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:22" s="3" customFormat="1">
+    <row r="91" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>45</v>
       </c>
@@ -7707,7 +7779,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:22" s="3" customFormat="1">
+    <row r="92" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>46</v>
       </c>
@@ -7761,7 +7833,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:22" s="3" customFormat="1">
+    <row r="93" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>743</v>
       </c>
@@ -7818,7 +7890,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:22" s="3" customFormat="1">
+    <row r="94" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>442</v>
       </c>
@@ -7878,7 +7950,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:22" s="3" customFormat="1">
+    <row r="95" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>443</v>
       </c>
@@ -7938,7 +8010,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:22" s="3" customFormat="1">
+    <row r="96" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>47</v>
       </c>
@@ -7998,7 +8070,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:22" s="3" customFormat="1">
+    <row r="97" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>48</v>
       </c>
@@ -8052,7 +8124,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:22" s="3" customFormat="1">
+    <row r="98" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>49</v>
       </c>
@@ -8106,7 +8178,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:22" s="3" customFormat="1">
+    <row r="99" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>746</v>
       </c>
@@ -8163,7 +8235,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:22" s="3" customFormat="1">
+    <row r="100" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>444</v>
       </c>
@@ -8223,7 +8295,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:22" s="3" customFormat="1">
+    <row r="101" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>445</v>
       </c>
@@ -8283,7 +8355,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:22" s="3" customFormat="1">
+    <row r="102" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>50</v>
       </c>
@@ -8343,7 +8415,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:22" s="3" customFormat="1">
+    <row r="103" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
         <v>51</v>
       </c>
@@ -8403,7 +8475,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:22" s="3" customFormat="1">
+    <row r="104" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
         <v>52</v>
       </c>
@@ -8463,7 +8535,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:22" s="3" customFormat="1">
+    <row r="105" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
         <v>53</v>
       </c>
@@ -8523,7 +8595,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:22" s="3" customFormat="1">
+    <row r="106" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>624</v>
       </c>
@@ -8577,7 +8649,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:22" s="3" customFormat="1">
+    <row r="107" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>625</v>
       </c>
@@ -8631,7 +8703,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:22" s="3" customFormat="1">
+    <row r="108" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>748</v>
       </c>
@@ -8688,7 +8760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:22" s="3" customFormat="1">
+    <row r="109" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>626</v>
       </c>
@@ -8748,7 +8820,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:22" s="3" customFormat="1">
+    <row r="110" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>627</v>
       </c>
@@ -8808,7 +8880,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:22" s="3" customFormat="1">
+    <row r="111" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>628</v>
       </c>
@@ -8868,7 +8940,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="112" spans="1:22" s="3" customFormat="1">
+    <row r="112" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>629</v>
       </c>
@@ -8922,7 +8994,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="113" spans="1:22" s="3" customFormat="1">
+    <row r="113" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>630</v>
       </c>
@@ -8976,7 +9048,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:22" s="3" customFormat="1">
+    <row r="114" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>749</v>
       </c>
@@ -9033,7 +9105,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:22" s="3" customFormat="1">
+    <row r="115" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
         <v>631</v>
       </c>
@@ -9093,7 +9165,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:22" s="3" customFormat="1">
+    <row r="116" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>632</v>
       </c>
@@ -9153,7 +9225,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="117" spans="1:22" s="3" customFormat="1">
+    <row r="117" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
         <v>633</v>
       </c>
@@ -9213,7 +9285,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:22" s="3" customFormat="1">
+    <row r="118" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>634</v>
       </c>
@@ -9267,7 +9339,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="119" spans="1:22" s="3" customFormat="1">
+    <row r="119" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>635</v>
       </c>
@@ -9321,7 +9393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:22" s="3" customFormat="1">
+    <row r="120" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>750</v>
       </c>
@@ -9378,7 +9450,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="121" spans="1:22" s="3" customFormat="1">
+    <row r="121" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>636</v>
       </c>
@@ -9438,7 +9510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:22" s="3" customFormat="1">
+    <row r="122" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>637</v>
       </c>
@@ -9498,7 +9570,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:22" s="3" customFormat="1">
+    <row r="123" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
         <v>638</v>
       </c>
@@ -9558,7 +9630,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:22" s="3" customFormat="1">
+    <row r="124" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>639</v>
       </c>
@@ -9618,7 +9690,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:22" s="3" customFormat="1">
+    <row r="125" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>640</v>
       </c>
@@ -9678,7 +9750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:22" s="3" customFormat="1">
+    <row r="126" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>641</v>
       </c>
@@ -9738,7 +9810,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="127" spans="1:22" s="3" customFormat="1">
+    <row r="127" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>642</v>
       </c>
@@ -9792,7 +9864,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="128" spans="1:22" s="3" customFormat="1">
+    <row r="128" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>643</v>
       </c>
@@ -9846,7 +9918,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="129" spans="1:22" s="3" customFormat="1">
+    <row r="129" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
         <v>751</v>
       </c>
@@ -9903,7 +9975,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="130" spans="1:22" s="3" customFormat="1">
+    <row r="130" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>644</v>
       </c>
@@ -9963,7 +10035,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="131" spans="1:22" s="3" customFormat="1">
+    <row r="131" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
         <v>645</v>
       </c>
@@ -10023,7 +10095,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="1:22" s="3" customFormat="1">
+    <row r="132" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>646</v>
       </c>
@@ -10083,7 +10155,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:22" s="3" customFormat="1">
+    <row r="133" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>647</v>
       </c>
@@ -10137,7 +10209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="134" spans="1:22" s="3" customFormat="1">
+    <row r="134" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>648</v>
       </c>
@@ -10191,7 +10263,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="135" spans="1:22" s="3" customFormat="1">
+    <row r="135" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>752</v>
       </c>
@@ -10248,7 +10320,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="136" spans="1:22" s="3" customFormat="1">
+    <row r="136" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>649</v>
       </c>
@@ -10308,7 +10380,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="137" spans="1:22" s="3" customFormat="1">
+    <row r="137" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>650</v>
       </c>
@@ -10368,7 +10440,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="138" spans="1:22" s="3" customFormat="1">
+    <row r="138" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>651</v>
       </c>
@@ -10428,7 +10500,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="139" spans="1:22" s="3" customFormat="1">
+    <row r="139" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>652</v>
       </c>
@@ -10482,7 +10554,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:22" s="3" customFormat="1">
+    <row r="140" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>653</v>
       </c>
@@ -10536,7 +10608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="141" spans="1:22" s="3" customFormat="1">
+    <row r="141" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>753</v>
       </c>
@@ -10593,7 +10665,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:22" s="3" customFormat="1">
+    <row r="142" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>654</v>
       </c>
@@ -10653,7 +10725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="143" spans="1:22" s="3" customFormat="1">
+    <row r="143" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
         <v>655</v>
       </c>
@@ -10713,7 +10785,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="144" spans="1:22" s="3" customFormat="1">
+    <row r="144" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
         <v>656</v>
       </c>
@@ -10773,7 +10845,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="145" spans="1:22" s="3" customFormat="1">
+    <row r="145" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
         <v>657</v>
       </c>
@@ -10833,7 +10905,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="146" spans="1:22" s="3" customFormat="1">
+    <row r="146" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
         <v>658</v>
       </c>
@@ -10893,7 +10965,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="147" spans="1:22" s="5" customFormat="1">
+    <row r="147" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
         <v>950</v>
       </c>
@@ -10944,7 +11016,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="148" spans="1:22" s="5" customFormat="1">
+    <row r="148" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="5" t="s">
         <v>951</v>
       </c>
@@ -10995,7 +11067,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="1:22" s="5" customFormat="1">
+    <row r="149" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
         <v>952</v>
       </c>
@@ -11049,7 +11121,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:22" s="5" customFormat="1">
+    <row r="150" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="s">
         <v>953</v>
       </c>
@@ -11103,7 +11175,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:22" s="5" customFormat="1">
+    <row r="151" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
         <v>954</v>
       </c>
@@ -11157,7 +11229,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="152" spans="1:22" s="5" customFormat="1">
+    <row r="152" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="5" t="s">
         <v>955</v>
       </c>
@@ -11211,7 +11283,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="1:22" s="5" customFormat="1">
+    <row r="153" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
         <v>956</v>
       </c>
@@ -11262,7 +11334,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="154" spans="1:22" s="5" customFormat="1">
+    <row r="154" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="s">
         <v>957</v>
       </c>
@@ -11313,7 +11385,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="155" spans="1:22" s="5" customFormat="1">
+    <row r="155" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
         <v>958</v>
       </c>
@@ -11367,7 +11439,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="156" spans="1:22" s="5" customFormat="1">
+    <row r="156" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
         <v>959</v>
       </c>
@@ -11421,7 +11493,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="1:22" s="5" customFormat="1">
+    <row r="157" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
         <v>960</v>
       </c>
@@ -11475,7 +11547,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:22" s="5" customFormat="1">
+    <row r="158" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="s">
         <v>961</v>
       </c>
@@ -11529,7 +11601,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="159" spans="1:22" s="5" customFormat="1">
+    <row r="159" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="5" t="s">
         <v>962</v>
       </c>
@@ -11580,7 +11652,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="160" spans="1:22" s="5" customFormat="1">
+    <row r="160" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="5" t="s">
         <v>963</v>
       </c>
@@ -11631,7 +11703,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="161" spans="1:22" s="5" customFormat="1">
+    <row r="161" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
         <v>964</v>
       </c>
@@ -11685,7 +11757,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="162" spans="1:22" s="5" customFormat="1">
+    <row r="162" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="5" t="s">
         <v>965</v>
       </c>
@@ -11739,7 +11811,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="163" spans="1:22" s="5" customFormat="1">
+    <row r="163" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="5" t="s">
         <v>966</v>
       </c>
@@ -11793,7 +11865,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:22" s="5" customFormat="1">
+    <row r="164" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="5" t="s">
         <v>967</v>
       </c>
@@ -11847,7 +11919,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="165" spans="1:22" s="5" customFormat="1">
+    <row r="165" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="5" t="s">
         <v>968</v>
       </c>
@@ -11901,7 +11973,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="166" spans="1:22" s="5" customFormat="1">
+    <row r="166" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="5" t="s">
         <v>969</v>
       </c>
@@ -11955,7 +12027,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="167" spans="1:22" s="5" customFormat="1">
+    <row r="167" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="5" t="s">
         <v>970</v>
       </c>
@@ -12009,7 +12081,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="168" spans="1:22">
+    <row r="168" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>37</v>
       </c>
@@ -12057,7 +12129,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="169" spans="1:22">
+    <row r="169" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>38</v>
       </c>
@@ -12105,7 +12177,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="170" spans="1:22">
+    <row r="170" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>807</v>
       </c>
@@ -12153,7 +12225,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="171" spans="1:22">
+    <row r="171" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>832</v>
       </c>
@@ -12201,7 +12273,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="172" spans="1:22">
+    <row r="172" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>391</v>
       </c>
@@ -12258,7 +12330,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="173" spans="1:22">
+    <row r="173" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>190</v>
       </c>
@@ -12315,7 +12387,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="174" spans="1:22">
+    <row r="174" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>191</v>
       </c>
@@ -12372,7 +12444,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="175" spans="1:22">
+    <row r="175" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>192</v>
       </c>
@@ -12429,7 +12501,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="176" spans="1:22">
+    <row r="176" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>193</v>
       </c>
@@ -12486,7 +12558,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="177" spans="1:22">
+    <row r="177" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>90</v>
       </c>
@@ -12528,7 +12600,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:22">
+    <row r="178" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>91</v>
       </c>
@@ -12576,7 +12648,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="179" spans="1:22">
+    <row r="179" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>843</v>
       </c>
@@ -12624,7 +12696,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="180" spans="1:22">
+    <row r="180" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>92</v>
       </c>
@@ -12672,7 +12744,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="181" spans="1:22">
+    <row r="181" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>93</v>
       </c>
@@ -12720,7 +12792,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="182" spans="1:22">
+    <row r="182" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>94</v>
       </c>
@@ -12768,7 +12840,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="183" spans="1:22">
+    <row r="183" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>95</v>
       </c>
@@ -12816,7 +12888,7 @@
         <v>10.74</v>
       </c>
     </row>
-    <row r="184" spans="1:22">
+    <row r="184" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>96</v>
       </c>
@@ -12864,7 +12936,7 @@
         <v>10.74</v>
       </c>
     </row>
-    <row r="185" spans="1:22">
+    <row r="185" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>97</v>
       </c>
@@ -12912,7 +12984,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="186" spans="1:22">
+    <row r="186" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>98</v>
       </c>
@@ -12960,7 +13032,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="187" spans="1:22">
+    <row r="187" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>99</v>
       </c>
@@ -13008,7 +13080,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="188" spans="1:22">
+    <row r="188" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>100</v>
       </c>
@@ -13056,7 +13128,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="189" spans="1:22">
+    <row r="189" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>828</v>
       </c>
@@ -13104,7 +13176,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="190" spans="1:22">
+    <row r="190" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>231</v>
       </c>
@@ -13152,7 +13224,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="191" spans="1:22">
+    <row r="191" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>562</v>
       </c>
@@ -13178,7 +13250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:22">
+    <row r="192" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>232</v>
       </c>
@@ -13226,7 +13298,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="193" spans="1:22">
+    <row r="193" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>233</v>
       </c>
@@ -13274,7 +13346,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="194" spans="1:22">
+    <row r="194" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>234</v>
       </c>
@@ -13322,7 +13394,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="195" spans="1:22">
+    <row r="195" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>561</v>
       </c>
@@ -13364,7 +13436,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="196" spans="1:22">
+    <row r="196" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>101</v>
       </c>
@@ -13415,7 +13487,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="197" spans="1:22">
+    <row r="197" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>102</v>
       </c>
@@ -13466,7 +13538,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="198" spans="1:22">
+    <row r="198" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>810</v>
       </c>
@@ -13514,7 +13586,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="199" spans="1:22">
+    <row r="199" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>822</v>
       </c>
@@ -13559,7 +13631,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="200" spans="1:22">
+    <row r="200" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>823</v>
       </c>
@@ -13604,7 +13676,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="201" spans="1:22">
+    <row r="201" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>835</v>
       </c>
@@ -13649,7 +13721,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="202" spans="1:22">
+    <row r="202" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>54</v>
       </c>
@@ -13709,7 +13781,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="203" spans="1:22">
+    <row r="203" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>55</v>
       </c>
@@ -13769,7 +13841,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="204" spans="1:22">
+    <row r="204" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>56</v>
       </c>
@@ -13829,7 +13901,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="205" spans="1:22">
+    <row r="205" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>57</v>
       </c>
@@ -13889,7 +13961,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="206" spans="1:22">
+    <row r="206" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>58</v>
       </c>
@@ -13949,7 +14021,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="207" spans="1:22">
+    <row r="207" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>59</v>
       </c>
@@ -14009,7 +14081,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="208" spans="1:22">
+    <row r="208" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>60</v>
       </c>
@@ -14069,7 +14141,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="209" spans="1:22">
+    <row r="209" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>61</v>
       </c>
@@ -14129,7 +14201,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="210" spans="1:22">
+    <row r="210" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>62</v>
       </c>
@@ -14189,7 +14261,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="211" spans="1:22">
+    <row r="211" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>63</v>
       </c>
@@ -14249,7 +14321,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="212" spans="1:22">
+    <row r="212" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>64</v>
       </c>
@@ -14309,7 +14381,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="213" spans="1:22">
+    <row r="213" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>65</v>
       </c>
@@ -14369,7 +14441,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="214" spans="1:22">
+    <row r="214" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>66</v>
       </c>
@@ -14429,7 +14501,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="215" spans="1:22">
+    <row r="215" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>67</v>
       </c>
@@ -14489,7 +14561,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="216" spans="1:22">
+    <row r="216" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>68</v>
       </c>
@@ -14549,7 +14621,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="217" spans="1:22">
+    <row r="217" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>69</v>
       </c>
@@ -14609,7 +14681,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="218" spans="1:22">
+    <row r="218" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>70</v>
       </c>
@@ -14669,7 +14741,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="219" spans="1:22">
+    <row r="219" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>71</v>
       </c>
@@ -14729,7 +14801,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="220" spans="1:22">
+    <row r="220" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>72</v>
       </c>
@@ -14789,7 +14861,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="221" spans="1:22">
+    <row r="221" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>73</v>
       </c>
@@ -14849,7 +14921,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="222" spans="1:22">
+    <row r="222" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>74</v>
       </c>
@@ -14909,7 +14981,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="223" spans="1:22">
+    <row r="223" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>75</v>
       </c>
@@ -14969,7 +15041,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="224" spans="1:22">
+    <row r="224" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>76</v>
       </c>
@@ -15029,7 +15101,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="225" spans="1:22">
+    <row r="225" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>77</v>
       </c>
@@ -15089,7 +15161,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="226" spans="1:22">
+    <row r="226" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>78</v>
       </c>
@@ -15149,7 +15221,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="227" spans="1:22">
+    <row r="227" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>79</v>
       </c>
@@ -15209,7 +15281,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="228" spans="1:22">
+    <row r="228" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>80</v>
       </c>
@@ -15269,7 +15341,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="229" spans="1:22">
+    <row r="229" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>81</v>
       </c>
@@ -15329,7 +15401,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="230" spans="1:22">
+    <row r="230" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>82</v>
       </c>
@@ -15389,7 +15461,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="231" spans="1:22">
+    <row r="231" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>83</v>
       </c>
@@ -15449,7 +15521,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="232" spans="1:22">
+    <row r="232" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>84</v>
       </c>
@@ -15509,7 +15581,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="233" spans="1:22">
+    <row r="233" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>85</v>
       </c>
@@ -15569,7 +15641,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="234" spans="1:22">
+    <row r="234" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>86</v>
       </c>
@@ -15629,7 +15701,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="235" spans="1:22">
+    <row r="235" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>87</v>
       </c>
@@ -15689,7 +15761,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="236" spans="1:22">
+    <row r="236" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>88</v>
       </c>
@@ -15749,7 +15821,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="237" spans="1:22">
+    <row r="237" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>89</v>
       </c>
@@ -15809,7 +15881,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="238" spans="1:22">
+    <row r="238" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>659</v>
       </c>
@@ -15869,7 +15941,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="239" spans="1:22">
+    <row r="239" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>660</v>
       </c>
@@ -15929,7 +16001,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:22">
+    <row r="240" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>661</v>
       </c>
@@ -15989,7 +16061,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="241" spans="1:22">
+    <row r="241" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>662</v>
       </c>
@@ -16049,7 +16121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="242" spans="1:22">
+    <row r="242" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>663</v>
       </c>
@@ -16109,7 +16181,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="243" spans="1:22">
+    <row r="243" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>664</v>
       </c>
@@ -16169,7 +16241,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="244" spans="1:22">
+    <row r="244" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>665</v>
       </c>
@@ -16229,7 +16301,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="245" spans="1:22">
+    <row r="245" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>666</v>
       </c>
@@ -16289,7 +16361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="246" spans="1:22">
+    <row r="246" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>667</v>
       </c>
@@ -16349,7 +16421,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="247" spans="1:22">
+    <row r="247" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>668</v>
       </c>
@@ -16409,7 +16481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="248" spans="1:22">
+    <row r="248" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>669</v>
       </c>
@@ -16469,7 +16541,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="249" spans="1:22">
+    <row r="249" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>670</v>
       </c>
@@ -16529,7 +16601,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="250" spans="1:22">
+    <row r="250" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>671</v>
       </c>
@@ -16589,7 +16661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="251" spans="1:22">
+    <row r="251" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>672</v>
       </c>
@@ -16649,7 +16721,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="252" spans="1:22">
+    <row r="252" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>673</v>
       </c>
@@ -16709,7 +16781,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="253" spans="1:22">
+    <row r="253" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>674</v>
       </c>
@@ -16769,7 +16841,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="254" spans="1:22">
+    <row r="254" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>675</v>
       </c>
@@ -16829,7 +16901,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="255" spans="1:22">
+    <row r="255" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>676</v>
       </c>
@@ -16889,7 +16961,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="256" spans="1:22">
+    <row r="256" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>677</v>
       </c>
@@ -16949,7 +17021,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="257" spans="1:22">
+    <row r="257" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>678</v>
       </c>
@@ -17009,7 +17081,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="258" spans="1:22">
+    <row r="258" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>679</v>
       </c>
@@ -17069,7 +17141,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="259" spans="1:22">
+    <row r="259" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>680</v>
       </c>
@@ -17129,7 +17201,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="260" spans="1:22">
+    <row r="260" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>681</v>
       </c>
@@ -17189,7 +17261,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="261" spans="1:22">
+    <row r="261" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>682</v>
       </c>
@@ -17249,7 +17321,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="262" spans="1:22">
+    <row r="262" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>683</v>
       </c>
@@ -17309,7 +17381,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="263" spans="1:22">
+    <row r="263" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>684</v>
       </c>
@@ -17369,7 +17441,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="264" spans="1:22">
+    <row r="264" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>685</v>
       </c>
@@ -17429,7 +17501,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="265" spans="1:22">
+    <row r="265" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>686</v>
       </c>
@@ -17489,7 +17561,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="266" spans="1:22">
+    <row r="266" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>687</v>
       </c>
@@ -17549,7 +17621,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="267" spans="1:22">
+    <row r="267" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>688</v>
       </c>
@@ -17609,7 +17681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="268" spans="1:22">
+    <row r="268" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>689</v>
       </c>
@@ -17669,7 +17741,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="269" spans="1:22">
+    <row r="269" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>690</v>
       </c>
@@ -17729,7 +17801,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="270" spans="1:22">
+    <row r="270" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>691</v>
       </c>
@@ -17789,7 +17861,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="271" spans="1:22">
+    <row r="271" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>692</v>
       </c>
@@ -17849,7 +17921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="272" spans="1:22">
+    <row r="272" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>693</v>
       </c>
@@ -17909,7 +17981,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="273" spans="1:22">
+    <row r="273" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>694</v>
       </c>
@@ -17969,7 +18041,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="274" spans="1:22">
+    <row r="274" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>695</v>
       </c>
@@ -18029,7 +18101,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="275" spans="1:22">
+    <row r="275" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>696</v>
       </c>
@@ -18089,7 +18161,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="276" spans="1:22">
+    <row r="276" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>697</v>
       </c>
@@ -18149,7 +18221,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="277" spans="1:22">
+    <row r="277" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>698</v>
       </c>
@@ -18209,7 +18281,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="278" spans="1:22">
+    <row r="278" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>699</v>
       </c>
@@ -18269,7 +18341,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="279" spans="1:22">
+    <row r="279" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>700</v>
       </c>
@@ -18329,7 +18401,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="280" spans="1:22">
+    <row r="280" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>701</v>
       </c>
@@ -18389,7 +18461,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="281" spans="1:22">
+    <row r="281" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>702</v>
       </c>
@@ -18449,7 +18521,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="282" spans="1:22">
+    <row r="282" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>703</v>
       </c>
@@ -18509,7 +18581,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="283" spans="1:22">
+    <row r="283" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>704</v>
       </c>
@@ -18569,7 +18641,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="284" spans="1:22">
+    <row r="284" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>705</v>
       </c>
@@ -18629,7 +18701,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="285" spans="1:22">
+    <row r="285" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>706</v>
       </c>
@@ -18689,7 +18761,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="286" spans="1:22">
+    <row r="286" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>707</v>
       </c>
@@ -18749,7 +18821,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="287" spans="1:22">
+    <row r="287" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>708</v>
       </c>
@@ -18809,7 +18881,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="288" spans="1:22">
+    <row r="288" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>709</v>
       </c>
@@ -18869,7 +18941,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="289" spans="1:22">
+    <row r="289" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>710</v>
       </c>
@@ -18929,7 +19001,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="290" spans="1:22">
+    <row r="290" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>711</v>
       </c>
@@ -18989,7 +19061,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="291" spans="1:22">
+    <row r="291" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>712</v>
       </c>
@@ -19049,7 +19121,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="292" spans="1:22">
+    <row r="292" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>713</v>
       </c>
@@ -19109,7 +19181,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="293" spans="1:22">
+    <row r="293" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>714</v>
       </c>
@@ -19169,7 +19241,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="294" spans="1:22">
+    <row r="294" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>715</v>
       </c>
@@ -19229,7 +19301,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="295" spans="1:22">
+    <row r="295" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>716</v>
       </c>
@@ -19289,7 +19361,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="296" spans="1:22">
+    <row r="296" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>717</v>
       </c>
@@ -19349,7 +19421,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="297" spans="1:22">
+    <row r="297" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>718</v>
       </c>
@@ -19409,7 +19481,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="298" spans="1:22">
+    <row r="298" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>719</v>
       </c>
@@ -19469,7 +19541,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="299" spans="1:22">
+    <row r="299" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>720</v>
       </c>
@@ -19529,7 +19601,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="300" spans="1:22">
+    <row r="300" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>721</v>
       </c>
@@ -19589,7 +19661,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="301" spans="1:22">
+    <row r="301" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>722</v>
       </c>
@@ -19649,7 +19721,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="302" spans="1:22">
+    <row r="302" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>723</v>
       </c>
@@ -19709,7 +19781,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="303" spans="1:22">
+    <row r="303" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>724</v>
       </c>
@@ -19769,7 +19841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="304" spans="1:22">
+    <row r="304" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>725</v>
       </c>
@@ -19829,7 +19901,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="305" spans="1:22">
+    <row r="305" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>726</v>
       </c>
@@ -19889,7 +19961,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="306" spans="1:22">
+    <row r="306" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>727</v>
       </c>
@@ -19949,7 +20021,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="307" spans="1:22">
+    <row r="307" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>728</v>
       </c>
@@ -20009,7 +20081,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="308" spans="1:22">
+    <row r="308" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>729</v>
       </c>
@@ -20069,7 +20141,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="309" spans="1:22">
+    <row r="309" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>730</v>
       </c>
@@ -20129,7 +20201,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="310" spans="1:22">
+    <row r="310" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>299</v>
       </c>
@@ -20183,7 +20255,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="311" spans="1:22">
+    <row r="311" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>301</v>
       </c>
@@ -20237,7 +20309,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="312" spans="1:22">
+    <row r="312" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>303</v>
       </c>
@@ -20291,7 +20363,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="313" spans="1:22">
+    <row r="313" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>305</v>
       </c>
@@ -20345,7 +20417,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="314" spans="1:22">
+    <row r="314" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>307</v>
       </c>
@@ -20399,7 +20471,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="315" spans="1:22">
+    <row r="315" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>309</v>
       </c>
@@ -20453,7 +20525,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="316" spans="1:22">
+    <row r="316" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>311</v>
       </c>
@@ -20507,7 +20579,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="317" spans="1:22">
+    <row r="317" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>313</v>
       </c>
@@ -20561,7 +20633,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="318" spans="1:22">
+    <row r="318" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>315</v>
       </c>
@@ -20615,7 +20687,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="319" spans="1:22">
+    <row r="319" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>317</v>
       </c>
@@ -20669,7 +20741,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="320" spans="1:22">
+    <row r="320" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>319</v>
       </c>
@@ -20723,7 +20795,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="321" spans="1:22">
+    <row r="321" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>321</v>
       </c>
@@ -20777,7 +20849,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="322" spans="1:22">
+    <row r="322" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>323</v>
       </c>
@@ -20831,7 +20903,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="323" spans="1:22">
+    <row r="323" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>325</v>
       </c>
@@ -20885,7 +20957,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="324" spans="1:22">
+    <row r="324" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>327</v>
       </c>
@@ -20939,7 +21011,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="325" spans="1:22">
+    <row r="325" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>329</v>
       </c>
@@ -20993,7 +21065,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="326" spans="1:22">
+    <row r="326" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>331</v>
       </c>
@@ -21047,7 +21119,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="327" spans="1:22">
+    <row r="327" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>333</v>
       </c>
@@ -21101,7 +21173,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="328" spans="1:22">
+    <row r="328" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>335</v>
       </c>
@@ -21155,7 +21227,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="329" spans="1:22">
+    <row r="329" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>337</v>
       </c>
@@ -21209,7 +21281,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="330" spans="1:22">
+    <row r="330" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>339</v>
       </c>
@@ -21263,7 +21335,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="331" spans="1:22">
+    <row r="331" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>341</v>
       </c>
@@ -21317,7 +21389,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="332" spans="1:22">
+    <row r="332" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>343</v>
       </c>
@@ -21371,7 +21443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="333" spans="1:22">
+    <row r="333" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>345</v>
       </c>
@@ -21425,7 +21497,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="334" spans="1:22">
+    <row r="334" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>347</v>
       </c>
@@ -21479,7 +21551,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="335" spans="1:22">
+    <row r="335" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>349</v>
       </c>
@@ -21533,7 +21605,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="336" spans="1:22">
+    <row r="336" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>351</v>
       </c>
@@ -21587,7 +21659,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="337" spans="1:22">
+    <row r="337" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>353</v>
       </c>
@@ -21641,7 +21713,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="338" spans="1:22">
+    <row r="338" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>355</v>
       </c>
@@ -21695,7 +21767,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="339" spans="1:22">
+    <row r="339" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>357</v>
       </c>
@@ -21749,7 +21821,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="340" spans="1:22">
+    <row r="340" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>359</v>
       </c>
@@ -21803,7 +21875,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="341" spans="1:22">
+    <row r="341" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>361</v>
       </c>
@@ -21857,7 +21929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="342" spans="1:22">
+    <row r="342" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>363</v>
       </c>
@@ -21911,7 +21983,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="343" spans="1:22">
+    <row r="343" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>365</v>
       </c>
@@ -21965,7 +22037,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="344" spans="1:22">
+    <row r="344" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>367</v>
       </c>
@@ -22019,7 +22091,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="345" spans="1:22">
+    <row r="345" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>369</v>
       </c>
@@ -22073,7 +22145,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="346" spans="1:22">
+    <row r="346" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>103</v>
       </c>
@@ -22133,7 +22205,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="347" spans="1:22">
+    <row r="347" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>104</v>
       </c>
@@ -22193,7 +22265,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="348" spans="1:22">
+    <row r="348" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>105</v>
       </c>
@@ -22253,7 +22325,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="349" spans="1:22">
+    <row r="349" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>106</v>
       </c>
@@ -22313,7 +22385,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="350" spans="1:22">
+    <row r="350" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>107</v>
       </c>
@@ -22373,7 +22445,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="351" spans="1:22">
+    <row r="351" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>844</v>
       </c>
@@ -22433,7 +22505,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="352" spans="1:22">
+    <row r="352" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>845</v>
       </c>
@@ -22493,7 +22565,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="353" spans="1:22">
+    <row r="353" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>108</v>
       </c>
@@ -22553,7 +22625,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="354" spans="1:22">
+    <row r="354" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>549</v>
       </c>
@@ -22613,7 +22685,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="355" spans="1:22">
+    <row r="355" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>551</v>
       </c>
@@ -22673,7 +22745,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="356" spans="1:22">
+    <row r="356" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>553</v>
       </c>
@@ -22733,7 +22805,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="357" spans="1:22">
+    <row r="357" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>556</v>
       </c>
@@ -22793,7 +22865,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="358" spans="1:22">
+    <row r="358" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>113</v>
       </c>
@@ -22841,7 +22913,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="359" spans="1:22">
+    <row r="359" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>269</v>
       </c>
@@ -22889,7 +22961,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="360" spans="1:22">
+    <row r="360" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>271</v>
       </c>
@@ -22937,7 +23009,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="361" spans="1:22">
+    <row r="361" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>275</v>
       </c>
@@ -22985,7 +23057,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="362" spans="1:22">
+    <row r="362" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>949</v>
       </c>
@@ -23030,7 +23102,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="363" spans="1:22">
+    <row r="363" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>276</v>
       </c>
@@ -23084,7 +23156,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="364" spans="1:22">
+    <row r="364" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>294</v>
       </c>
@@ -23132,7 +23204,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="365" spans="1:22">
+    <row r="365" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>295</v>
       </c>
@@ -23180,7 +23252,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="366" spans="1:22">
+    <row r="366" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>296</v>
       </c>
@@ -23228,7 +23300,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="367" spans="1:22">
+    <row r="367" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>297</v>
       </c>
@@ -23276,7 +23348,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="368" spans="1:22">
+    <row r="368" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>298</v>
       </c>
@@ -23324,7 +23396,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="369" spans="1:22">
+    <row r="369" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>619</v>
       </c>
@@ -23369,7 +23441,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="370" spans="1:22">
+    <row r="370" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>620</v>
       </c>
@@ -23414,7 +23486,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="371" spans="1:22">
+    <row r="371" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>621</v>
       </c>
@@ -23459,7 +23531,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="372" spans="1:22">
+    <row r="372" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>622</v>
       </c>
@@ -23504,7 +23576,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="373" spans="1:22">
+    <row r="373" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>623</v>
       </c>
@@ -23549,60 +23621,47 @@
         <v>30</v>
       </c>
     </row>
-    <row r="374" spans="1:22">
+    <row r="374" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
-        <v>371</v>
+        <v>971</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>371</v>
+        <v>971</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D374" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="E374" s="1">
+        <v>1</v>
+      </c>
+      <c r="F374" s="1">
+        <v>1</v>
+      </c>
+      <c r="G374" s="1">
+        <v>0</v>
+      </c>
+      <c r="H374" s="1">
+        <v>0</v>
+      </c>
+      <c r="I374" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A375" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="E374" s="1">
-        <v>1</v>
-      </c>
-      <c r="F374" s="1">
-        <v>1</v>
-      </c>
-      <c r="G374" s="1">
-        <v>0</v>
-      </c>
-      <c r="H374" s="1">
-        <v>0</v>
-      </c>
-      <c r="S374" s="1" t="str">
-        <f t="shared" ref="S374:U375" si="54">_xlfn.LET(_xlpm.a,($E374+S$3*$G374)*(1+S$2),_xlpm.b,($F374+S$3*$H374)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
-        <v>1-1</v>
-      </c>
-      <c r="T374" s="1" t="str">
-        <f t="shared" si="54"/>
-        <v>1-1</v>
-      </c>
-      <c r="U374" s="1" t="str">
-        <f t="shared" si="54"/>
-        <v>6-6</v>
-      </c>
-      <c r="V374" s="1">
-        <f t="shared" ref="V374" si="55">_xlfn.LET(_xlpm.a,($E374+U$3*$G374)*(1+U$2),_xlpm.b,($F374+U$3*$H374)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="375" spans="1:22">
-      <c r="A375" s="1" t="s">
-        <v>372</v>
-      </c>
       <c r="B375" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E375" s="1">
         <v>1</v>
@@ -23616,8 +23675,11 @@
       <c r="H375" s="1">
         <v>0</v>
       </c>
+      <c r="I375" s="1">
+        <v>0</v>
+      </c>
       <c r="S375" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" ref="S375:U376" si="54">_xlfn.LET(_xlpm.a,($E375+S$3*$G375)*(1+S$2),_xlpm.b,($F375+S$3*$H375)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
         <v>1-1</v>
       </c>
       <c r="T375" s="1" t="str">
@@ -23629,64 +23691,67 @@
         <v>6-6</v>
       </c>
       <c r="V375" s="1">
-        <f t="shared" ref="V375:V392" si="56">_xlfn.LET(_xlpm.a,($E375+U$3*$G375)*(1+U$2),_xlpm.b,($F375+U$3*$H375)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <f t="shared" ref="V375" si="55">_xlfn.LET(_xlpm.a,($E375+U$3*$G375)*(1+U$2),_xlpm.b,($F375+U$3*$H375)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="376" spans="1:22">
+    <row r="376" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D376" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E376" s="1">
+        <v>1</v>
+      </c>
+      <c r="F376" s="1">
+        <v>1</v>
+      </c>
+      <c r="G376" s="1">
+        <v>0</v>
+      </c>
+      <c r="H376" s="1">
+        <v>0</v>
+      </c>
+      <c r="I376" s="1">
+        <v>0</v>
+      </c>
+      <c r="S376" s="1" t="str">
+        <f t="shared" si="54"/>
+        <v>1-1</v>
+      </c>
+      <c r="T376" s="1" t="str">
+        <f t="shared" si="54"/>
+        <v>1-1</v>
+      </c>
+      <c r="U376" s="1" t="str">
+        <f t="shared" si="54"/>
+        <v>6-6</v>
+      </c>
+      <c r="V376" s="1">
+        <f t="shared" ref="V376:V395" si="56">_xlfn.LET(_xlpm.a,($E376+U$3*$G376)*(1+U$2),_xlpm.b,($F376+U$3*$H376)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="377" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A377" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="E376" s="1">
-        <v>1</v>
-      </c>
-      <c r="F376" s="1">
-        <v>1</v>
-      </c>
-      <c r="G376" s="1">
-        <v>0</v>
-      </c>
-      <c r="H376" s="1">
-        <v>0</v>
-      </c>
-      <c r="S376" s="1" t="str">
-        <f t="shared" ref="S376:U391" si="57">_xlfn.LET(_xlpm.a,($E376+S$3*$G376)*(1+S$2),_xlpm.b,($F376+S$3*$H376)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
-        <v>1-1</v>
-      </c>
-      <c r="T376" s="1" t="str">
-        <f t="shared" si="57"/>
-        <v>1-1</v>
-      </c>
-      <c r="U376" s="1" t="str">
-        <f t="shared" si="57"/>
-        <v>6-6</v>
-      </c>
-      <c r="V376" s="1">
-        <f t="shared" si="56"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="377" spans="1:22">
-      <c r="A377" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="B377" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D377" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E377" s="1">
         <v>1</v>
@@ -23700,8 +23765,11 @@
       <c r="H377" s="1">
         <v>0</v>
       </c>
+      <c r="I377" s="1">
+        <v>0</v>
+      </c>
       <c r="S377" s="1" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" ref="S377:U394" si="57">_xlfn.LET(_xlpm.a,($E377+S$3*$G377)*(1+S$2),_xlpm.b,($F377+S$3*$H377)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
         <v>1-1</v>
       </c>
       <c r="T377" s="1" t="str">
@@ -23717,18 +23785,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="378" spans="1:22">
+    <row r="378" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
-        <v>375</v>
+        <v>972</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>375</v>
+        <v>972</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D378" s="1" t="s">
-        <v>375</v>
+        <v>972</v>
       </c>
       <c r="E378" s="1">
         <v>1</v>
@@ -23742,35 +23810,22 @@
       <c r="H378" s="1">
         <v>0</v>
       </c>
-      <c r="S378" s="1" t="str">
-        <f t="shared" si="57"/>
-        <v>1-1</v>
-      </c>
-      <c r="T378" s="1" t="str">
-        <f t="shared" si="57"/>
-        <v>1-1</v>
-      </c>
-      <c r="U378" s="1" t="str">
-        <f t="shared" si="57"/>
-        <v>6-6</v>
-      </c>
-      <c r="V378" s="1">
-        <f t="shared" si="56"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="379" spans="1:22">
+      <c r="I378" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E379" s="1">
         <v>1</v>
@@ -23782,6 +23837,9 @@
         <v>0</v>
       </c>
       <c r="H379" s="1">
+        <v>0</v>
+      </c>
+      <c r="I379" s="1">
         <v>0</v>
       </c>
       <c r="S379" s="1" t="str">
@@ -23801,18 +23859,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="380" spans="1:22">
+    <row r="380" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E380" s="1">
         <v>1</v>
@@ -23824,6 +23882,9 @@
         <v>0</v>
       </c>
       <c r="H380" s="1">
+        <v>0</v>
+      </c>
+      <c r="I380" s="1">
         <v>0</v>
       </c>
       <c r="S380" s="1" t="str">
@@ -23843,18 +23904,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="381" spans="1:22">
+    <row r="381" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E381" s="1">
         <v>1</v>
@@ -23866,6 +23927,9 @@
         <v>0</v>
       </c>
       <c r="H381" s="1">
+        <v>0</v>
+      </c>
+      <c r="I381" s="1">
         <v>0</v>
       </c>
       <c r="S381" s="1" t="str">
@@ -23885,18 +23949,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="382" spans="1:22">
+    <row r="382" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
-        <v>379</v>
+        <v>973</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>379</v>
+        <v>973</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>379</v>
+        <v>973</v>
       </c>
       <c r="E382" s="1">
         <v>1</v>
@@ -23910,35 +23974,22 @@
       <c r="H382" s="1">
         <v>0</v>
       </c>
-      <c r="S382" s="1" t="str">
-        <f t="shared" si="57"/>
-        <v>1-1</v>
-      </c>
-      <c r="T382" s="1" t="str">
-        <f t="shared" si="57"/>
-        <v>1-1</v>
-      </c>
-      <c r="U382" s="1" t="str">
-        <f t="shared" si="57"/>
-        <v>6-6</v>
-      </c>
-      <c r="V382" s="1">
-        <f t="shared" si="56"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="383" spans="1:22">
+      <c r="I382" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E383" s="1">
         <v>1</v>
@@ -23950,6 +24001,9 @@
         <v>0</v>
       </c>
       <c r="H383" s="1">
+        <v>0</v>
+      </c>
+      <c r="I383" s="1">
         <v>0</v>
       </c>
       <c r="S383" s="1" t="str">
@@ -23969,18 +24023,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="384" spans="1:22">
+    <row r="384" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E384" s="1">
         <v>1</v>
@@ -23992,6 +24046,9 @@
         <v>0</v>
       </c>
       <c r="H384" s="1">
+        <v>0</v>
+      </c>
+      <c r="I384" s="1">
         <v>0</v>
       </c>
       <c r="S384" s="1" t="str">
@@ -24011,18 +24068,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="385" spans="1:22">
+    <row r="385" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E385" s="1">
         <v>1</v>
@@ -24034,6 +24091,9 @@
         <v>0</v>
       </c>
       <c r="H385" s="1">
+        <v>0</v>
+      </c>
+      <c r="I385" s="1">
         <v>0</v>
       </c>
       <c r="S385" s="1" t="str">
@@ -24053,18 +24113,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="386" spans="1:22">
+    <row r="386" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E386" s="1">
         <v>1</v>
@@ -24076,6 +24136,9 @@
         <v>0</v>
       </c>
       <c r="H386" s="1">
+        <v>0</v>
+      </c>
+      <c r="I386" s="1">
         <v>0</v>
       </c>
       <c r="S386" s="1" t="str">
@@ -24095,18 +24158,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="387" spans="1:22">
+    <row r="387" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E387" s="1">
         <v>1</v>
@@ -24118,6 +24181,9 @@
         <v>0</v>
       </c>
       <c r="H387" s="1">
+        <v>0</v>
+      </c>
+      <c r="I387" s="1">
         <v>0</v>
       </c>
       <c r="S387" s="1" t="str">
@@ -24137,18 +24203,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="388" spans="1:22">
+    <row r="388" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="E388" s="1">
         <v>1</v>
@@ -24160,6 +24226,9 @@
         <v>0</v>
       </c>
       <c r="H388" s="1">
+        <v>0</v>
+      </c>
+      <c r="I388" s="1">
         <v>0</v>
       </c>
       <c r="S388" s="1" t="str">
@@ -24179,18 +24248,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="389" spans="1:22">
+    <row r="389" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D389" s="1" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E389" s="1">
         <v>1</v>
@@ -24202,6 +24271,9 @@
         <v>0</v>
       </c>
       <c r="H389" s="1">
+        <v>0</v>
+      </c>
+      <c r="I389" s="1">
         <v>0</v>
       </c>
       <c r="S389" s="1" t="str">
@@ -24221,18 +24293,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="390" spans="1:22">
+    <row r="390" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E390" s="1">
         <v>1</v>
@@ -24244,6 +24316,9 @@
         <v>0</v>
       </c>
       <c r="H390" s="1">
+        <v>0</v>
+      </c>
+      <c r="I390" s="1">
         <v>0</v>
       </c>
       <c r="S390" s="1" t="str">
@@ -24263,18 +24338,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="391" spans="1:22">
+    <row r="391" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E391" s="1">
         <v>1</v>
@@ -24286,6 +24361,9 @@
         <v>0</v>
       </c>
       <c r="H391" s="1">
+        <v>0</v>
+      </c>
+      <c r="I391" s="1">
         <v>0</v>
       </c>
       <c r="S391" s="1" t="str">
@@ -24305,73 +24383,226 @@
         <v>6</v>
       </c>
     </row>
-    <row r="392" spans="1:22">
+    <row r="392" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
-        <v>947</v>
+        <v>386</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>947</v>
+        <v>386</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D392" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="E392" s="1">
+        <v>1</v>
+      </c>
+      <c r="F392" s="1">
+        <v>1</v>
+      </c>
+      <c r="G392" s="1">
+        <v>0</v>
+      </c>
+      <c r="H392" s="1">
+        <v>0</v>
+      </c>
+      <c r="I392" s="1">
+        <v>0</v>
+      </c>
+      <c r="S392" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>1-1</v>
+      </c>
+      <c r="T392" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>1-1</v>
+      </c>
+      <c r="U392" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>6-6</v>
+      </c>
+      <c r="V392" s="1">
+        <f t="shared" si="56"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="393" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A393" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B393" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C393" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D393" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="E393" s="1">
+        <v>1</v>
+      </c>
+      <c r="F393" s="1">
+        <v>1</v>
+      </c>
+      <c r="G393" s="1">
+        <v>0</v>
+      </c>
+      <c r="H393" s="1">
+        <v>0</v>
+      </c>
+      <c r="I393" s="1">
+        <v>0</v>
+      </c>
+      <c r="S393" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>1-1</v>
+      </c>
+      <c r="T393" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>1-1</v>
+      </c>
+      <c r="U393" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>6-6</v>
+      </c>
+      <c r="V393" s="1">
+        <f t="shared" si="56"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="394" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A394" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B394" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C394" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D394" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E394" s="1">
+        <v>1</v>
+      </c>
+      <c r="F394" s="1">
+        <v>1</v>
+      </c>
+      <c r="G394" s="1">
+        <v>0</v>
+      </c>
+      <c r="H394" s="1">
+        <v>0</v>
+      </c>
+      <c r="I394" s="1">
+        <v>0</v>
+      </c>
+      <c r="S394" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>1-1</v>
+      </c>
+      <c r="T394" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>1-1</v>
+      </c>
+      <c r="U394" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>6-6</v>
+      </c>
+      <c r="V394" s="1">
+        <f t="shared" si="56"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="395" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A395" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="B395" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="C395" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D395" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="E392" s="1">
-        <v>1</v>
-      </c>
-      <c r="F392" s="1">
-        <v>1</v>
-      </c>
-      <c r="G392" s="1">
-        <v>0</v>
-      </c>
-      <c r="H392" s="1">
+      <c r="E395" s="1">
+        <v>1</v>
+      </c>
+      <c r="F395" s="1">
+        <v>1</v>
+      </c>
+      <c r="G395" s="1">
+        <v>0</v>
+      </c>
+      <c r="H395" s="1">
         <v>2</v>
       </c>
-      <c r="K392" s="1" t="s">
+      <c r="K395" s="1" t="s">
         <v>948</v>
       </c>
-      <c r="L392" s="1" t="s">
+      <c r="L395" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="S392" s="1" t="str">
-        <f t="shared" ref="S392:U392" si="58">_xlfn.LET(_xlpm.a,($E392+S$3*$G392)*(1+S$2),_xlpm.b,($F392+S$3*$H392)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
-        <v>1-1</v>
-      </c>
-      <c r="T392" s="1" t="str">
+      <c r="S395" s="1" t="str">
+        <f t="shared" ref="S395:U395" si="58">_xlfn.LET(_xlpm.a,($E395+S$3*$G395)*(1+S$2),_xlpm.b,($F395+S$3*$H395)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
+        <v>1-1</v>
+      </c>
+      <c r="T395" s="1" t="str">
         <f t="shared" si="58"/>
         <v>1-9</v>
       </c>
-      <c r="U392" s="1" t="str">
+      <c r="U395" s="1" t="str">
         <f t="shared" si="58"/>
         <v>6-54</v>
       </c>
-      <c r="V392" s="1">
+      <c r="V395" s="1">
         <f t="shared" si="56"/>
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:V392" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:V395" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B147:B167">
+    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B191">
+    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B195">
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B362">
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B395">
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B374">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D374">
     <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B195">
+  <conditionalFormatting sqref="D378">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B392">
+  <conditionalFormatting sqref="B378">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B362">
+  <conditionalFormatting sqref="B382">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B147:B167">
+  <conditionalFormatting sqref="D382">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/configs/Affix.xlsx
+++ b/configs/Affix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2139B6-AA0F-47CD-8C21-1A9A45063DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96020D5-109E-4348-9737-149B724020E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2313" uniqueCount="974">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2513" uniqueCount="1025">
   <si>
     <t>id</t>
   </si>
@@ -2997,6 +2997,160 @@
   <si>
     <t>setmagic</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>setany</t>
+  </si>
+  <si>
+    <t>setanys</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skfbltm1</t>
+  </si>
+  <si>
+    <t>skfrngm1</t>
+  </si>
+  <si>
+    <t>skfinfm1</t>
+  </si>
+  <si>
+    <t>skfbalm1</t>
+  </si>
+  <si>
+    <t>skfblsm1</t>
+  </si>
+  <si>
+    <t>skfblsm2</t>
+  </si>
+  <si>
+    <t>skfwalm1</t>
+  </si>
+  <si>
+    <t>skfwalm2</t>
+  </si>
+  <si>
+    <t>sktchmm1</t>
+  </si>
+  <si>
+    <t>sktbltm1</t>
+  </si>
+  <si>
+    <t>sktltnm1</t>
+  </si>
+  <si>
+    <t>sktltnm2</t>
+  </si>
+  <si>
+    <t>sktnovm1</t>
+  </si>
+  <si>
+    <t>sktshdm1</t>
+  </si>
+  <si>
+    <t>sktshdm2</t>
+  </si>
+  <si>
+    <t>sktblzm1</t>
+  </si>
+  <si>
+    <t>sktblzm2</t>
+  </si>
+  <si>
+    <t>skbbasm1</t>
+  </si>
+  <si>
+    <t>skbcrtm1</t>
+  </si>
+  <si>
+    <t>skbthrm1</t>
+  </si>
+  <si>
+    <t>skbclvm1</t>
+  </si>
+  <si>
+    <t>skbcrzm1</t>
+  </si>
+  <si>
+    <t>skbcrzm2</t>
+  </si>
+  <si>
+    <t>skbfblm1</t>
+  </si>
+  <si>
+    <t>skbfblm2</t>
+  </si>
+  <si>
+    <t>skxdefm1</t>
+  </si>
+  <si>
+    <t>skxdogm1</t>
+  </si>
+  <si>
+    <t>skxctam1</t>
+  </si>
+  <si>
+    <t>skxwmsm1</t>
+  </si>
+  <si>
+    <t>skxchgm1</t>
+  </si>
+  <si>
+    <t>skxtstm1</t>
+  </si>
+  <si>
+    <t>skxtstm2</t>
+  </si>
+  <si>
+    <t>skhhelm1</t>
+  </si>
+  <si>
+    <t>skhhelm2</t>
+  </si>
+  <si>
+    <t>skhgsdm1</t>
+  </si>
+  <si>
+    <t>skhinvm1</t>
+  </si>
+  <si>
+    <t>skhhsdm1</t>
+  </si>
+  <si>
+    <t>skhlokm1</t>
+  </si>
+  <si>
+    <t>skhlokm2</t>
+  </si>
+  <si>
+    <t>skhmhlm1</t>
+  </si>
+  <si>
+    <t>skhmhlm2</t>
+  </si>
+  <si>
+    <t>skpbasm1</t>
+  </si>
+  <si>
+    <t>skppoim1</t>
+  </si>
+  <si>
+    <t>skpsklm1</t>
+  </si>
+  <si>
+    <t>skprunm1</t>
+  </si>
+  <si>
+    <t>skpcblm1</t>
+  </si>
+  <si>
+    <t>skpcblm2</t>
+  </si>
+  <si>
+    <t>skpsdmm1</t>
+  </si>
+  <si>
+    <t>skpsdmm2</t>
   </si>
 </sst>
 </file>
@@ -3080,47 +3234,7 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3477,7 +3591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X395"/>
+  <dimension ref="A1:X445"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.875" style="1" customWidth="1"/>
@@ -24550,7 +24664,7 @@
         <v>546</v>
       </c>
       <c r="S395" s="1" t="str">
-        <f t="shared" ref="S395:U395" si="58">_xlfn.LET(_xlpm.a,($E395+S$3*$G395)*(1+S$2),_xlpm.b,($F395+S$3*$H395)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
+        <f t="shared" ref="S395:U397" si="58">_xlfn.LET(_xlpm.a,($E395+S$3*$G395)*(1+S$2),_xlpm.b,($F395+S$3*$H395)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
         <v>1-1</v>
       </c>
       <c r="T395" s="1" t="str">
@@ -24566,43 +24680,1513 @@
         <v>30</v>
       </c>
     </row>
+    <row r="396" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A396" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="B396" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="C396" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D396" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="E396" s="1">
+        <v>1</v>
+      </c>
+      <c r="F396" s="1">
+        <v>1</v>
+      </c>
+      <c r="G396" s="1">
+        <v>0</v>
+      </c>
+      <c r="H396" s="1">
+        <v>0</v>
+      </c>
+      <c r="I396" s="1">
+        <v>0</v>
+      </c>
+      <c r="S396" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>1-1</v>
+      </c>
+      <c r="T396" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>1-1</v>
+      </c>
+      <c r="U396" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>6-6</v>
+      </c>
+      <c r="V396" s="1">
+        <f t="shared" ref="V396:V397" si="59">_xlfn.LET(_xlpm.a,($E396+U$3*$G396)*(1+U$2),_xlpm.b,($F396+U$3*$H396)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="397" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A397" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="B397" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="C397" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D397" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="E397" s="1">
+        <v>5</v>
+      </c>
+      <c r="F397" s="1">
+        <v>10</v>
+      </c>
+      <c r="G397" s="1">
+        <v>0</v>
+      </c>
+      <c r="H397" s="1">
+        <v>0</v>
+      </c>
+      <c r="I397" s="1">
+        <v>0</v>
+      </c>
+      <c r="S397" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>5-10</v>
+      </c>
+      <c r="T397" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>5-10</v>
+      </c>
+      <c r="U397" s="1" t="str">
+        <f t="shared" si="58"/>
+        <v>30-60</v>
+      </c>
+      <c r="V397" s="1">
+        <f t="shared" si="59"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="398" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A398" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="B398" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D398" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="E398" s="1">
+        <v>1</v>
+      </c>
+      <c r="F398" s="1">
+        <v>1</v>
+      </c>
+      <c r="G398" s="1">
+        <v>0</v>
+      </c>
+      <c r="H398" s="1">
+        <v>0</v>
+      </c>
+      <c r="I398" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A399" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="B399" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="C399" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D399" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="E399" s="1">
+        <v>1</v>
+      </c>
+      <c r="F399" s="1">
+        <v>5</v>
+      </c>
+      <c r="G399" s="1">
+        <v>0</v>
+      </c>
+      <c r="H399" s="1">
+        <v>0</v>
+      </c>
+      <c r="I399" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A400" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="B400" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="C400" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D400" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="E400" s="1">
+        <v>1</v>
+      </c>
+      <c r="F400" s="1">
+        <v>7</v>
+      </c>
+      <c r="G400" s="1">
+        <v>0</v>
+      </c>
+      <c r="H400" s="1">
+        <v>0</v>
+      </c>
+      <c r="I400" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A401" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="B401" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="C401" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D401" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="E401" s="1">
+        <v>1</v>
+      </c>
+      <c r="F401" s="1">
+        <v>1</v>
+      </c>
+      <c r="G401" s="1">
+        <v>0</v>
+      </c>
+      <c r="H401" s="1">
+        <v>0</v>
+      </c>
+      <c r="I401" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A402" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="B402" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="C402" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D402" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="E402" s="1">
+        <v>20</v>
+      </c>
+      <c r="F402" s="1">
+        <v>33</v>
+      </c>
+      <c r="G402" s="1">
+        <v>0</v>
+      </c>
+      <c r="H402" s="1">
+        <v>0</v>
+      </c>
+      <c r="I402" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A403" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="B403" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="C403" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D403" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="E403" s="1">
+        <v>1</v>
+      </c>
+      <c r="F403" s="1">
+        <v>1</v>
+      </c>
+      <c r="G403" s="1">
+        <v>0</v>
+      </c>
+      <c r="H403" s="1">
+        <v>0</v>
+      </c>
+      <c r="I403" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A404" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="B404" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="C404" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D404" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="E404" s="1">
+        <v>10</v>
+      </c>
+      <c r="F404" s="1">
+        <v>40</v>
+      </c>
+      <c r="G404" s="1">
+        <v>0</v>
+      </c>
+      <c r="H404" s="1">
+        <v>0</v>
+      </c>
+      <c r="I404" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A405" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="B405" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="C405" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D405" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="E405" s="1">
+        <v>1</v>
+      </c>
+      <c r="F405" s="1">
+        <v>1</v>
+      </c>
+      <c r="G405" s="1">
+        <v>0</v>
+      </c>
+      <c r="H405" s="1">
+        <v>0</v>
+      </c>
+      <c r="I405" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A406" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="B406" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="C406" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D406" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="E406" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F406" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="G406" s="1">
+        <v>0</v>
+      </c>
+      <c r="H406" s="1">
+        <v>0</v>
+      </c>
+      <c r="I406" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A407" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="B407" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="C407" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D407" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="E407" s="1">
+        <v>15</v>
+      </c>
+      <c r="F407" s="1">
+        <v>0</v>
+      </c>
+      <c r="G407" s="1">
+        <v>0</v>
+      </c>
+      <c r="H407" s="1">
+        <v>0</v>
+      </c>
+      <c r="I407" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A408" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="B408" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="C408" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D408" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="E408" s="1">
+        <v>1</v>
+      </c>
+      <c r="F408" s="1">
+        <v>1</v>
+      </c>
+      <c r="G408" s="1">
+        <v>0</v>
+      </c>
+      <c r="H408" s="1">
+        <v>0</v>
+      </c>
+      <c r="I408" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A409" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="B409" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="C409" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D409" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="E409" s="1">
+        <v>5</v>
+      </c>
+      <c r="F409" s="1">
+        <v>15</v>
+      </c>
+      <c r="G409" s="1">
+        <v>0</v>
+      </c>
+      <c r="H409" s="1">
+        <v>0</v>
+      </c>
+      <c r="I409" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A410" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="B410" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="C410" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D410" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="E410" s="1">
+        <v>100</v>
+      </c>
+      <c r="F410" s="1">
+        <v>300</v>
+      </c>
+      <c r="G410" s="1">
+        <v>0</v>
+      </c>
+      <c r="H410" s="1">
+        <v>0</v>
+      </c>
+      <c r="I410" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A411" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="B411" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="C411" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D411" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="E411" s="1">
+        <v>300</v>
+      </c>
+      <c r="F411" s="1">
+        <v>800</v>
+      </c>
+      <c r="G411" s="1">
+        <v>0</v>
+      </c>
+      <c r="H411" s="1">
+        <v>0</v>
+      </c>
+      <c r="I411" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A412" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="B412" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="C412" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D412" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="E412" s="1">
+        <v>5</v>
+      </c>
+      <c r="F412" s="1">
+        <v>15</v>
+      </c>
+      <c r="G412" s="1">
+        <v>0</v>
+      </c>
+      <c r="H412" s="1">
+        <v>0</v>
+      </c>
+      <c r="I412" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A413" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="B413" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="C413" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D413" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="E413" s="1">
+        <v>1</v>
+      </c>
+      <c r="F413" s="1">
+        <v>3</v>
+      </c>
+      <c r="G413" s="1">
+        <v>0</v>
+      </c>
+      <c r="H413" s="1">
+        <v>0</v>
+      </c>
+      <c r="I413" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A414" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="B414" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="C414" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D414" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="E414" s="1">
+        <v>3</v>
+      </c>
+      <c r="F414" s="1">
+        <v>9</v>
+      </c>
+      <c r="G414" s="1">
+        <v>0</v>
+      </c>
+      <c r="H414" s="1">
+        <v>0</v>
+      </c>
+      <c r="I414" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A415" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="B415" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="C415" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D415" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="E415" s="1">
+        <v>1</v>
+      </c>
+      <c r="F415" s="1">
+        <v>1</v>
+      </c>
+      <c r="G415" s="1">
+        <v>0</v>
+      </c>
+      <c r="H415" s="1">
+        <v>0</v>
+      </c>
+      <c r="I415" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A416" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="B416" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="C416" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D416" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="E416" s="1">
+        <v>12</v>
+      </c>
+      <c r="F416" s="1">
+        <v>24</v>
+      </c>
+      <c r="G416" s="1">
+        <v>0</v>
+      </c>
+      <c r="H416" s="1">
+        <v>0</v>
+      </c>
+      <c r="I416" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A417" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="B417" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="C417" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D417" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="E417" s="1">
+        <v>25</v>
+      </c>
+      <c r="F417" s="1">
+        <v>75</v>
+      </c>
+      <c r="G417" s="1">
+        <v>0</v>
+      </c>
+      <c r="H417" s="1">
+        <v>0</v>
+      </c>
+      <c r="I417" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A418" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="B418" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="C418" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D418" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="E418" s="1">
+        <v>1</v>
+      </c>
+      <c r="F418" s="1">
+        <v>1</v>
+      </c>
+      <c r="G418" s="1">
+        <v>0</v>
+      </c>
+      <c r="H418" s="1">
+        <v>0</v>
+      </c>
+      <c r="I418" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A419" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="B419" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="C419" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D419" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="E419" s="1">
+        <v>1</v>
+      </c>
+      <c r="F419" s="1">
+        <v>1</v>
+      </c>
+      <c r="G419" s="1">
+        <v>0</v>
+      </c>
+      <c r="H419" s="1">
+        <v>0</v>
+      </c>
+      <c r="I419" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A420" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="B420" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="C420" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D420" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="E420" s="1">
+        <v>1</v>
+      </c>
+      <c r="F420" s="1">
+        <v>1</v>
+      </c>
+      <c r="G420" s="1">
+        <v>0</v>
+      </c>
+      <c r="H420" s="1">
+        <v>0</v>
+      </c>
+      <c r="I420" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A421" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B421" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C421" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D421" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E421" s="1">
+        <v>2</v>
+      </c>
+      <c r="F421" s="1">
+        <v>6</v>
+      </c>
+      <c r="G421" s="1">
+        <v>0</v>
+      </c>
+      <c r="H421" s="1">
+        <v>0</v>
+      </c>
+      <c r="I421" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A422" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B422" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C422" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D422" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E422" s="1">
+        <v>5</v>
+      </c>
+      <c r="F422" s="1">
+        <v>20</v>
+      </c>
+      <c r="G422" s="1">
+        <v>0</v>
+      </c>
+      <c r="H422" s="1">
+        <v>0</v>
+      </c>
+      <c r="I422" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A423" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B423" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C423" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D423" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E423" s="1">
+        <v>1</v>
+      </c>
+      <c r="F423" s="1">
+        <v>1</v>
+      </c>
+      <c r="G423" s="1">
+        <v>0</v>
+      </c>
+      <c r="H423" s="1">
+        <v>0</v>
+      </c>
+      <c r="I423" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A424" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B424" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C424" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D424" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E424" s="1">
+        <v>10</v>
+      </c>
+      <c r="F424" s="1">
+        <v>25</v>
+      </c>
+      <c r="G424" s="1">
+        <v>0</v>
+      </c>
+      <c r="H424" s="1">
+        <v>0</v>
+      </c>
+      <c r="I424" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A425" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B425" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C425" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D425" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E425" s="1">
+        <v>1</v>
+      </c>
+      <c r="F425" s="1">
+        <v>1</v>
+      </c>
+      <c r="G425" s="1">
+        <v>0</v>
+      </c>
+      <c r="H425" s="1">
+        <v>0</v>
+      </c>
+      <c r="I425" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A426" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B426" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C426" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D426" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E426" s="1">
+        <v>1</v>
+      </c>
+      <c r="F426" s="1">
+        <v>1</v>
+      </c>
+      <c r="G426" s="1">
+        <v>0</v>
+      </c>
+      <c r="H426" s="1">
+        <v>0</v>
+      </c>
+      <c r="I426" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A427" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B427" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C427" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D427" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E427" s="1">
+        <v>5</v>
+      </c>
+      <c r="F427" s="1">
+        <v>15</v>
+      </c>
+      <c r="G427" s="1">
+        <v>0</v>
+      </c>
+      <c r="H427" s="1">
+        <v>0</v>
+      </c>
+      <c r="I427" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A428" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B428" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C428" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D428" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E428" s="1">
+        <v>1</v>
+      </c>
+      <c r="F428" s="1">
+        <v>1</v>
+      </c>
+      <c r="G428" s="1">
+        <v>0</v>
+      </c>
+      <c r="H428" s="1">
+        <v>0</v>
+      </c>
+      <c r="I428" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A429" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B429" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C429" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D429" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E429" s="1">
+        <v>10</v>
+      </c>
+      <c r="F429" s="1">
+        <v>25</v>
+      </c>
+      <c r="G429" s="1">
+        <v>0</v>
+      </c>
+      <c r="H429" s="1">
+        <v>0</v>
+      </c>
+      <c r="I429" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A430" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B430" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C430" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D430" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E430" s="1">
+        <v>1</v>
+      </c>
+      <c r="F430" s="1">
+        <v>1</v>
+      </c>
+      <c r="G430" s="1">
+        <v>0</v>
+      </c>
+      <c r="H430" s="1">
+        <v>0</v>
+      </c>
+      <c r="I430" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A431" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B431" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C431" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D431" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E431" s="1">
+        <v>100</v>
+      </c>
+      <c r="F431" s="1">
+        <v>300</v>
+      </c>
+      <c r="G431" s="1">
+        <v>0</v>
+      </c>
+      <c r="H431" s="1">
+        <v>0</v>
+      </c>
+      <c r="I431" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A432" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B432" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C432" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D432" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E432" s="1">
+        <v>100</v>
+      </c>
+      <c r="F432" s="1">
+        <v>200</v>
+      </c>
+      <c r="G432" s="1">
+        <v>0</v>
+      </c>
+      <c r="H432" s="1">
+        <v>0</v>
+      </c>
+      <c r="I432" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A433" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B433" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C433" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D433" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E433" s="1">
+        <v>1</v>
+      </c>
+      <c r="F433" s="1">
+        <v>1</v>
+      </c>
+      <c r="G433" s="1">
+        <v>0</v>
+      </c>
+      <c r="H433" s="1">
+        <v>0</v>
+      </c>
+      <c r="I433" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A434" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B434" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C434" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D434" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E434" s="1">
+        <v>1</v>
+      </c>
+      <c r="F434" s="1">
+        <v>1</v>
+      </c>
+      <c r="G434" s="1">
+        <v>0</v>
+      </c>
+      <c r="H434" s="1">
+        <v>0</v>
+      </c>
+      <c r="I434" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A435" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B435" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C435" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D435" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E435" s="1">
+        <v>1</v>
+      </c>
+      <c r="F435" s="1">
+        <v>1</v>
+      </c>
+      <c r="G435" s="1">
+        <v>0</v>
+      </c>
+      <c r="H435" s="1">
+        <v>0</v>
+      </c>
+      <c r="I435" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A436" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B436" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C436" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D436" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E436" s="1">
+        <v>50</v>
+      </c>
+      <c r="F436" s="1">
+        <v>100</v>
+      </c>
+      <c r="G436" s="1">
+        <v>0</v>
+      </c>
+      <c r="H436" s="1">
+        <v>0</v>
+      </c>
+      <c r="I436" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A437" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B437" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C437" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D437" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E437" s="1">
+        <v>5</v>
+      </c>
+      <c r="F437" s="1">
+        <v>10</v>
+      </c>
+      <c r="G437" s="1">
+        <v>0</v>
+      </c>
+      <c r="H437" s="1">
+        <v>0</v>
+      </c>
+      <c r="I437" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A438" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B438" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C438" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D438" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E438" s="1">
+        <v>1</v>
+      </c>
+      <c r="F438" s="1">
+        <v>1</v>
+      </c>
+      <c r="G438" s="1">
+        <v>0</v>
+      </c>
+      <c r="H438" s="1">
+        <v>0</v>
+      </c>
+      <c r="I438" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A439" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B439" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C439" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D439" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E439" s="1">
+        <v>1</v>
+      </c>
+      <c r="F439" s="1">
+        <v>1</v>
+      </c>
+      <c r="G439" s="1">
+        <v>0</v>
+      </c>
+      <c r="H439" s="1">
+        <v>0</v>
+      </c>
+      <c r="I439" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A440" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B440" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C440" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D440" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E440" s="1">
+        <v>1</v>
+      </c>
+      <c r="F440" s="1">
+        <v>1</v>
+      </c>
+      <c r="G440" s="1">
+        <v>0</v>
+      </c>
+      <c r="H440" s="1">
+        <v>0</v>
+      </c>
+      <c r="I440" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A441" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B441" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C441" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D441" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E441" s="1">
+        <v>25</v>
+      </c>
+      <c r="F441" s="1">
+        <v>75</v>
+      </c>
+      <c r="G441" s="1">
+        <v>0</v>
+      </c>
+      <c r="H441" s="1">
+        <v>0</v>
+      </c>
+      <c r="I441" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A442" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B442" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C442" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D442" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E442" s="1">
+        <v>5</v>
+      </c>
+      <c r="F442" s="1">
+        <v>10</v>
+      </c>
+      <c r="G442" s="1">
+        <v>0</v>
+      </c>
+      <c r="H442" s="1">
+        <v>0</v>
+      </c>
+      <c r="I442" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A443" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B443" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C443" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D443" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E443" s="1">
+        <v>5</v>
+      </c>
+      <c r="F443" s="1">
+        <v>25</v>
+      </c>
+      <c r="G443" s="1">
+        <v>0</v>
+      </c>
+      <c r="H443" s="1">
+        <v>0</v>
+      </c>
+      <c r="I443" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A444" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B444" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C444" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D444" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E444" s="1">
+        <v>1</v>
+      </c>
+      <c r="F444" s="1">
+        <v>1</v>
+      </c>
+      <c r="G444" s="1">
+        <v>0</v>
+      </c>
+      <c r="H444" s="1">
+        <v>0</v>
+      </c>
+      <c r="I444" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A445" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B445" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C445" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D445" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E445" s="1">
+        <v>15</v>
+      </c>
+      <c r="F445" s="1">
+        <v>30</v>
+      </c>
+      <c r="G445" s="1">
+        <v>0</v>
+      </c>
+      <c r="H445" s="1">
+        <v>0</v>
+      </c>
+      <c r="I445" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:V395" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B147:B167">
-    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B191">
-    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B195">
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B362">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B395">
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B374">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  <conditionalFormatting sqref="A1:A395 A446:A1048576">
+    <cfRule type="duplicateValues" dxfId="7" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D374">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D378">
+    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D382">
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D396">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B378">
+  <conditionalFormatting sqref="D397:D445">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B382">
+  <conditionalFormatting sqref="A397:A445">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D382">
+  <conditionalFormatting sqref="B397:B445">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/configs/Affix.xlsx
+++ b/configs/Affix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9581E7F8-C680-4920-BB16-EF916E5B0E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F78868D-7D27-49D6-B8FA-41C2EC980416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21620" yWindow="0" windowWidth="16870" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29050,29 +29050,29 @@
   <conditionalFormatting sqref="A485:A1048576 A1:A178 A180:A434">
     <cfRule type="duplicateValues" dxfId="8" priority="45"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B177">
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B192">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D179">
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D413">
-    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D417">
-    <cfRule type="duplicateValues" dxfId="4" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D421">
-    <cfRule type="duplicateValues" dxfId="3" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D435">
-    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D436:D484">
-    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B177">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/configs/Affix.xlsx
+++ b/configs/Affix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86238AB3-1E47-45E6-A600-EBEAAAA9D87B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E67A8F-77D0-4223-ABB6-A41943BA64A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$V$492</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$V$493</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2935" uniqueCount="1076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="1079">
   <si>
     <t>id</t>
   </si>
@@ -3304,6 +3304,15 @@
   </si>
   <si>
     <t>spis</t>
+  </si>
+  <si>
+    <t>skhwoh1</t>
+  </si>
+  <si>
+    <t>skhwoh</t>
+  </si>
+  <si>
+    <t>hwoh_lvl</t>
   </si>
 </sst>
 </file>
@@ -3395,7 +3404,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3822,7 +3841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X492"/>
+  <dimension ref="A1:X493"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="10.90625" style="1" customWidth="1"/>
@@ -15486,7 +15505,7 @@
         <v>70</v>
       </c>
       <c r="S222" s="1" t="str">
-        <f t="shared" ref="S222:U391" si="32">_xlfn.LET(_xlpm.a,($E222+S$3*$G222)*(1+S$2),_xlpm.b,($F222+S$3*$H222)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
+        <f t="shared" ref="S222:U392" si="32">_xlfn.LET(_xlpm.a,($E222+S$3*$G222)*(1+S$2),_xlpm.b,($F222+S$3*$H222)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
         <v>1-1</v>
       </c>
       <c r="T222" s="1" t="str">
@@ -21252,7 +21271,7 @@
         <v>6-18</v>
       </c>
       <c r="V318" s="1">
-        <f t="shared" ref="V318:V381" si="37">_xlfn.LET(_xlpm.a,($E318+U$3*$G318)*(1+U$2),_xlpm.b,($F318+U$3*$H318)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <f t="shared" ref="V318:V382" si="37">_xlfn.LET(_xlpm.a,($E318+U$3*$G318)*(1+U$2),_xlpm.b,($F318+U$3*$H318)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
         <v>12</v>
       </c>
     </row>
@@ -23147,17 +23166,17 @@
       </c>
     </row>
     <row r="354" spans="1:22">
-      <c r="A354" s="6" t="s">
-        <v>1024</v>
+      <c r="A354" s="1" t="s">
+        <v>1076</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>489</v>
+        <v>1076</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>200</v>
+        <v>1077</v>
       </c>
       <c r="E354" s="1">
         <v>1</v>
@@ -23169,55 +23188,33 @@
         <v>0</v>
       </c>
       <c r="H354" s="1">
-        <v>0</v>
-      </c>
-      <c r="I354" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N354" s="1" t="s">
-        <v>770</v>
+        <v>1078</v>
       </c>
       <c r="O354" s="1" t="s">
-        <v>770</v>
+        <v>1078</v>
       </c>
       <c r="P354" s="1">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="Q354" s="1">
-        <v>1</v>
-      </c>
-      <c r="R354" s="1">
-        <v>70</v>
-      </c>
-      <c r="S354" s="1" t="str">
-        <f t="shared" ref="S354:U369" si="39">_xlfn.LET(_xlpm.a,($E354+S$3*$G354)*(1+S$2),_xlpm.b,($F354+S$3*$H354)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
-        <v>1-1</v>
-      </c>
-      <c r="T354" s="1" t="str">
-        <f t="shared" si="39"/>
-        <v>1-1</v>
-      </c>
-      <c r="U354" s="1" t="str">
-        <f t="shared" si="39"/>
-        <v>6-6</v>
-      </c>
-      <c r="V354" s="1">
-        <f t="shared" si="37"/>
-        <v>6</v>
+        <v>32</v>
       </c>
     </row>
     <row r="355" spans="1:22">
       <c r="A355" s="6" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E355" s="1">
         <v>1</v>
@@ -23235,22 +23232,22 @@
         <v>0</v>
       </c>
       <c r="N355" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="O355" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="P355" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q355" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R355" s="1">
         <v>70</v>
       </c>
       <c r="S355" s="1" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" ref="S355:U370" si="39">_xlfn.LET(_xlpm.a,($E355+S$3*$G355)*(1+S$2),_xlpm.b,($F355+S$3*$H355)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
         <v>1-1</v>
       </c>
       <c r="T355" s="1" t="str">
@@ -23268,16 +23265,16 @@
     </row>
     <row r="356" spans="1:22">
       <c r="A356" s="6" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E356" s="1">
         <v>1</v>
@@ -23295,16 +23292,16 @@
         <v>0</v>
       </c>
       <c r="N356" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="O356" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="P356" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q356" s="1">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R356" s="1">
         <v>70</v>
@@ -23328,16 +23325,16 @@
     </row>
     <row r="357" spans="1:22">
       <c r="A357" s="6" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E357" s="1">
         <v>1</v>
@@ -23355,16 +23352,16 @@
         <v>0</v>
       </c>
       <c r="N357" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="O357" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="P357" s="1">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Q357" s="1">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="R357" s="1">
         <v>70</v>
@@ -23388,16 +23385,16 @@
     </row>
     <row r="358" spans="1:22">
       <c r="A358" s="6" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E358" s="1">
         <v>1</v>
@@ -23415,16 +23412,16 @@
         <v>0</v>
       </c>
       <c r="N358" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="O358" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="P358" s="1">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="Q358" s="1">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="R358" s="1">
         <v>70</v>
@@ -23448,16 +23445,16 @@
     </row>
     <row r="359" spans="1:22">
       <c r="A359" s="6" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E359" s="1">
         <v>1</v>
@@ -23475,16 +23472,16 @@
         <v>0</v>
       </c>
       <c r="N359" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="O359" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="P359" s="1">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="Q359" s="1">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R359" s="1">
         <v>70</v>
@@ -23508,16 +23505,16 @@
     </row>
     <row r="360" spans="1:22">
       <c r="A360" s="6" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E360" s="1">
         <v>1</v>
@@ -23535,16 +23532,16 @@
         <v>0</v>
       </c>
       <c r="N360" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="O360" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="P360" s="1">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q360" s="1">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="R360" s="1">
         <v>70</v>
@@ -23568,16 +23565,16 @@
     </row>
     <row r="361" spans="1:22">
       <c r="A361" s="6" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E361" s="1">
         <v>1</v>
@@ -23595,16 +23592,16 @@
         <v>0</v>
       </c>
       <c r="N361" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="O361" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="P361" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q361" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R361" s="1">
         <v>70</v>
@@ -23628,16 +23625,16 @@
     </row>
     <row r="362" spans="1:22">
       <c r="A362" s="6" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E362" s="1">
         <v>1</v>
@@ -23655,16 +23652,16 @@
         <v>0</v>
       </c>
       <c r="N362" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="O362" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="P362" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q362" s="1">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R362" s="1">
         <v>70</v>
@@ -23688,16 +23685,16 @@
     </row>
     <row r="363" spans="1:22">
       <c r="A363" s="6" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E363" s="1">
         <v>1</v>
@@ -23715,16 +23712,16 @@
         <v>0</v>
       </c>
       <c r="N363" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O363" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="P363" s="1">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Q363" s="1">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="R363" s="1">
         <v>70</v>
@@ -23748,16 +23745,16 @@
     </row>
     <row r="364" spans="1:22">
       <c r="A364" s="6" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E364" s="1">
         <v>1</v>
@@ -23775,16 +23772,16 @@
         <v>0</v>
       </c>
       <c r="N364" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="O364" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="P364" s="1">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="Q364" s="1">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="R364" s="1">
         <v>70</v>
@@ -23808,16 +23805,16 @@
     </row>
     <row r="365" spans="1:22">
       <c r="A365" s="6" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E365" s="1">
         <v>1</v>
@@ -23835,16 +23832,16 @@
         <v>0</v>
       </c>
       <c r="N365" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="O365" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="P365" s="1">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="Q365" s="1">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R365" s="1">
         <v>70</v>
@@ -23868,16 +23865,16 @@
     </row>
     <row r="366" spans="1:22">
       <c r="A366" s="6" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E366" s="1">
         <v>1</v>
@@ -23895,16 +23892,16 @@
         <v>0</v>
       </c>
       <c r="N366" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="O366" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="P366" s="1">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q366" s="1">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="R366" s="1">
         <v>70</v>
@@ -23928,16 +23925,16 @@
     </row>
     <row r="367" spans="1:22">
       <c r="A367" s="6" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E367" s="1">
         <v>1</v>
@@ -23955,16 +23952,16 @@
         <v>0</v>
       </c>
       <c r="N367" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="O367" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="P367" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q367" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R367" s="1">
         <v>70</v>
@@ -23988,16 +23985,16 @@
     </row>
     <row r="368" spans="1:22">
       <c r="A368" s="6" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E368" s="1">
         <v>1</v>
@@ -24015,16 +24012,16 @@
         <v>0</v>
       </c>
       <c r="N368" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="O368" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="P368" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q368" s="1">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R368" s="1">
         <v>70</v>
@@ -24048,16 +24045,16 @@
     </row>
     <row r="369" spans="1:22">
       <c r="A369" s="6" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E369" s="1">
         <v>1</v>
@@ -24075,16 +24072,16 @@
         <v>0</v>
       </c>
       <c r="N369" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="O369" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="P369" s="1">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Q369" s="1">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="R369" s="1">
         <v>70</v>
@@ -24108,16 +24105,16 @@
     </row>
     <row r="370" spans="1:22">
       <c r="A370" s="6" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E370" s="1">
         <v>1</v>
@@ -24135,30 +24132,30 @@
         <v>0</v>
       </c>
       <c r="N370" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="O370" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="P370" s="1">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="Q370" s="1">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="R370" s="1">
         <v>70</v>
       </c>
       <c r="S370" s="1" t="str">
-        <f t="shared" ref="S370:U389" si="40">_xlfn.LET(_xlpm.a,($E370+S$3*$G370)*(1+S$2),_xlpm.b,($F370+S$3*$H370)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
+        <f t="shared" si="39"/>
         <v>1-1</v>
       </c>
       <c r="T370" s="1" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>1-1</v>
       </c>
       <c r="U370" s="1" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>6-6</v>
       </c>
       <c r="V370" s="1">
@@ -24168,16 +24165,16 @@
     </row>
     <row r="371" spans="1:22">
       <c r="A371" s="6" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E371" s="1">
         <v>1</v>
@@ -24195,22 +24192,22 @@
         <v>0</v>
       </c>
       <c r="N371" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="O371" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="P371" s="1">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="Q371" s="1">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R371" s="1">
         <v>70</v>
       </c>
       <c r="S371" s="1" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" ref="S371:U390" si="40">_xlfn.LET(_xlpm.a,($E371+S$3*$G371)*(1+S$2),_xlpm.b,($F371+S$3*$H371)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
         <v>1-1</v>
       </c>
       <c r="T371" s="1" t="str">
@@ -24228,16 +24225,16 @@
     </row>
     <row r="372" spans="1:22">
       <c r="A372" s="6" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E372" s="1">
         <v>1</v>
@@ -24255,16 +24252,16 @@
         <v>0</v>
       </c>
       <c r="N372" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="O372" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="P372" s="1">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q372" s="1">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="R372" s="1">
         <v>70</v>
@@ -24288,16 +24285,16 @@
     </row>
     <row r="373" spans="1:22">
       <c r="A373" s="6" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E373" s="1">
         <v>1</v>
@@ -24315,16 +24312,16 @@
         <v>0</v>
       </c>
       <c r="N373" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="O373" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="P373" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q373" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R373" s="1">
         <v>70</v>
@@ -24348,16 +24345,16 @@
     </row>
     <row r="374" spans="1:22">
       <c r="A374" s="6" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D374" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E374" s="1">
         <v>1</v>
@@ -24375,16 +24372,16 @@
         <v>0</v>
       </c>
       <c r="N374" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="O374" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="P374" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q374" s="1">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R374" s="1">
         <v>70</v>
@@ -24408,16 +24405,16 @@
     </row>
     <row r="375" spans="1:22">
       <c r="A375" s="6" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E375" s="1">
         <v>1</v>
@@ -24435,16 +24432,16 @@
         <v>0</v>
       </c>
       <c r="N375" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="O375" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="P375" s="1">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Q375" s="1">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="R375" s="1">
         <v>70</v>
@@ -24468,16 +24465,16 @@
     </row>
     <row r="376" spans="1:22">
       <c r="A376" s="6" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D376" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E376" s="1">
         <v>1</v>
@@ -24495,16 +24492,16 @@
         <v>0</v>
       </c>
       <c r="N376" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="O376" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="P376" s="1">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="Q376" s="1">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="R376" s="1">
         <v>70</v>
@@ -24528,16 +24525,16 @@
     </row>
     <row r="377" spans="1:22">
       <c r="A377" s="6" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D377" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E377" s="1">
         <v>1</v>
@@ -24555,16 +24552,16 @@
         <v>0</v>
       </c>
       <c r="N377" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="O377" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="P377" s="1">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="Q377" s="1">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R377" s="1">
         <v>70</v>
@@ -24588,16 +24585,16 @@
     </row>
     <row r="378" spans="1:22">
       <c r="A378" s="6" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D378" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E378" s="1">
         <v>1</v>
@@ -24615,16 +24612,16 @@
         <v>0</v>
       </c>
       <c r="N378" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="O378" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="P378" s="1">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q378" s="1">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="R378" s="1">
         <v>70</v>
@@ -24648,16 +24645,16 @@
     </row>
     <row r="379" spans="1:22">
       <c r="A379" s="6" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E379" s="1">
         <v>1</v>
@@ -24675,16 +24672,16 @@
         <v>0</v>
       </c>
       <c r="N379" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="O379" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="P379" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q379" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R379" s="1">
         <v>70</v>
@@ -24708,16 +24705,16 @@
     </row>
     <row r="380" spans="1:22">
       <c r="A380" s="6" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E380" s="1">
         <v>1</v>
@@ -24735,16 +24732,16 @@
         <v>0</v>
       </c>
       <c r="N380" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="O380" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="P380" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q380" s="1">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R380" s="1">
         <v>70</v>
@@ -24768,16 +24765,16 @@
     </row>
     <row r="381" spans="1:22">
       <c r="A381" s="6" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E381" s="1">
         <v>1</v>
@@ -24795,16 +24792,16 @@
         <v>0</v>
       </c>
       <c r="N381" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="O381" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="P381" s="1">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Q381" s="1">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="R381" s="1">
         <v>70</v>
@@ -24828,16 +24825,16 @@
     </row>
     <row r="382" spans="1:22">
       <c r="A382" s="6" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="E382" s="1">
         <v>1</v>
@@ -24855,16 +24852,16 @@
         <v>0</v>
       </c>
       <c r="N382" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="O382" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="P382" s="1">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="Q382" s="1">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="R382" s="1">
         <v>70</v>
@@ -24882,22 +24879,22 @@
         <v>6-6</v>
       </c>
       <c r="V382" s="1">
-        <f t="shared" ref="V382:V389" si="41">_xlfn.LET(_xlpm.a,($E382+U$3*$G382)*(1+U$2),_xlpm.b,($F382+U$3*$H382)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <f t="shared" si="37"/>
         <v>6</v>
       </c>
     </row>
     <row r="383" spans="1:22">
       <c r="A383" s="6" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E383" s="1">
         <v>1</v>
@@ -24915,16 +24912,16 @@
         <v>0</v>
       </c>
       <c r="N383" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="O383" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="P383" s="1">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="Q383" s="1">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R383" s="1">
         <v>70</v>
@@ -24942,22 +24939,22 @@
         <v>6-6</v>
       </c>
       <c r="V383" s="1">
-        <f t="shared" si="41"/>
+        <f t="shared" ref="V383:V390" si="41">_xlfn.LET(_xlpm.a,($E383+U$3*$G383)*(1+U$2),_xlpm.b,($F383+U$3*$H383)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
         <v>6</v>
       </c>
     </row>
     <row r="384" spans="1:22">
       <c r="A384" s="6" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E384" s="1">
         <v>1</v>
@@ -24975,16 +24972,16 @@
         <v>0</v>
       </c>
       <c r="N384" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="O384" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="P384" s="1">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q384" s="1">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="R384" s="1">
         <v>70</v>
@@ -25008,16 +25005,16 @@
     </row>
     <row r="385" spans="1:22">
       <c r="A385" s="6" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E385" s="1">
         <v>1</v>
@@ -25035,16 +25032,16 @@
         <v>0</v>
       </c>
       <c r="N385" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="O385" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="P385" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q385" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R385" s="1">
         <v>70</v>
@@ -25068,16 +25065,16 @@
     </row>
     <row r="386" spans="1:22">
       <c r="A386" s="6" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E386" s="1">
         <v>1</v>
@@ -25095,16 +25092,16 @@
         <v>0</v>
       </c>
       <c r="N386" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="O386" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="P386" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q386" s="1">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R386" s="1">
         <v>70</v>
@@ -25128,16 +25125,16 @@
     </row>
     <row r="387" spans="1:22">
       <c r="A387" s="6" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E387" s="1">
         <v>1</v>
@@ -25155,16 +25152,16 @@
         <v>0</v>
       </c>
       <c r="N387" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="O387" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="P387" s="1">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Q387" s="1">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="R387" s="1">
         <v>70</v>
@@ -25188,16 +25185,16 @@
     </row>
     <row r="388" spans="1:22">
       <c r="A388" s="6" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E388" s="1">
         <v>1</v>
@@ -25215,16 +25212,16 @@
         <v>0</v>
       </c>
       <c r="N388" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="O388" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="P388" s="1">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="Q388" s="1">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="R388" s="1">
         <v>70</v>
@@ -25248,16 +25245,16 @@
     </row>
     <row r="389" spans="1:22">
       <c r="A389" s="6" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D389" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E389" s="1">
         <v>1</v>
@@ -25275,16 +25272,16 @@
         <v>0</v>
       </c>
       <c r="N389" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="O389" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="P389" s="1">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="Q389" s="1">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R389" s="1">
         <v>70</v>
@@ -25307,17 +25304,17 @@
       </c>
     </row>
     <row r="390" spans="1:22">
-      <c r="A390" s="1" t="s">
-        <v>103</v>
+      <c r="A390" s="6" t="s">
+        <v>1059</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>389</v>
+        <v>243</v>
       </c>
       <c r="E390" s="1">
         <v>1</v>
@@ -25329,49 +25326,49 @@
         <v>0</v>
       </c>
       <c r="H390" s="1">
-        <v>2</v>
-      </c>
-      <c r="K390" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="L390" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="M390" s="1" t="s">
-        <v>941</v>
+        <v>0</v>
+      </c>
+      <c r="I390" s="1">
+        <v>0</v>
+      </c>
+      <c r="N390" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="O390" s="1" t="s">
+        <v>805</v>
       </c>
       <c r="P390" s="1">
+        <v>31</v>
+      </c>
+      <c r="Q390" s="1">
+        <v>35</v>
+      </c>
+      <c r="R390" s="1">
+        <v>70</v>
+      </c>
+      <c r="S390" s="1" t="str">
+        <f t="shared" si="40"/>
+        <v>1-1</v>
+      </c>
+      <c r="T390" s="1" t="str">
+        <f t="shared" si="40"/>
+        <v>1-1</v>
+      </c>
+      <c r="U390" s="1" t="str">
+        <f t="shared" si="40"/>
+        <v>6-6</v>
+      </c>
+      <c r="V390" s="1">
+        <f t="shared" si="41"/>
         <v>6</v>
-      </c>
-      <c r="Q390" s="1">
-        <v>7</v>
-      </c>
-      <c r="R390" s="1">
-        <v>100</v>
-      </c>
-      <c r="S390" s="1" t="str">
-        <f t="shared" si="32"/>
-        <v>1-1</v>
-      </c>
-      <c r="T390" s="1" t="str">
-        <f t="shared" si="32"/>
-        <v>1-9</v>
-      </c>
-      <c r="U390" s="1" t="str">
-        <f t="shared" si="32"/>
-        <v>6-54</v>
-      </c>
-      <c r="V390" s="1">
-        <f t="shared" ref="V390" si="42">_xlfn.LET(_xlpm.a,($E390+U$3*$G390)*(1+U$2),_xlpm.b,($F390+U$3*$H390)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
-        <v>30</v>
       </c>
     </row>
     <row r="391" spans="1:22">
       <c r="A391" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>39</v>
@@ -25392,7 +25389,7 @@
         <v>2</v>
       </c>
       <c r="K391" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L391" s="1" t="s">
         <v>546</v>
@@ -25401,10 +25398,10 @@
         <v>941</v>
       </c>
       <c r="P391" s="1">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="Q391" s="1">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="R391" s="1">
         <v>100</v>
@@ -25422,16 +25419,16 @@
         <v>6-54</v>
       </c>
       <c r="V391" s="1">
-        <f t="shared" ref="V391:V398" si="43">_xlfn.LET(_xlpm.a,($E391+U$3*$G391)*(1+U$2),_xlpm.b,($F391+U$3*$H391)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <f t="shared" ref="V391" si="42">_xlfn.LET(_xlpm.a,($E391+U$3*$G391)*(1+U$2),_xlpm.b,($F391+U$3*$H391)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
         <v>30</v>
       </c>
     </row>
     <row r="392" spans="1:22">
       <c r="A392" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>39</v>
@@ -25452,7 +25449,7 @@
         <v>2</v>
       </c>
       <c r="K392" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L392" s="1" t="s">
         <v>546</v>
@@ -25461,37 +25458,37 @@
         <v>941</v>
       </c>
       <c r="P392" s="1">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="Q392" s="1">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="R392" s="1">
         <v>100</v>
       </c>
       <c r="S392" s="1" t="str">
-        <f t="shared" ref="S392:U413" si="44">_xlfn.LET(_xlpm.a,($E392+S$3*$G392)*(1+S$2),_xlpm.b,($F392+S$3*$H392)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
+        <f t="shared" si="32"/>
         <v>1-1</v>
       </c>
       <c r="T392" s="1" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="32"/>
         <v>1-9</v>
       </c>
       <c r="U392" s="1" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="32"/>
         <v>6-54</v>
       </c>
       <c r="V392" s="1">
-        <f t="shared" si="43"/>
+        <f t="shared" ref="V392:V399" si="43">_xlfn.LET(_xlpm.a,($E392+U$3*$G392)*(1+U$2),_xlpm.b,($F392+U$3*$H392)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
         <v>30</v>
       </c>
     </row>
     <row r="393" spans="1:22">
       <c r="A393" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>39</v>
@@ -25512,7 +25509,7 @@
         <v>2</v>
       </c>
       <c r="K393" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L393" s="1" t="s">
         <v>546</v>
@@ -25521,16 +25518,16 @@
         <v>941</v>
       </c>
       <c r="P393" s="1">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="Q393" s="1">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="R393" s="1">
         <v>100</v>
       </c>
       <c r="S393" s="1" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" ref="S393:U414" si="44">_xlfn.LET(_xlpm.a,($E393+S$3*$G393)*(1+S$2),_xlpm.b,($F393+S$3*$H393)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
         <v>1-1</v>
       </c>
       <c r="T393" s="1" t="str">
@@ -25548,16 +25545,16 @@
     </row>
     <row r="394" spans="1:22">
       <c r="A394" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D394" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E394" s="1">
         <v>1</v>
@@ -25572,19 +25569,19 @@
         <v>2</v>
       </c>
       <c r="K394" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L394" s="1" t="s">
         <v>546</v>
       </c>
       <c r="M394" s="1" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="P394" s="1">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="Q394" s="1">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="R394" s="1">
         <v>100</v>
@@ -25607,11 +25604,11 @@
       </c>
     </row>
     <row r="395" spans="1:22">
-      <c r="A395" t="s">
-        <v>844</v>
+      <c r="A395" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>39</v>
@@ -25632,7 +25629,7 @@
         <v>2</v>
       </c>
       <c r="K395" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L395" s="1" t="s">
         <v>546</v>
@@ -25641,10 +25638,10 @@
         <v>942</v>
       </c>
       <c r="P395" s="1">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="Q395" s="1">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="R395" s="1">
         <v>100</v>
@@ -25668,10 +25665,10 @@
     </row>
     <row r="396" spans="1:22">
       <c r="A396" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>39</v>
@@ -25692,7 +25689,7 @@
         <v>2</v>
       </c>
       <c r="K396" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L396" s="1" t="s">
         <v>546</v>
@@ -25701,10 +25698,10 @@
         <v>942</v>
       </c>
       <c r="P396" s="1">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="Q396" s="1">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="R396" s="1">
         <v>100</v>
@@ -25727,11 +25724,11 @@
       </c>
     </row>
     <row r="397" spans="1:22">
-      <c r="A397" s="1" t="s">
-        <v>108</v>
+      <c r="A397" t="s">
+        <v>845</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>39</v>
@@ -25752,7 +25749,7 @@
         <v>2</v>
       </c>
       <c r="K397" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L397" s="1" t="s">
         <v>546</v>
@@ -25761,10 +25758,10 @@
         <v>942</v>
       </c>
       <c r="P397" s="1">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="Q397" s="1">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="R397" s="1">
         <v>100</v>
@@ -25788,16 +25785,16 @@
     </row>
     <row r="398" spans="1:22">
       <c r="A398" s="1" t="s">
-        <v>549</v>
+        <v>108</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>555</v>
+        <v>532</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D398" s="1" t="s">
-        <v>548</v>
+        <v>390</v>
       </c>
       <c r="E398" s="1">
         <v>1</v>
@@ -25812,19 +25809,19 @@
         <v>2</v>
       </c>
       <c r="K398" s="1" t="s">
-        <v>550</v>
+        <v>121</v>
       </c>
       <c r="L398" s="1" t="s">
         <v>546</v>
       </c>
       <c r="M398" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="P398" s="1">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="Q398" s="1">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="R398" s="1">
         <v>100</v>
@@ -25848,10 +25845,10 @@
     </row>
     <row r="399" spans="1:22">
       <c r="A399" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>39</v>
@@ -25872,7 +25869,7 @@
         <v>2</v>
       </c>
       <c r="K399" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="L399" s="1" t="s">
         <v>546</v>
@@ -25881,10 +25878,10 @@
         <v>943</v>
       </c>
       <c r="P399" s="1">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="Q399" s="1">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="R399" s="1">
         <v>100</v>
@@ -25902,16 +25899,16 @@
         <v>6-54</v>
       </c>
       <c r="V399" s="1">
-        <f t="shared" ref="V399" si="45">_xlfn.LET(_xlpm.a,($E399+U$3*$G399)*(1+U$2),_xlpm.b,($F399+U$3*$H399)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <f t="shared" si="43"/>
         <v>30</v>
       </c>
     </row>
     <row r="400" spans="1:22">
       <c r="A400" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>39</v>
@@ -25932,7 +25929,7 @@
         <v>2</v>
       </c>
       <c r="K400" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="L400" s="1" t="s">
         <v>546</v>
@@ -25941,10 +25938,10 @@
         <v>943</v>
       </c>
       <c r="P400" s="1">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="Q400" s="1">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="R400" s="1">
         <v>100</v>
@@ -25962,16 +25959,16 @@
         <v>6-54</v>
       </c>
       <c r="V400" s="1">
-        <f t="shared" ref="V400" si="46">_xlfn.LET(_xlpm.a,($E400+U$3*$G400)*(1+U$2),_xlpm.b,($F400+U$3*$H400)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <f t="shared" ref="V400" si="45">_xlfn.LET(_xlpm.a,($E400+U$3*$G400)*(1+U$2),_xlpm.b,($F400+U$3*$H400)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
         <v>30</v>
       </c>
     </row>
     <row r="401" spans="1:22">
       <c r="A401" s="1" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>39</v>
@@ -25992,7 +25989,7 @@
         <v>2</v>
       </c>
       <c r="K401" s="1" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="L401" s="1" t="s">
         <v>546</v>
@@ -26022,70 +26019,82 @@
         <v>6-54</v>
       </c>
       <c r="V401" s="1">
-        <f t="shared" ref="V401" si="47">_xlfn.LET(_xlpm.a,($E401+U$3*$G401)*(1+U$2),_xlpm.b,($F401+U$3*$H401)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <f t="shared" ref="V401" si="46">_xlfn.LET(_xlpm.a,($E401+U$3*$G401)*(1+U$2),_xlpm.b,($F401+U$3*$H401)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
         <v>30</v>
       </c>
     </row>
     <row r="402" spans="1:22">
       <c r="A402" s="1" t="s">
-        <v>113</v>
+        <v>556</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>533</v>
+        <v>557</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D402" s="1" t="s">
-        <v>244</v>
+        <v>548</v>
       </c>
       <c r="E402" s="1">
         <v>1</v>
       </c>
       <c r="F402" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G402" s="1">
         <v>0</v>
       </c>
       <c r="H402" s="1">
-        <v>1.25</v>
+        <v>2</v>
+      </c>
+      <c r="K402" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="L402" s="1" t="s">
+        <v>546</v>
       </c>
       <c r="M402" s="1" t="s">
-        <v>839</v>
+        <v>943</v>
+      </c>
+      <c r="P402" s="1">
+        <v>19</v>
+      </c>
+      <c r="Q402" s="1">
+        <v>21</v>
       </c>
       <c r="R402" s="1">
         <v>100</v>
       </c>
       <c r="S402" s="1" t="str">
         <f t="shared" si="44"/>
-        <v>1-10</v>
+        <v>1-1</v>
       </c>
       <c r="T402" s="1" t="str">
         <f t="shared" si="44"/>
-        <v>1-15</v>
+        <v>1-9</v>
       </c>
       <c r="U402" s="1" t="str">
         <f t="shared" si="44"/>
-        <v>6-90</v>
+        <v>6-54</v>
       </c>
       <c r="V402" s="1">
-        <f t="shared" ref="V402" si="48">_xlfn.LET(_xlpm.a,($E402+U$3*$G402)*(1+U$2),_xlpm.b,($F402+U$3*$H402)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
-        <v>48</v>
+        <f t="shared" ref="V402" si="47">_xlfn.LET(_xlpm.a,($E402+U$3*$G402)*(1+U$2),_xlpm.b,($F402+U$3*$H402)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <v>30</v>
       </c>
     </row>
     <row r="403" spans="1:22">
       <c r="A403" s="1" t="s">
-        <v>269</v>
+        <v>113</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D403" s="1" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="E403" s="1">
         <v>1</v>
@@ -26118,118 +26127,112 @@
         <v>6-90</v>
       </c>
       <c r="V403" s="1">
-        <f t="shared" ref="V403" si="49">_xlfn.LET(_xlpm.a,($E403+U$3*$G403)*(1+U$2),_xlpm.b,($F403+U$3*$H403)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <f t="shared" ref="V403" si="48">_xlfn.LET(_xlpm.a,($E403+U$3*$G403)*(1+U$2),_xlpm.b,($F403+U$3*$H403)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
         <v>48</v>
       </c>
     </row>
     <row r="404" spans="1:22">
       <c r="A404" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D404" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E404" s="1">
         <v>1</v>
       </c>
       <c r="F404" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G404" s="1">
         <v>0</v>
       </c>
       <c r="H404" s="1">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="M404" s="1" t="s">
-        <v>944</v>
+        <v>839</v>
       </c>
       <c r="R404" s="1">
         <v>100</v>
       </c>
       <c r="S404" s="1" t="str">
         <f t="shared" si="44"/>
-        <v>1-1</v>
+        <v>1-10</v>
       </c>
       <c r="T404" s="1" t="str">
         <f t="shared" si="44"/>
-        <v>1-2</v>
+        <v>1-15</v>
       </c>
       <c r="U404" s="1" t="str">
         <f t="shared" si="44"/>
-        <v>6-12</v>
+        <v>6-90</v>
       </c>
       <c r="V404" s="1">
-        <f t="shared" ref="V404" si="50">_xlfn.LET(_xlpm.a,($E404+U$3*$G404)*(1+U$2),_xlpm.b,($F404+U$3*$H404)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
-        <v>9</v>
+        <f t="shared" ref="V404" si="49">_xlfn.LET(_xlpm.a,($E404+U$3*$G404)*(1+U$2),_xlpm.b,($F404+U$3*$H404)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <v>48</v>
       </c>
     </row>
     <row r="405" spans="1:22">
       <c r="A405" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E405" s="1">
         <v>1</v>
       </c>
       <c r="F405" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G405" s="1">
         <v>0</v>
       </c>
       <c r="H405" s="1">
-        <v>1.25</v>
-      </c>
-      <c r="N405" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="O405" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="P405" s="1">
-        <v>28</v>
-      </c>
-      <c r="Q405" s="1">
-        <v>32</v>
+        <v>0.25</v>
+      </c>
+      <c r="M405" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="R405" s="1">
+        <v>100</v>
       </c>
       <c r="S405" s="1" t="str">
         <f t="shared" si="44"/>
-        <v>1-5</v>
+        <v>1-1</v>
       </c>
       <c r="T405" s="1" t="str">
         <f t="shared" si="44"/>
-        <v>1-10</v>
+        <v>1-2</v>
       </c>
       <c r="U405" s="1" t="str">
         <f t="shared" si="44"/>
-        <v>6-60</v>
+        <v>6-12</v>
       </c>
       <c r="V405" s="1">
-        <f t="shared" ref="V405:V407" si="51">_xlfn.LET(_xlpm.a,($E405+U$3*$G405)*(1+U$2),_xlpm.b,($F405+U$3*$H405)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
-        <v>33</v>
+        <f t="shared" ref="V405" si="50">_xlfn.LET(_xlpm.a,($E405+U$3*$G405)*(1+U$2),_xlpm.b,($F405+U$3*$H405)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="406" spans="1:22">
-      <c r="A406" s="6" t="s">
-        <v>949</v>
+      <c r="A406" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>949</v>
+        <v>536</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>39</v>
@@ -26238,19 +26241,16 @@
         <v>273</v>
       </c>
       <c r="E406" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F406" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G406" s="1">
         <v>0</v>
       </c>
       <c r="H406" s="1">
-        <v>0</v>
-      </c>
-      <c r="I406" s="1">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="N406" s="1" t="s">
         <v>273</v>
@@ -26258,197 +26258,200 @@
       <c r="O406" s="1" t="s">
         <v>273</v>
       </c>
+      <c r="P406" s="1">
+        <v>28</v>
+      </c>
+      <c r="Q406" s="1">
+        <v>32</v>
+      </c>
       <c r="S406" s="1" t="str">
         <f t="shared" si="44"/>
-        <v>10-10</v>
+        <v>1-5</v>
       </c>
       <c r="T406" s="1" t="str">
         <f t="shared" si="44"/>
-        <v>10-10</v>
+        <v>1-10</v>
       </c>
       <c r="U406" s="1" t="str">
         <f t="shared" si="44"/>
-        <v>60-60</v>
+        <v>6-60</v>
       </c>
       <c r="V406" s="1">
-        <f t="shared" ref="V406" si="52">_xlfn.LET(_xlpm.a,($E406+U$3*$G406)*(1+U$2),_xlpm.b,($F406+U$3*$H406)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
-        <v>60</v>
+        <f t="shared" ref="V406:V408" si="51">_xlfn.LET(_xlpm.a,($E406+U$3*$G406)*(1+U$2),_xlpm.b,($F406+U$3*$H406)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <v>33</v>
       </c>
     </row>
     <row r="407" spans="1:22">
-      <c r="A407" s="1" t="s">
-        <v>276</v>
+      <c r="A407" s="6" t="s">
+        <v>949</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>537</v>
+        <v>949</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D407" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E407" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F407" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G407" s="1">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="H407" s="1">
-        <v>8.75</v>
-      </c>
-      <c r="M407" s="1" t="s">
-        <v>945</v>
-      </c>
-      <c r="P407" s="1">
-        <v>30</v>
-      </c>
-      <c r="Q407" s="1">
-        <v>34</v>
-      </c>
-      <c r="R407" s="1">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I407" s="1">
+        <v>0</v>
+      </c>
+      <c r="N407" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="O407" s="1" t="s">
+        <v>273</v>
       </c>
       <c r="S407" s="1" t="str">
         <f t="shared" si="44"/>
-        <v>5-15</v>
+        <v>10-10</v>
       </c>
       <c r="T407" s="1" t="str">
         <f t="shared" si="44"/>
-        <v>10-50</v>
+        <v>10-10</v>
       </c>
       <c r="U407" s="1" t="str">
         <f t="shared" si="44"/>
+        <v>60-60</v>
+      </c>
+      <c r="V407" s="1">
+        <f t="shared" ref="V407" si="52">_xlfn.LET(_xlpm.a,($E407+U$3*$G407)*(1+U$2),_xlpm.b,($F407+U$3*$H407)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="408" spans="1:22">
+      <c r="A408" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B408" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C408" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D408" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E408" s="1">
+        <v>5</v>
+      </c>
+      <c r="F408" s="1">
+        <v>15</v>
+      </c>
+      <c r="G408" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="H408" s="1">
+        <v>8.75</v>
+      </c>
+      <c r="M408" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="P408" s="1">
+        <v>30</v>
+      </c>
+      <c r="Q408" s="1">
+        <v>34</v>
+      </c>
+      <c r="R408" s="1">
+        <v>20</v>
+      </c>
+      <c r="S408" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>5-15</v>
+      </c>
+      <c r="T408" s="1" t="str">
+        <f t="shared" si="44"/>
+        <v>10-50</v>
+      </c>
+      <c r="U408" s="1" t="str">
+        <f t="shared" si="44"/>
         <v>60-300</v>
       </c>
-      <c r="V407" s="1">
+      <c r="V408" s="1">
         <f t="shared" si="51"/>
         <v>180</v>
       </c>
     </row>
-    <row r="408" spans="1:22">
-      <c r="A408" s="1" t="s">
+    <row r="409" spans="1:22">
+      <c r="A409" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B408" s="1" t="s">
+      <c r="B409" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="C408" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D408" s="1" t="s">
+      <c r="C409" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D409" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="E408" s="1">
+      <c r="E409" s="1">
         <v>2.5</v>
       </c>
-      <c r="F408" s="1">
+      <c r="F409" s="1">
         <v>5</v>
       </c>
-      <c r="G408" s="1">
+      <c r="G409" s="1">
         <v>0.625</v>
       </c>
-      <c r="H408" s="1">
+      <c r="H409" s="1">
         <v>1.25</v>
       </c>
-      <c r="N408" s="1" t="s">
+      <c r="N409" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="O408" s="1" t="s">
+      <c r="O409" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="P408" s="1">
+      <c r="P409" s="1">
         <v>25</v>
       </c>
-      <c r="Q408" s="1">
+      <c r="Q409" s="1">
         <v>28</v>
       </c>
-      <c r="S408" s="1" t="str">
+      <c r="S409" s="1" t="str">
         <f t="shared" si="44"/>
         <v>2.5-5</v>
       </c>
-      <c r="T408" s="1" t="str">
+      <c r="T409" s="1" t="str">
         <f t="shared" si="44"/>
         <v>5-10</v>
       </c>
-      <c r="U408" s="1" t="str">
+      <c r="U409" s="1" t="str">
         <f t="shared" si="44"/>
         <v>30-60</v>
       </c>
-      <c r="V408" s="1">
-        <f t="shared" ref="V408" si="53">_xlfn.LET(_xlpm.a,($E408+U$3*$G408)*(1+U$2),_xlpm.b,($F408+U$3*$H408)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
+      <c r="V409" s="1">
+        <f t="shared" ref="V409" si="53">_xlfn.LET(_xlpm.a,($E409+U$3*$G409)*(1+U$2),_xlpm.b,($F409+U$3*$H409)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
         <v>45</v>
-      </c>
-    </row>
-    <row r="409" spans="1:22">
-      <c r="A409" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="B409" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="C409" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D409" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="E409" s="1">
-        <v>5</v>
-      </c>
-      <c r="F409" s="1">
-        <v>10</v>
-      </c>
-      <c r="G409" s="1">
-        <v>1.25</v>
-      </c>
-      <c r="H409" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="N409" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="O409" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="P409" s="1">
-        <v>25</v>
-      </c>
-      <c r="Q409" s="1">
-        <v>28</v>
-      </c>
-      <c r="S409" s="1" t="str">
-        <f t="shared" si="44"/>
-        <v>5-10</v>
-      </c>
-      <c r="T409" s="1" t="str">
-        <f t="shared" si="44"/>
-        <v>10-20</v>
-      </c>
-      <c r="U409" s="1" t="str">
-        <f t="shared" si="44"/>
-        <v>60-120</v>
-      </c>
-      <c r="V409" s="1">
-        <f t="shared" ref="V409:V412" si="54">_xlfn.LET(_xlpm.a,($E409+U$3*$G409)*(1+U$2),_xlpm.b,($F409+U$3*$H409)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
-        <v>90</v>
       </c>
     </row>
     <row r="410" spans="1:22">
       <c r="A410" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D410" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E410" s="1">
         <v>5</v>
@@ -26463,10 +26466,10 @@
         <v>2.5</v>
       </c>
       <c r="N410" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O410" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P410" s="1">
         <v>25</v>
@@ -26487,22 +26490,22 @@
         <v>60-120</v>
       </c>
       <c r="V410" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" ref="V410:V413" si="54">_xlfn.LET(_xlpm.a,($E410+U$3*$G410)*(1+U$2),_xlpm.b,($F410+U$3*$H410)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
         <v>90</v>
       </c>
     </row>
     <row r="411" spans="1:22">
       <c r="A411" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E411" s="1">
         <v>5</v>
@@ -26517,10 +26520,10 @@
         <v>2.5</v>
       </c>
       <c r="N411" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O411" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P411" s="1">
         <v>25</v>
@@ -26547,16 +26550,16 @@
     </row>
     <row r="412" spans="1:22">
       <c r="A412" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E412" s="1">
         <v>5</v>
@@ -26571,10 +26574,10 @@
         <v>2.5</v>
       </c>
       <c r="N412" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O412" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P412" s="1">
         <v>25</v>
@@ -26600,68 +26603,71 @@
       </c>
     </row>
     <row r="413" spans="1:22">
-      <c r="A413" s="6" t="s">
-        <v>619</v>
+      <c r="A413" s="1" t="s">
+        <v>298</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>619</v>
+        <v>542</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D413" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E413" s="1">
         <v>5</v>
       </c>
       <c r="F413" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G413" s="1">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="H413" s="1">
-        <v>0</v>
-      </c>
-      <c r="I413" s="1">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N413" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="O413" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
+      </c>
+      <c r="P413" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q413" s="1">
+        <v>28</v>
       </c>
       <c r="S413" s="1" t="str">
         <f t="shared" si="44"/>
-        <v>5-5</v>
+        <v>5-10</v>
       </c>
       <c r="T413" s="1" t="str">
         <f t="shared" si="44"/>
-        <v>5-5</v>
+        <v>10-20</v>
       </c>
       <c r="U413" s="1" t="str">
         <f t="shared" si="44"/>
-        <v>30-30</v>
+        <v>60-120</v>
       </c>
       <c r="V413" s="1">
-        <f t="shared" ref="V413:V417" si="55">_xlfn.LET(_xlpm.a,($E413+U$3*$G413)*(1+U$2),_xlpm.b,($F413+U$3*$H413)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
-        <v>30</v>
+        <f t="shared" si="54"/>
+        <v>90</v>
       </c>
     </row>
     <row r="414" spans="1:22">
       <c r="A414" s="6" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E414" s="1">
         <v>5</v>
@@ -26679,40 +26685,40 @@
         <v>0</v>
       </c>
       <c r="N414" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O414" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="S414" s="1" t="str">
-        <f t="shared" ref="S414:U417" si="56">_xlfn.LET(_xlpm.a,($E414+S$3*$G414)*(1+S$2),_xlpm.b,($F414+S$3*$H414)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
+        <f t="shared" si="44"/>
         <v>5-5</v>
       </c>
       <c r="T414" s="1" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="44"/>
         <v>5-5</v>
       </c>
       <c r="U414" s="1" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="44"/>
         <v>30-30</v>
       </c>
       <c r="V414" s="1">
-        <f t="shared" si="55"/>
+        <f t="shared" ref="V414:V418" si="55">_xlfn.LET(_xlpm.a,($E414+U$3*$G414)*(1+U$2),_xlpm.b,($F414+U$3*$H414)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
         <v>30</v>
       </c>
     </row>
     <row r="415" spans="1:22">
       <c r="A415" s="6" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D415" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E415" s="1">
         <v>5</v>
@@ -26730,13 +26736,13 @@
         <v>0</v>
       </c>
       <c r="N415" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O415" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="S415" s="1" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" ref="S415:U418" si="56">_xlfn.LET(_xlpm.a,($E415+S$3*$G415)*(1+S$2),_xlpm.b,($F415+S$3*$H415)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
         <v>5-5</v>
       </c>
       <c r="T415" s="1" t="str">
@@ -26754,16 +26760,16 @@
     </row>
     <row r="416" spans="1:22">
       <c r="A416" s="6" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E416" s="1">
         <v>5</v>
@@ -26781,10 +26787,10 @@
         <v>0</v>
       </c>
       <c r="N416" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O416" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="S416" s="1" t="str">
         <f t="shared" si="56"/>
@@ -26805,16 +26811,16 @@
     </row>
     <row r="417" spans="1:22">
       <c r="A417" s="6" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E417" s="1">
         <v>5</v>
@@ -26832,10 +26838,10 @@
         <v>0</v>
       </c>
       <c r="N417" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O417" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="S417" s="1" t="str">
         <f t="shared" si="56"/>
@@ -26855,23 +26861,23 @@
       </c>
     </row>
     <row r="418" spans="1:22">
-      <c r="A418" s="1" t="s">
-        <v>971</v>
+      <c r="A418" s="6" t="s">
+        <v>623</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>971</v>
+        <v>623</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D418" s="1" t="s">
-        <v>971</v>
+        <v>292</v>
       </c>
       <c r="E418" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F418" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G418" s="1">
         <v>0</v>
@@ -26881,20 +26887,42 @@
       </c>
       <c r="I418" s="1">
         <v>0</v>
+      </c>
+      <c r="N418" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="O418" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="S418" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>5-5</v>
+      </c>
+      <c r="T418" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>5-5</v>
+      </c>
+      <c r="U418" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>30-30</v>
+      </c>
+      <c r="V418" s="1">
+        <f t="shared" si="55"/>
+        <v>30</v>
       </c>
     </row>
     <row r="419" spans="1:22">
       <c r="A419" s="1" t="s">
-        <v>371</v>
+        <v>971</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>371</v>
+        <v>971</v>
       </c>
       <c r="C419" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>371</v>
+        <v>971</v>
       </c>
       <c r="E419" s="1">
         <v>1</v>
@@ -26910,36 +26938,20 @@
       </c>
       <c r="I419" s="1">
         <v>0</v>
-      </c>
-      <c r="S419" s="1" t="str">
-        <f t="shared" ref="S419:U420" si="57">_xlfn.LET(_xlpm.a,($E419+S$3*$G419)*(1+S$2),_xlpm.b,($F419+S$3*$H419)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
-        <v>1-1</v>
-      </c>
-      <c r="T419" s="1" t="str">
-        <f t="shared" si="57"/>
-        <v>1-1</v>
-      </c>
-      <c r="U419" s="1" t="str">
-        <f t="shared" si="57"/>
-        <v>6-6</v>
-      </c>
-      <c r="V419" s="1">
-        <f t="shared" ref="V419" si="58">_xlfn.LET(_xlpm.a,($E419+U$3*$G419)*(1+U$2),_xlpm.b,($F419+U$3*$H419)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
-        <v>6</v>
       </c>
     </row>
     <row r="420" spans="1:22">
       <c r="A420" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D420" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E420" s="1">
         <v>1</v>
@@ -26957,7 +26969,7 @@
         <v>0</v>
       </c>
       <c r="S420" s="1" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" ref="S420:U421" si="57">_xlfn.LET(_xlpm.a,($E420+S$3*$G420)*(1+S$2),_xlpm.b,($F420+S$3*$H420)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
         <v>1-1</v>
       </c>
       <c r="T420" s="1" t="str">
@@ -26969,96 +26981,112 @@
         <v>6-6</v>
       </c>
       <c r="V420" s="1">
-        <f t="shared" ref="V420:V439" si="59">_xlfn.LET(_xlpm.a,($E420+U$3*$G420)*(1+U$2),_xlpm.b,($F420+U$3*$H420)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <f t="shared" ref="V420" si="58">_xlfn.LET(_xlpm.a,($E420+U$3*$G420)*(1+U$2),_xlpm.b,($F420+U$3*$H420)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
         <v>6</v>
       </c>
     </row>
     <row r="421" spans="1:22">
       <c r="A421" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B421" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C421" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D421" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E421" s="1">
+        <v>1</v>
+      </c>
+      <c r="F421" s="1">
+        <v>1</v>
+      </c>
+      <c r="G421" s="1">
+        <v>0</v>
+      </c>
+      <c r="H421" s="1">
+        <v>0</v>
+      </c>
+      <c r="I421" s="1">
+        <v>0</v>
+      </c>
+      <c r="S421" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>1-1</v>
+      </c>
+      <c r="T421" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>1-1</v>
+      </c>
+      <c r="U421" s="1" t="str">
+        <f t="shared" si="57"/>
+        <v>6-6</v>
+      </c>
+      <c r="V421" s="1">
+        <f t="shared" ref="V421:V440" si="59">_xlfn.LET(_xlpm.a,($E421+U$3*$G421)*(1+U$2),_xlpm.b,($F421+U$3*$H421)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="422" spans="1:22">
+      <c r="A422" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B421" s="1" t="s">
+      <c r="B422" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="C421" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D421" s="1" t="s">
+      <c r="C422" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D422" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="E421" s="1">
-        <v>1</v>
-      </c>
-      <c r="F421" s="1">
-        <v>1</v>
-      </c>
-      <c r="G421" s="1">
-        <v>0</v>
-      </c>
-      <c r="H421" s="1">
-        <v>0</v>
-      </c>
-      <c r="I421" s="1">
-        <v>0</v>
-      </c>
-      <c r="S421" s="1" t="str">
-        <f t="shared" ref="S421:U438" si="60">_xlfn.LET(_xlpm.a,($E421+S$3*$G421)*(1+S$2),_xlpm.b,($F421+S$3*$H421)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
-        <v>1-1</v>
-      </c>
-      <c r="T421" s="1" t="str">
+      <c r="E422" s="1">
+        <v>1</v>
+      </c>
+      <c r="F422" s="1">
+        <v>1</v>
+      </c>
+      <c r="G422" s="1">
+        <v>0</v>
+      </c>
+      <c r="H422" s="1">
+        <v>0</v>
+      </c>
+      <c r="I422" s="1">
+        <v>0</v>
+      </c>
+      <c r="S422" s="1" t="str">
+        <f t="shared" ref="S422:U439" si="60">_xlfn.LET(_xlpm.a,($E422+S$3*$G422)*(1+S$2),_xlpm.b,($F422+S$3*$H422)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
+        <v>1-1</v>
+      </c>
+      <c r="T422" s="1" t="str">
         <f t="shared" si="60"/>
         <v>1-1</v>
       </c>
-      <c r="U421" s="1" t="str">
+      <c r="U422" s="1" t="str">
         <f t="shared" si="60"/>
         <v>6-6</v>
       </c>
-      <c r="V421" s="1">
+      <c r="V422" s="1">
         <f t="shared" si="59"/>
         <v>6</v>
       </c>
     </row>
-    <row r="422" spans="1:22">
-      <c r="A422" s="1" t="s">
-        <v>972</v>
-      </c>
-      <c r="B422" s="1" t="s">
-        <v>972</v>
-      </c>
-      <c r="C422" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D422" s="1" t="s">
-        <v>972</v>
-      </c>
-      <c r="E422" s="1">
-        <v>1</v>
-      </c>
-      <c r="F422" s="1">
-        <v>1</v>
-      </c>
-      <c r="G422" s="1">
-        <v>0</v>
-      </c>
-      <c r="H422" s="1">
-        <v>0</v>
-      </c>
-      <c r="I422" s="1">
-        <v>0</v>
-      </c>
-    </row>
     <row r="423" spans="1:22">
       <c r="A423" s="1" t="s">
-        <v>374</v>
+        <v>972</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>374</v>
+        <v>972</v>
       </c>
       <c r="C423" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>374</v>
+        <v>972</v>
       </c>
       <c r="E423" s="1">
         <v>1</v>
@@ -27074,36 +27102,20 @@
       </c>
       <c r="I423" s="1">
         <v>0</v>
-      </c>
-      <c r="S423" s="1" t="str">
-        <f t="shared" si="60"/>
-        <v>1-1</v>
-      </c>
-      <c r="T423" s="1" t="str">
-        <f t="shared" si="60"/>
-        <v>1-1</v>
-      </c>
-      <c r="U423" s="1" t="str">
-        <f t="shared" si="60"/>
-        <v>6-6</v>
-      </c>
-      <c r="V423" s="1">
-        <f t="shared" si="59"/>
-        <v>6</v>
       </c>
     </row>
     <row r="424" spans="1:22">
       <c r="A424" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C424" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E424" s="1">
         <v>1</v>
@@ -27139,16 +27151,16 @@
     </row>
     <row r="425" spans="1:22">
       <c r="A425" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C425" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D425" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E425" s="1">
         <v>1</v>
@@ -27184,16 +27196,16 @@
     </row>
     <row r="426" spans="1:22">
       <c r="A426" s="1" t="s">
-        <v>973</v>
+        <v>376</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>973</v>
+        <v>376</v>
       </c>
       <c r="C426" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>973</v>
+        <v>376</v>
       </c>
       <c r="E426" s="1">
         <v>1</v>
@@ -27209,20 +27221,36 @@
       </c>
       <c r="I426" s="1">
         <v>0</v>
+      </c>
+      <c r="S426" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>1-1</v>
+      </c>
+      <c r="T426" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>1-1</v>
+      </c>
+      <c r="U426" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>6-6</v>
+      </c>
+      <c r="V426" s="1">
+        <f t="shared" si="59"/>
+        <v>6</v>
       </c>
     </row>
     <row r="427" spans="1:22">
       <c r="A427" s="1" t="s">
-        <v>377</v>
+        <v>973</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>377</v>
+        <v>973</v>
       </c>
       <c r="C427" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>377</v>
+        <v>973</v>
       </c>
       <c r="E427" s="1">
         <v>1</v>
@@ -27238,36 +27266,20 @@
       </c>
       <c r="I427" s="1">
         <v>0</v>
-      </c>
-      <c r="S427" s="1" t="str">
-        <f t="shared" si="60"/>
-        <v>1-1</v>
-      </c>
-      <c r="T427" s="1" t="str">
-        <f t="shared" si="60"/>
-        <v>1-1</v>
-      </c>
-      <c r="U427" s="1" t="str">
-        <f t="shared" si="60"/>
-        <v>6-6</v>
-      </c>
-      <c r="V427" s="1">
-        <f t="shared" si="59"/>
-        <v>6</v>
       </c>
     </row>
     <row r="428" spans="1:22">
       <c r="A428" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C428" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E428" s="1">
         <v>1</v>
@@ -27303,16 +27315,16 @@
     </row>
     <row r="429" spans="1:22">
       <c r="A429" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C429" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E429" s="1">
         <v>1</v>
@@ -27348,16 +27360,16 @@
     </row>
     <row r="430" spans="1:22">
       <c r="A430" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C430" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E430" s="1">
         <v>1</v>
@@ -27392,17 +27404,17 @@
       </c>
     </row>
     <row r="431" spans="1:22">
-      <c r="A431" s="6" t="s">
-        <v>381</v>
+      <c r="A431" s="1" t="s">
+        <v>380</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C431" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D431" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E431" s="1">
         <v>1</v>
@@ -27437,17 +27449,17 @@
       </c>
     </row>
     <row r="432" spans="1:22">
-      <c r="A432" s="1" t="s">
-        <v>382</v>
+      <c r="A432" s="6" t="s">
+        <v>381</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C432" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D432" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E432" s="1">
         <v>1</v>
@@ -27483,16 +27495,16 @@
     </row>
     <row r="433" spans="1:22">
       <c r="A433" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C433" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E433" s="1">
         <v>1</v>
@@ -27528,16 +27540,16 @@
     </row>
     <row r="434" spans="1:22">
       <c r="A434" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C434" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D434" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E434" s="1">
         <v>1</v>
@@ -27573,16 +27585,16 @@
     </row>
     <row r="435" spans="1:22">
       <c r="A435" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C435" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E435" s="1">
         <v>1</v>
@@ -27618,16 +27630,16 @@
     </row>
     <row r="436" spans="1:22">
       <c r="A436" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C436" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E436" s="1">
         <v>1</v>
@@ -27663,16 +27675,16 @@
     </row>
     <row r="437" spans="1:22">
       <c r="A437" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C437" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E437" s="1">
         <v>1</v>
@@ -27708,16 +27720,16 @@
     </row>
     <row r="438" spans="1:22">
       <c r="A438" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C438" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D438" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E438" s="1">
         <v>1</v>
@@ -27753,189 +27765,205 @@
     </row>
     <row r="439" spans="1:22">
       <c r="A439" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B439" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C439" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D439" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E439" s="1">
+        <v>1</v>
+      </c>
+      <c r="F439" s="1">
+        <v>1</v>
+      </c>
+      <c r="G439" s="1">
+        <v>0</v>
+      </c>
+      <c r="H439" s="1">
+        <v>0</v>
+      </c>
+      <c r="I439" s="1">
+        <v>0</v>
+      </c>
+      <c r="S439" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>1-1</v>
+      </c>
+      <c r="T439" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>1-1</v>
+      </c>
+      <c r="U439" s="1" t="str">
+        <f t="shared" si="60"/>
+        <v>6-6</v>
+      </c>
+      <c r="V439" s="1">
+        <f t="shared" si="59"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="440" spans="1:22">
+      <c r="A440" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="B439" s="1" t="s">
+      <c r="B440" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="C439" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D439" s="1" t="s">
+      <c r="C440" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D440" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="E439" s="1">
-        <v>1</v>
-      </c>
-      <c r="F439" s="1">
-        <v>1</v>
-      </c>
-      <c r="G439" s="1">
-        <v>0</v>
-      </c>
-      <c r="H439" s="1">
+      <c r="E440" s="1">
+        <v>1</v>
+      </c>
+      <c r="F440" s="1">
+        <v>1</v>
+      </c>
+      <c r="G440" s="1">
+        <v>0</v>
+      </c>
+      <c r="H440" s="1">
         <v>2</v>
       </c>
-      <c r="K439" s="1" t="s">
+      <c r="K440" s="1" t="s">
         <v>948</v>
       </c>
-      <c r="L439" s="1" t="s">
+      <c r="L440" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="S439" s="1" t="str">
-        <f t="shared" ref="S439:U441" si="61">_xlfn.LET(_xlpm.a,($E439+S$3*$G439)*(1+S$2),_xlpm.b,($F439+S$3*$H439)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
-        <v>1-1</v>
-      </c>
-      <c r="T439" s="1" t="str">
+      <c r="S440" s="1" t="str">
+        <f t="shared" ref="S440:U442" si="61">_xlfn.LET(_xlpm.a,($E440+S$3*$G440)*(1+S$2),_xlpm.b,($F440+S$3*$H440)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
+        <v>1-1</v>
+      </c>
+      <c r="T440" s="1" t="str">
         <f t="shared" si="61"/>
         <v>1-9</v>
       </c>
-      <c r="U439" s="1" t="str">
+      <c r="U440" s="1" t="str">
         <f t="shared" si="61"/>
         <v>6-54</v>
       </c>
-      <c r="V439" s="1">
+      <c r="V440" s="1">
         <f t="shared" si="59"/>
         <v>30</v>
       </c>
     </row>
-    <row r="440" spans="1:22">
-      <c r="A440" s="6" t="s">
+    <row r="441" spans="1:22">
+      <c r="A441" s="6" t="s">
         <v>975</v>
       </c>
-      <c r="B440" s="1" t="s">
+      <c r="B441" s="1" t="s">
         <v>975</v>
       </c>
-      <c r="C440" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D440" s="1" t="s">
+      <c r="C441" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D441" s="1" t="s">
         <v>974</v>
       </c>
-      <c r="E440" s="1">
-        <v>1</v>
-      </c>
-      <c r="F440" s="1">
-        <v>1</v>
-      </c>
-      <c r="G440" s="1">
-        <v>0</v>
-      </c>
-      <c r="H440" s="1">
-        <v>0</v>
-      </c>
-      <c r="I440" s="1">
-        <v>0</v>
-      </c>
-      <c r="S440" s="1" t="str">
+      <c r="E441" s="1">
+        <v>1</v>
+      </c>
+      <c r="F441" s="1">
+        <v>1</v>
+      </c>
+      <c r="G441" s="1">
+        <v>0</v>
+      </c>
+      <c r="H441" s="1">
+        <v>0</v>
+      </c>
+      <c r="I441" s="1">
+        <v>0</v>
+      </c>
+      <c r="S441" s="1" t="str">
         <f t="shared" si="61"/>
         <v>1-1</v>
       </c>
-      <c r="T440" s="1" t="str">
+      <c r="T441" s="1" t="str">
         <f t="shared" si="61"/>
         <v>1-1</v>
       </c>
-      <c r="U440" s="1" t="str">
+      <c r="U441" s="1" t="str">
         <f t="shared" si="61"/>
         <v>6-6</v>
       </c>
-      <c r="V440" s="1">
-        <f t="shared" ref="V440:V441" si="62">_xlfn.LET(_xlpm.a,($E440+U$3*$G440)*(1+U$2),_xlpm.b,($F440+U$3*$H440)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
+      <c r="V441" s="1">
+        <f t="shared" ref="V441:V442" si="62">_xlfn.LET(_xlpm.a,($E441+U$3*$G441)*(1+U$2),_xlpm.b,($F441+U$3*$H441)*(1+U$2),_xlpm.a/2+_xlpm.b/2)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="441" spans="1:22">
-      <c r="A441" s="1" t="s">
+    <row r="442" spans="1:22">
+      <c r="A442" s="1" t="s">
         <v>976</v>
       </c>
-      <c r="B441" s="1" t="s">
+      <c r="B442" s="1" t="s">
         <v>976</v>
       </c>
-      <c r="C441" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D441" s="1" t="s">
+      <c r="C442" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D442" s="1" t="s">
         <v>976</v>
       </c>
-      <c r="E441" s="1">
+      <c r="E442" s="1">
         <v>5</v>
       </c>
-      <c r="F441" s="1">
+      <c r="F442" s="1">
         <v>10</v>
       </c>
-      <c r="G441" s="1">
-        <v>0</v>
-      </c>
-      <c r="H441" s="1">
-        <v>0</v>
-      </c>
-      <c r="I441" s="1">
-        <v>0</v>
-      </c>
-      <c r="S441" s="1" t="str">
+      <c r="G442" s="1">
+        <v>0</v>
+      </c>
+      <c r="H442" s="1">
+        <v>0</v>
+      </c>
+      <c r="I442" s="1">
+        <v>0</v>
+      </c>
+      <c r="S442" s="1" t="str">
         <f t="shared" si="61"/>
         <v>5-10</v>
       </c>
-      <c r="T441" s="1" t="str">
+      <c r="T442" s="1" t="str">
         <f t="shared" si="61"/>
         <v>5-10</v>
       </c>
-      <c r="U441" s="1" t="str">
+      <c r="U442" s="1" t="str">
         <f t="shared" si="61"/>
         <v>30-60</v>
       </c>
-      <c r="V441" s="1">
+      <c r="V442" s="1">
         <f t="shared" si="62"/>
         <v>45</v>
       </c>
     </row>
-    <row r="442" spans="1:22">
-      <c r="A442" s="1" t="s">
-        <v>977</v>
-      </c>
-      <c r="B442" s="1" t="s">
-        <v>977</v>
-      </c>
-      <c r="C442" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D442" s="1" t="s">
-        <v>977</v>
-      </c>
-      <c r="E442" s="1">
-        <v>1</v>
-      </c>
-      <c r="F442" s="1">
-        <v>1</v>
-      </c>
-      <c r="G442" s="1">
-        <v>0</v>
-      </c>
-      <c r="H442" s="1">
-        <v>0</v>
-      </c>
-      <c r="I442" s="1">
-        <v>0</v>
-      </c>
-    </row>
     <row r="443" spans="1:22">
       <c r="A443" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="C443" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D443" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E443" s="1">
         <v>1</v>
       </c>
       <c r="F443" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G443" s="1">
         <v>0</v>
@@ -27949,22 +27977,22 @@
     </row>
     <row r="444" spans="1:22">
       <c r="A444" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="C444" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E444" s="1">
         <v>1</v>
       </c>
       <c r="F444" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G444" s="1">
         <v>0</v>
@@ -27978,22 +28006,22 @@
     </row>
     <row r="445" spans="1:22">
       <c r="A445" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="C445" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D445" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="E445" s="1">
         <v>1</v>
       </c>
       <c r="F445" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G445" s="1">
         <v>0</v>
@@ -28007,22 +28035,22 @@
     </row>
     <row r="446" spans="1:22">
       <c r="A446" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="C446" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D446" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E446" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F446" s="1">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="G446" s="1">
         <v>0</v>
@@ -28036,22 +28064,22 @@
     </row>
     <row r="447" spans="1:22">
       <c r="A447" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="C447" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D447" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E447" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F447" s="1">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="G447" s="1">
         <v>0</v>
@@ -28065,22 +28093,22 @@
     </row>
     <row r="448" spans="1:22">
       <c r="A448" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C448" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E448" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F448" s="1">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="G448" s="1">
         <v>0</v>
@@ -28094,22 +28122,22 @@
     </row>
     <row r="449" spans="1:9">
       <c r="A449" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="C449" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D449" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="E449" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F449" s="1">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="G449" s="1">
         <v>0</v>
@@ -28123,22 +28151,22 @@
     </row>
     <row r="450" spans="1:9">
       <c r="A450" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="C450" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="E450" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F450" s="1">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G450" s="1">
         <v>0</v>
@@ -28152,22 +28180,22 @@
     </row>
     <row r="451" spans="1:9">
       <c r="A451" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C451" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D451" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E451" s="1">
-        <v>15</v>
+        <v>0.5</v>
       </c>
       <c r="F451" s="1">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="G451" s="1">
         <v>0</v>
@@ -28181,22 +28209,22 @@
     </row>
     <row r="452" spans="1:9">
       <c r="A452" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C452" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D452" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E452" s="1">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F452" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G452" s="1">
         <v>0</v>
@@ -28210,22 +28238,22 @@
     </row>
     <row r="453" spans="1:9">
       <c r="A453" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="C453" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D453" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="E453" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F453" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G453" s="1">
         <v>0</v>
@@ -28239,22 +28267,22 @@
     </row>
     <row r="454" spans="1:9">
       <c r="A454" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="C454" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D454" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E454" s="1">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F454" s="1">
-        <v>300</v>
+        <v>15</v>
       </c>
       <c r="G454" s="1">
         <v>0</v>
@@ -28268,22 +28296,22 @@
     </row>
     <row r="455" spans="1:9">
       <c r="A455" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C455" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D455" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E455" s="1">
+        <v>100</v>
+      </c>
+      <c r="F455" s="1">
         <v>300</v>
-      </c>
-      <c r="F455" s="1">
-        <v>800</v>
       </c>
       <c r="G455" s="1">
         <v>0</v>
@@ -28297,22 +28325,22 @@
     </row>
     <row r="456" spans="1:9">
       <c r="A456" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="C456" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D456" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="E456" s="1">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="F456" s="1">
-        <v>15</v>
+        <v>800</v>
       </c>
       <c r="G456" s="1">
         <v>0</v>
@@ -28326,22 +28354,22 @@
     </row>
     <row r="457" spans="1:9">
       <c r="A457" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="C457" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D457" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="E457" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F457" s="1">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G457" s="1">
         <v>0</v>
@@ -28355,22 +28383,22 @@
     </row>
     <row r="458" spans="1:9">
       <c r="A458" s="1" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="C458" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D458" s="1" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E458" s="1">
+        <v>1</v>
+      </c>
+      <c r="F458" s="1">
         <v>3</v>
-      </c>
-      <c r="F458" s="1">
-        <v>9</v>
       </c>
       <c r="G458" s="1">
         <v>0</v>
@@ -28384,7 +28412,7 @@
     </row>
     <row r="459" spans="1:9">
       <c r="A459" s="1" t="s">
-        <v>1061</v>
+        <v>993</v>
       </c>
       <c r="B459" s="1" t="s">
         <v>993</v>
@@ -28393,7 +28421,7 @@
         <v>39</v>
       </c>
       <c r="D459" s="1" t="s">
-        <v>1061</v>
+        <v>993</v>
       </c>
       <c r="E459" s="1">
         <v>3</v>
@@ -28413,7 +28441,7 @@
     </row>
     <row r="460" spans="1:9">
       <c r="A460" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B460" s="1" t="s">
         <v>993</v>
@@ -28422,7 +28450,7 @@
         <v>39</v>
       </c>
       <c r="D460" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E460" s="1">
         <v>3</v>
@@ -28442,7 +28470,7 @@
     </row>
     <row r="461" spans="1:9">
       <c r="A461" s="1" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B461" s="1" t="s">
         <v>993</v>
@@ -28451,7 +28479,7 @@
         <v>39</v>
       </c>
       <c r="D461" s="1" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="E461" s="1">
         <v>3</v>
@@ -28471,7 +28499,7 @@
     </row>
     <row r="462" spans="1:9">
       <c r="A462" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B462" s="1" t="s">
         <v>993</v>
@@ -28480,7 +28508,7 @@
         <v>39</v>
       </c>
       <c r="D462" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="E462" s="1">
         <v>3</v>
@@ -28500,7 +28528,7 @@
     </row>
     <row r="463" spans="1:9">
       <c r="A463" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B463" s="1" t="s">
         <v>993</v>
@@ -28509,7 +28537,7 @@
         <v>39</v>
       </c>
       <c r="D463" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="E463" s="1">
         <v>3</v>
@@ -28529,22 +28557,22 @@
     </row>
     <row r="464" spans="1:9">
       <c r="A464" s="1" t="s">
-        <v>994</v>
+        <v>1065</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D464" s="1" t="s">
-        <v>994</v>
+        <v>1065</v>
       </c>
       <c r="E464" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F464" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G464" s="1">
         <v>0</v>
@@ -28558,22 +28586,22 @@
     </row>
     <row r="465" spans="1:9">
       <c r="A465" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="C465" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D465" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="E465" s="1">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F465" s="1">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G465" s="1">
         <v>0</v>
@@ -28587,22 +28615,22 @@
     </row>
     <row r="466" spans="1:9">
       <c r="A466" s="1" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="C466" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D466" s="1" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="E466" s="1">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F466" s="1">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="G466" s="1">
         <v>0</v>
@@ -28616,22 +28644,22 @@
     </row>
     <row r="467" spans="1:9">
       <c r="A467" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="C467" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D467" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E467" s="1">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F467" s="1">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="G467" s="1">
         <v>0</v>
@@ -28645,22 +28673,22 @@
     </row>
     <row r="468" spans="1:9">
       <c r="A468" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C468" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D468" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E468" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F468" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G468" s="1">
         <v>0</v>
@@ -28674,22 +28702,22 @@
     </row>
     <row r="469" spans="1:9">
       <c r="A469" s="1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D469" s="1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E469" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F469" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G469" s="1">
         <v>0</v>
@@ -28703,22 +28731,22 @@
     </row>
     <row r="470" spans="1:9">
       <c r="A470" s="1" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="C470" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D470" s="1" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E470" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F470" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G470" s="1">
         <v>0</v>
@@ -28732,16 +28760,16 @@
     </row>
     <row r="471" spans="1:9">
       <c r="A471" s="1" t="s">
-        <v>1066</v>
+        <v>1000</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>1066</v>
+        <v>1000</v>
       </c>
       <c r="C471" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D471" s="1" t="s">
-        <v>1066</v>
+        <v>1000</v>
       </c>
       <c r="E471" s="1">
         <v>1</v>
@@ -28761,22 +28789,22 @@
     </row>
     <row r="472" spans="1:9">
       <c r="A472" s="1" t="s">
-        <v>1001</v>
+        <v>1066</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>1001</v>
+        <v>1066</v>
       </c>
       <c r="C472" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D472" s="1" t="s">
-        <v>1001</v>
+        <v>1066</v>
       </c>
       <c r="E472" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F472" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G472" s="1">
         <v>0</v>
@@ -28790,22 +28818,22 @@
     </row>
     <row r="473" spans="1:9">
       <c r="A473" s="1" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C473" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D473" s="1" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E473" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F473" s="1">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G473" s="1">
         <v>0</v>
@@ -28819,22 +28847,22 @@
     </row>
     <row r="474" spans="1:9">
       <c r="A474" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C474" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D474" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E474" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F474" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G474" s="1">
         <v>0</v>
@@ -28848,22 +28876,22 @@
     </row>
     <row r="475" spans="1:9">
       <c r="A475" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C475" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D475" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="E475" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F475" s="1">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G475" s="1">
         <v>0</v>
@@ -28877,22 +28905,22 @@
     </row>
     <row r="476" spans="1:9">
       <c r="A476" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C476" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D476" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E476" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F476" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G476" s="1">
         <v>0</v>
@@ -28906,22 +28934,22 @@
     </row>
     <row r="477" spans="1:9">
       <c r="A477" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C477" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D477" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="E477" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F477" s="1">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G477" s="1">
         <v>0</v>
@@ -28935,22 +28963,22 @@
     </row>
     <row r="478" spans="1:9">
       <c r="A478" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C478" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D478" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E478" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F478" s="1">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="G478" s="1">
         <v>0</v>
@@ -28964,22 +28992,22 @@
     </row>
     <row r="479" spans="1:9">
       <c r="A479" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C479" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D479" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="E479" s="1">
         <v>100</v>
       </c>
       <c r="F479" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G479" s="1">
         <v>0</v>
@@ -28993,22 +29021,22 @@
     </row>
     <row r="480" spans="1:9">
       <c r="A480" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C480" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D480" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E480" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F480" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="G480" s="1">
         <v>0</v>
@@ -29022,16 +29050,16 @@
     </row>
     <row r="481" spans="1:9">
       <c r="A481" s="1" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D481" s="1" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="E481" s="1">
         <v>1</v>
@@ -29051,16 +29079,16 @@
     </row>
     <row r="482" spans="1:9">
       <c r="A482" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C482" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D482" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E482" s="1">
         <v>1</v>
@@ -29080,22 +29108,22 @@
     </row>
     <row r="483" spans="1:9">
       <c r="A483" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C483" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D483" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="E483" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F483" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G483" s="1">
         <v>0</v>
@@ -29109,22 +29137,22 @@
     </row>
     <row r="484" spans="1:9">
       <c r="A484" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C484" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D484" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="E484" s="1">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F484" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G484" s="1">
         <v>0</v>
@@ -29138,22 +29166,22 @@
     </row>
     <row r="485" spans="1:9">
       <c r="A485" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D485" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="E485" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F485" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G485" s="1">
         <v>0</v>
@@ -29167,16 +29195,16 @@
     </row>
     <row r="486" spans="1:9">
       <c r="A486" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D486" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="E486" s="1">
         <v>1</v>
@@ -29196,16 +29224,16 @@
     </row>
     <row r="487" spans="1:9">
       <c r="A487" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="C487" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D487" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="E487" s="1">
         <v>1</v>
@@ -29225,22 +29253,22 @@
     </row>
     <row r="488" spans="1:9">
       <c r="A488" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C488" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D488" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E488" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F488" s="1">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="G488" s="1">
         <v>0</v>
@@ -29254,22 +29282,22 @@
     </row>
     <row r="489" spans="1:9">
       <c r="A489" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C489" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D489" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E489" s="1">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F489" s="1">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="G489" s="1">
         <v>0</v>
@@ -29283,22 +29311,22 @@
     </row>
     <row r="490" spans="1:9">
       <c r="A490" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C490" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D490" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="E490" s="1">
         <v>5</v>
       </c>
       <c r="F490" s="1">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G490" s="1">
         <v>0</v>
@@ -29312,22 +29340,22 @@
     </row>
     <row r="491" spans="1:9">
       <c r="A491" s="1" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C491" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="E491" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F491" s="1">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G491" s="1">
         <v>0</v>
@@ -29341,79 +29369,111 @@
     </row>
     <row r="492" spans="1:9">
       <c r="A492" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B492" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C492" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D492" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E492" s="1">
+        <v>1</v>
+      </c>
+      <c r="F492" s="1">
+        <v>1</v>
+      </c>
+      <c r="G492" s="1">
+        <v>0</v>
+      </c>
+      <c r="H492" s="1">
+        <v>0</v>
+      </c>
+      <c r="I492" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="1:9">
+      <c r="A493" s="1" t="s">
         <v>1021</v>
       </c>
-      <c r="B492" s="1" t="s">
+      <c r="B493" s="1" t="s">
         <v>1021</v>
       </c>
-      <c r="C492" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D492" s="1" t="s">
+      <c r="C493" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D493" s="1" t="s">
         <v>1021</v>
       </c>
-      <c r="E492" s="1">
+      <c r="E493" s="1">
         <v>15</v>
       </c>
-      <c r="F492" s="1">
+      <c r="F493" s="1">
         <v>30</v>
       </c>
-      <c r="G492" s="1">
-        <v>0</v>
-      </c>
-      <c r="H492" s="1">
-        <v>0</v>
-      </c>
-      <c r="I492" s="1">
+      <c r="G493" s="1">
+        <v>0</v>
+      </c>
+      <c r="H493" s="1">
+        <v>0</v>
+      </c>
+      <c r="I493" s="1">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:V492" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:V493" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A441:A492">
-    <cfRule type="duplicateValues" dxfId="14" priority="58"/>
+  <conditionalFormatting sqref="A442:A493">
+    <cfRule type="duplicateValues" dxfId="15" priority="59"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A493:A1048576 A183:A439 A1:A181">
-    <cfRule type="duplicateValues" dxfId="13" priority="50"/>
+  <conditionalFormatting sqref="A494:A1048576 A183:A440 A1:A181">
+    <cfRule type="duplicateValues" dxfId="14" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B180">
-    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B195">
-    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B471">
-    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
+  <conditionalFormatting sqref="B472">
+    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D182">
-    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D418">
+  <conditionalFormatting sqref="D419">
+    <cfRule type="duplicateValues" dxfId="9" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D423">
     <cfRule type="duplicateValues" dxfId="8" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D422">
-    <cfRule type="duplicateValues" dxfId="7" priority="18"/>
+  <conditionalFormatting sqref="D427">
+    <cfRule type="duplicateValues" dxfId="7" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D426">
-    <cfRule type="duplicateValues" dxfId="6" priority="15"/>
+  <conditionalFormatting sqref="D441">
+    <cfRule type="duplicateValues" dxfId="6" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D440">
-    <cfRule type="duplicateValues" dxfId="5" priority="13"/>
+  <conditionalFormatting sqref="D442:D458 D465:D471 D473:D493">
+    <cfRule type="duplicateValues" dxfId="5" priority="61"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D441:D457 D464:D470 D472:D492">
-    <cfRule type="duplicateValues" dxfId="4" priority="60"/>
+  <conditionalFormatting sqref="D459:D464">
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D458:D463">
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+  <conditionalFormatting sqref="D472">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D471">
+  <conditionalFormatting sqref="B199">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B199">
+  <conditionalFormatting sqref="B201">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B201">
+  <conditionalFormatting sqref="B354">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/configs/Affix.xlsx
+++ b/configs/Affix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E67A8F-77D0-4223-ABB6-A41943BA64A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0685330E-D549-4470-B1C0-815CCB047020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1770" yWindow="1770" windowWidth="30825" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3842,15 +3842,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X493"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.90625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="8" style="1" customWidth="1"/>
-    <col min="5" max="8" width="6.36328125" style="1" customWidth="1"/>
-    <col min="9" max="12" width="7.26953125" style="1" customWidth="1"/>
-    <col min="13" max="22" width="7.90625" style="1" customWidth="1"/>
+    <col min="5" max="8" width="6.42578125" style="1" customWidth="1"/>
+    <col min="9" max="12" width="7.28515625" style="1" customWidth="1"/>
+    <col min="13" max="22" width="7.85546875" style="1" customWidth="1"/>
     <col min="23" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -6798,7 +6798,7 @@
         <v>838</v>
       </c>
       <c r="R60" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S60" s="1" t="str">
         <f t="shared" si="7"/>
@@ -6846,7 +6846,7 @@
         <v>838</v>
       </c>
       <c r="R61" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S61" s="1" t="str">
         <f t="shared" si="7"/>
@@ -14131,7 +14131,7 @@
         <v>228</v>
       </c>
       <c r="R196" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S196" s="1" t="str">
         <f t="shared" si="25"/>
@@ -14220,7 +14220,7 @@
         <v>229</v>
       </c>
       <c r="R198" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S198" s="1" t="str">
         <f t="shared" ref="S198:U209" si="27">_xlfn.LET(_xlpm.a,($E198+S$3*$G198)*(1+S$2),_xlpm.b,($F198+S$3*$H198)*(1+S$2),_xlpm.a&amp;"-"&amp;_xlpm.b)</f>
@@ -14303,7 +14303,7 @@
         <v>840</v>
       </c>
       <c r="R200" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S200" s="1" t="str">
         <f t="shared" si="27"/>
@@ -14386,7 +14386,7 @@
         <v>235</v>
       </c>
       <c r="R202" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S202" s="1" t="str">
         <f t="shared" si="27"/>
@@ -29440,41 +29440,41 @@
   <conditionalFormatting sqref="B195">
     <cfRule type="duplicateValues" dxfId="12" priority="8"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B199">
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B201">
+    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B354">
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B472">
-    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D182">
-    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D419">
-    <cfRule type="duplicateValues" dxfId="9" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D423">
-    <cfRule type="duplicateValues" dxfId="8" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D427">
-    <cfRule type="duplicateValues" dxfId="7" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D441">
-    <cfRule type="duplicateValues" dxfId="6" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D442:D458 D465:D471 D473:D493">
-    <cfRule type="duplicateValues" dxfId="5" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D459:D464">
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D472">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B199">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B201">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B354">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
